--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="372">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -917,6 +917,26 @@
   </si>
   <si>
     <t>106</t>
+  </si>
+  <si>
+    <t>* Select which teams or groups are in scope for the planned assessments
+* Select which capabilities/actions are in scope for each group's assessment
+* Select weights for each included action based on goals of the assessment and importance to the business
+* Set a preliminary target score for each included action to use for comparison
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>* Use objective (not subjective) scoring metrics for assessment evaluation
+* Document how metrics used in the assessment are calculated and state all assumptions
+* Use the same calculation assumptions and formulas across scopes if possible
+* List relevant documentation of process and policy as evidentiary support for each score
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>* Complete an initial assessment for different scopes of the business to establish a baseline
+* Plot scores over time to track maturity progress for priority scopes
+* Complete analysis on what contributed to or hindered progress across scopes or different areas of the assessment
+10*Ceil(x/3)</t>
   </si>
   <si>
     <t>* Define process for reviewing asking for credits from CSPs
@@ -1068,10 +1088,45 @@
 10*Ceil(x/4)</t>
   </si>
   <si>
+    <t>* Defined scope of each project to be estimated
+* Developed list of known inputs to the project
+* Have a process to determine what may be missing from the inputs or scope
+* Have a policy review to determine additional needs for inputs or scope
+* For each component of the estimate, list all assumptions
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Inventory possible commitment based discounts (RIs, Savings Plans, CUDs, etc.) available for deployed resources
+* Consider any private negotiated line item discounts vs public RI/CUD discounts
+* Set resource type standards to make use of spend commitments while maintaining needs of the business
+* Scenario plan commitment options versus potential changes in resources
+* Reference commit allocation strategy to calculate cost impact of shared scope vs private account commitments
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Use pricing lists or pricing calculators to estimate workload spend
+* Run workloads as trial experiments to get baseline spend
+* Estimate workload costs based on similar applications already deployed in your environment
+* Determine fixed costs vs formulas for variable costs due to growth of workloads
+* Factor in discounts and uptime metrics to determine accurate spend vs list
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>1. Calculate kg of carbon dioxide equivalents (kgCO2e), or similar, for new and ongoing workloads
+2. Compare carbon calculations with targets for new projects and overall consumption</t>
+  </si>
+  <si>
     <t>* Define and follow process for gathering deployment plans from teams
 * Determine timeline for each new project to adjust the forecast during that time
 * Determine how optimizations and lower run rate will impact the forecast on a rolling basis
 10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Refer teams to Documented Estimating Scope &amp; Policy and include these methods in trainings
+* Teams track baseline spend for resources they own, and share changes to baseline with leadership
+* Teams will share updates about their change in usage of shared resources and dependencies
+* Track team adoption of better estimates via KPIs around baseline or plan vs actuals
+10*Ceil(x/4)</t>
   </si>
   <si>
     <t>* Define cost drivers from finance/business
@@ -1081,6 +1136,15 @@
 10*Ceil(x/4)</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': '0 items completed'}, {'Score': 3, 'Condition': '1 item completed'}, {'Score': 5, 'Condition': '2 items completed'}, {'Score': 8, 'Condition': '3 items completed'}, {'Score': 10, 'Condition': '4 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': '1 item completed'}, {'Score': 5, 'Condition': '2 items completed'}, {'Score': 8, 'Condition': '3 items completed'}, {'Score': 10, 'Condition': '4 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 4, 'Condition': '1 item completed'}, {'Score': 7, 'Condition': '2 items completed'}, {'Score': 10, 'Condition': '3 items completed'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': None}]</t>
   </si>
   <si>
@@ -1099,9 +1163,6 @@
     <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Done and clearly defined'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 4, 'Condition': '1 item completed'}, {'Score': 7, 'Condition': '2 items completed'}, {'Score': 10, 'Condition': '3 items completed'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'Does not exist'}, {'Score': 10, 'Condition': 'Exists'}]</t>
   </si>
   <si>
@@ -1123,9 +1184,6 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item  completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': '1 item completed'}, {'Score': 5, 'Condition': '2 items completed'}, {'Score': 8, 'Condition': '3 items completed'}, {'Score': 10, 'Condition': '4 items completed'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 7, 'Condition': '4 items completed'}, {'Score': 9, 'Condition': '5 items completed'}, {'Score': 10, 'Condition': '6 items completed'}]</t>
   </si>
   <si>
@@ -1150,16 +1208,22 @@
     <t>[{'Score': 0, 'Condition': 'No alerting'}, {'Score': 10, 'Condition': 'Alerting exists'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': 'item 1 completed'}, {'Score': 10, 'Condition': 'item 2 completed'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 10, 'Condition': 'set goal thresholds for kpis and unit costs'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'Not monitored'}, {'Score': 2, 'Condition': 'Reported'}, {'Score': 5, 'Condition': 'Manual remediation'}, {'Score': 10, 'Condition': 'Automated remediation'}]</t>
   </si>
   <si>
+    <t>0: 0 items completed</t>
+  </si>
+  <si>
+    <t>0: No items completed</t>
+  </si>
+  <si>
     <t>0: None</t>
-  </si>
-  <si>
-    <t>0: No items completed</t>
   </si>
   <si>
     <t>0: Not done</t>
@@ -2509,10 +2573,13 @@
         <v>171</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="H2">
         <f>E2*VALUE(LEFT(G2, FIND(":", G2)-1))</f>
@@ -2535,10 +2602,13 @@
         <v>172</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="H3">
         <f>E3*VALUE(LEFT(G3, FIND(":", G3)-1))</f>
@@ -2561,10 +2631,13 @@
         <v>173</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="H4">
         <f>E4*VALUE(LEFT(G4, FIND(":", G4)-1))</f>
@@ -2590,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H5">
         <f>E5*VALUE(LEFT(G5, FIND(":", G5)-1))</f>
@@ -2616,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H6">
         <f>E6*VALUE(LEFT(G6, FIND(":", G6)-1))</f>
@@ -2644,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H7">
         <f>E7*VALUE(LEFT(G7, FIND(":", G7)-1))</f>
@@ -2670,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H8">
         <f>E8*VALUE(LEFT(G8, FIND(":", G8)-1))</f>
@@ -2696,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H9">
         <f>E9*VALUE(LEFT(G9, FIND(":", G9)-1))</f>
@@ -2722,10 +2795,10 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H10">
         <f>E10*VALUE(LEFT(G10, FIND(":", G10)-1))</f>
@@ -2751,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H11">
         <f>E11*VALUE(LEFT(G11, FIND(":", G11)-1))</f>
@@ -2779,7 +2852,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="H12">
         <f>E12*VALUE(LEFT(G12, FIND(":", G12)-1))</f>
@@ -2805,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H13">
         <f>E13*VALUE(LEFT(G13, FIND(":", G13)-1))</f>
@@ -2831,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H14">
         <f>E14*VALUE(LEFT(G14, FIND(":", G14)-1))</f>
@@ -2857,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H15">
         <f>E15*VALUE(LEFT(G15, FIND(":", G15)-1))</f>
@@ -2883,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H16">
         <f>E16*VALUE(LEFT(G16, FIND(":", G16)-1))</f>
@@ -2909,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H17">
         <f>E17*VALUE(LEFT(G17, FIND(":", G17)-1))</f>
@@ -2937,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H18">
         <f>E18*VALUE(LEFT(G18, FIND(":", G18)-1))</f>
@@ -2963,7 +3036,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="H19">
         <f>E19*VALUE(LEFT(G19, FIND(":", G19)-1))</f>
@@ -2989,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H20">
         <f>E20*VALUE(LEFT(G20, FIND(":", G20)-1))</f>
@@ -3015,10 +3088,10 @@
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H21">
         <f>E21*VALUE(LEFT(G21, FIND(":", G21)-1))</f>
@@ -3044,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H22">
         <f>E22*VALUE(LEFT(G22, FIND(":", G22)-1))</f>
@@ -3072,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H23">
         <f>E23*VALUE(LEFT(G23, FIND(":", G23)-1))</f>
@@ -3098,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H24">
         <f>E24*VALUE(LEFT(G24, FIND(":", G24)-1))</f>
@@ -3124,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H25">
         <f>E25*VALUE(LEFT(G25, FIND(":", G25)-1))</f>
@@ -3150,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H26">
         <f>E26*VALUE(LEFT(G26, FIND(":", G26)-1))</f>
@@ -3176,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H27">
         <f>E27*VALUE(LEFT(G27, FIND(":", G27)-1))</f>
@@ -3202,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H28">
         <f>E28*VALUE(LEFT(G28, FIND(":", G28)-1))</f>
@@ -3230,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H29">
         <f>E29*VALUE(LEFT(G29, FIND(":", G29)-1))</f>
@@ -3256,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H30">
         <f>E30*VALUE(LEFT(G30, FIND(":", G30)-1))</f>
@@ -3282,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="H31">
         <f>E31*VALUE(LEFT(G31, FIND(":", G31)-1))</f>
@@ -3308,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H32">
         <f>E32*VALUE(LEFT(G32, FIND(":", G32)-1))</f>
@@ -3334,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H33">
         <f>E33*VALUE(LEFT(G33, FIND(":", G33)-1))</f>
@@ -3360,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="H34">
         <f>E34*VALUE(LEFT(G34, FIND(":", G34)-1))</f>
@@ -3388,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H35">
         <f>E35*VALUE(LEFT(G35, FIND(":", G35)-1))</f>
@@ -3414,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H36">
         <f>E36*VALUE(LEFT(G36, FIND(":", G36)-1))</f>
@@ -3440,10 +3513,10 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H37">
         <f>E37*VALUE(LEFT(G37, FIND(":", G37)-1))</f>
@@ -3469,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H38">
         <f>E38*VALUE(LEFT(G38, FIND(":", G38)-1))</f>
@@ -3495,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H39">
         <f>E39*VALUE(LEFT(G39, FIND(":", G39)-1))</f>
@@ -3521,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H40">
         <f>E40*VALUE(LEFT(G40, FIND(":", G40)-1))</f>
@@ -3551,7 +3624,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="H41">
         <f>E41*VALUE(LEFT(G41, FIND(":", G41)-1))</f>
@@ -3577,10 +3650,10 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H42">
         <f>E42*VALUE(LEFT(G42, FIND(":", G42)-1))</f>
@@ -3606,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="H43">
         <f>E43*VALUE(LEFT(G43, FIND(":", G43)-1))</f>
@@ -3632,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H44">
         <f>E44*VALUE(LEFT(G44, FIND(":", G44)-1))</f>
@@ -3658,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H45">
         <f>E45*VALUE(LEFT(G45, FIND(":", G45)-1))</f>
@@ -3684,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H46">
         <f>E46*VALUE(LEFT(G46, FIND(":", G46)-1))</f>
@@ -3712,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="H47">
         <f>E47*VALUE(LEFT(G47, FIND(":", G47)-1))</f>
@@ -3738,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H48">
         <f>E48*VALUE(LEFT(G48, FIND(":", G48)-1))</f>
@@ -3764,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H49">
         <f>E49*VALUE(LEFT(G49, FIND(":", G49)-1))</f>
@@ -3790,7 +3863,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="H50">
         <f>E50*VALUE(LEFT(G50, FIND(":", G50)-1))</f>
@@ -3816,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H51">
         <f>E51*VALUE(LEFT(G51, FIND(":", G51)-1))</f>
@@ -3842,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H52">
         <f>E52*VALUE(LEFT(G52, FIND(":", G52)-1))</f>
@@ -3870,7 +3943,7 @@
         <v>1</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="H53">
         <f>E53*VALUE(LEFT(G53, FIND(":", G53)-1))</f>
@@ -3896,7 +3969,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="H54">
         <f>E54*VALUE(LEFT(G54, FIND(":", G54)-1))</f>
@@ -3922,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H55">
         <f>E55*VALUE(LEFT(G55, FIND(":", G55)-1))</f>
@@ -3948,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H56">
         <f>E56*VALUE(LEFT(G56, FIND(":", G56)-1))</f>
@@ -3974,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H57">
         <f>E57*VALUE(LEFT(G57, FIND(":", G57)-1))</f>
@@ -4000,10 +4073,10 @@
         <v>1</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H58">
         <f>E58*VALUE(LEFT(G58, FIND(":", G58)-1))</f>
@@ -4031,7 +4104,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H59">
         <f>E59*VALUE(LEFT(G59, FIND(":", G59)-1))</f>
@@ -4057,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="H60">
         <f>E60*VALUE(LEFT(G60, FIND(":", G60)-1))</f>
@@ -4083,7 +4156,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="H61">
         <f>E61*VALUE(LEFT(G61, FIND(":", G61)-1))</f>
@@ -4109,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H62">
         <f>E62*VALUE(LEFT(G62, FIND(":", G62)-1))</f>
@@ -4135,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H63">
         <f>E63*VALUE(LEFT(G63, FIND(":", G63)-1))</f>
@@ -4161,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H64">
         <f>E64*VALUE(LEFT(G64, FIND(":", G64)-1))</f>
@@ -4189,10 +4262,10 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H65">
         <f>E65*VALUE(LEFT(G65, FIND(":", G65)-1))</f>
@@ -4218,10 +4291,10 @@
         <v>1</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="H66">
         <f>E66*VALUE(LEFT(G66, FIND(":", G66)-1))</f>
@@ -4247,10 +4320,10 @@
         <v>1</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H67">
         <f>E67*VALUE(LEFT(G67, FIND(":", G67)-1))</f>
@@ -4276,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="H68">
         <f>E68*VALUE(LEFT(G68, FIND(":", G68)-1))</f>
@@ -4305,10 +4378,10 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="H69">
         <f>E69*VALUE(LEFT(G69, FIND(":", G69)-1))</f>
@@ -4334,10 +4407,10 @@
         <v>1</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H70">
         <f>E70*VALUE(LEFT(G70, FIND(":", G70)-1))</f>
@@ -4363,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H71">
         <f>E71*VALUE(LEFT(G71, FIND(":", G71)-1))</f>
@@ -4391,10 +4464,10 @@
         <v>1</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H72">
         <f>E72*VALUE(LEFT(G72, FIND(":", G72)-1))</f>
@@ -4420,10 +4493,10 @@
         <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H73">
         <f>E73*VALUE(LEFT(G73, FIND(":", G73)-1))</f>
@@ -4449,7 +4522,7 @@
         <v>1</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="H74">
         <f>E74*VALUE(LEFT(G74, FIND(":", G74)-1))</f>
@@ -4475,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H75">
         <f>E75*VALUE(LEFT(G75, FIND(":", G75)-1))</f>
@@ -4501,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H76">
         <f>E76*VALUE(LEFT(G76, FIND(":", G76)-1))</f>
@@ -4527,10 +4600,10 @@
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H77">
         <f>E77*VALUE(LEFT(G77, FIND(":", G77)-1))</f>
@@ -4556,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H78">
         <f>E78*VALUE(LEFT(G78, FIND(":", G78)-1))</f>
@@ -4584,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H79">
         <f>E79*VALUE(LEFT(G79, FIND(":", G79)-1))</f>
@@ -4610,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H80">
         <f>E80*VALUE(LEFT(G80, FIND(":", G80)-1))</f>
@@ -4636,7 +4709,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H81">
         <f>E81*VALUE(LEFT(G81, FIND(":", G81)-1))</f>
@@ -4662,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="H82">
         <f>E82*VALUE(LEFT(G82, FIND(":", G82)-1))</f>
@@ -4688,7 +4761,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H83">
         <f>E83*VALUE(LEFT(G83, FIND(":", G83)-1))</f>
@@ -4714,10 +4787,10 @@
         <v>1</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H84">
         <f>E84*VALUE(LEFT(G84, FIND(":", G84)-1))</f>
@@ -4743,10 +4816,10 @@
         <v>1</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H85">
         <f>E85*VALUE(LEFT(G85, FIND(":", G85)-1))</f>
@@ -4772,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H86">
         <f>E86*VALUE(LEFT(G86, FIND(":", G86)-1))</f>
@@ -4798,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="H87">
         <f>E87*VALUE(LEFT(G87, FIND(":", G87)-1))</f>
@@ -4826,7 +4899,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H88">
         <f>E88*VALUE(LEFT(G88, FIND(":", G88)-1))</f>
@@ -4852,10 +4925,10 @@
         <v>1</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H89">
         <f>E89*VALUE(LEFT(G89, FIND(":", G89)-1))</f>
@@ -4881,10 +4954,10 @@
         <v>1</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H90">
         <f>E90*VALUE(LEFT(G90, FIND(":", G90)-1))</f>
@@ -4910,7 +4983,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H91">
         <f>E91*VALUE(LEFT(G91, FIND(":", G91)-1))</f>
@@ -4936,7 +5009,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="H92">
         <f>E92*VALUE(LEFT(G92, FIND(":", G92)-1))</f>
@@ -4962,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H93">
         <f>E93*VALUE(LEFT(G93, FIND(":", G93)-1))</f>
@@ -4988,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H94">
         <f>E94*VALUE(LEFT(G94, FIND(":", G94)-1))</f>
@@ -5018,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H95">
         <f>E95*VALUE(LEFT(G95, FIND(":", G95)-1))</f>
@@ -5044,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H96">
         <f>E96*VALUE(LEFT(G96, FIND(":", G96)-1))</f>
@@ -5070,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H97">
         <f>E97*VALUE(LEFT(G97, FIND(":", G97)-1))</f>
@@ -5096,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H98">
         <f>E98*VALUE(LEFT(G98, FIND(":", G98)-1))</f>
@@ -5122,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="H99">
         <f>E99*VALUE(LEFT(G99, FIND(":", G99)-1))</f>
@@ -5148,7 +5221,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H100">
         <f>E100*VALUE(LEFT(G100, FIND(":", G100)-1))</f>
@@ -5176,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="H101">
         <f>E101*VALUE(LEFT(G101, FIND(":", G101)-1))</f>
@@ -5202,7 +5275,7 @@
         <v>1</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="H102">
         <f>E102*VALUE(LEFT(G102, FIND(":", G102)-1))</f>
@@ -5228,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H103">
         <f>E103*VALUE(LEFT(G103, FIND(":", G103)-1))</f>
@@ -5254,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H104">
         <f>E104*VALUE(LEFT(G104, FIND(":", G104)-1))</f>
@@ -5280,7 +5353,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H105">
         <f>E105*VALUE(LEFT(G105, FIND(":", G105)-1))</f>
@@ -5306,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H106">
         <f>E106*VALUE(LEFT(G106, FIND(":", G106)-1))</f>
@@ -5334,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H107">
         <f>E107*VALUE(LEFT(G107, FIND(":", G107)-1))</f>
@@ -5360,10 +5433,10 @@
         <v>1</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H108">
         <f>E108*VALUE(LEFT(G108, FIND(":", G108)-1))</f>
@@ -5389,7 +5462,7 @@
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H109">
         <f>E109*VALUE(LEFT(G109, FIND(":", G109)-1))</f>
@@ -5415,10 +5488,10 @@
         <v>1</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="H110">
         <f>E110*VALUE(LEFT(G110, FIND(":", G110)-1))</f>
@@ -5444,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="H111">
         <f>E111*VALUE(LEFT(G111, FIND(":", G111)-1))</f>
@@ -5470,10 +5543,10 @@
         <v>1</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H112">
         <f>E112*VALUE(LEFT(G112, FIND(":", G112)-1))</f>
@@ -5498,10 +5571,13 @@
         <v>282</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="H113">
         <f>E113*VALUE(LEFT(G113, FIND(":", G113)-1))</f>
@@ -5524,10 +5600,13 @@
         <v>283</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="H114">
         <f>E114*VALUE(LEFT(G114, FIND(":", G114)-1))</f>
@@ -5550,10 +5629,13 @@
         <v>284</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="H115">
         <f>E115*VALUE(LEFT(G115, FIND(":", G115)-1))</f>
@@ -5576,10 +5658,13 @@
         <v>285</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="H116">
         <f>E116*VALUE(LEFT(G116, FIND(":", G116)-1))</f>
@@ -5605,10 +5690,10 @@
         <v>1</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H117">
         <f>E117*VALUE(LEFT(G117, FIND(":", G117)-1))</f>
@@ -5634,7 +5719,7 @@
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="H118">
         <f>E118*VALUE(LEFT(G118, FIND(":", G118)-1))</f>
@@ -5657,10 +5742,13 @@
         <v>288</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="H119">
         <f>E119*VALUE(LEFT(G119, FIND(":", G119)-1))</f>
@@ -5688,10 +5776,10 @@
         <v>1</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H120">
         <f>E120*VALUE(LEFT(G120, FIND(":", G120)-1))</f>
@@ -5717,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H121">
         <f>E121*VALUE(LEFT(G121, FIND(":", G121)-1))</f>
@@ -5743,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H122">
         <f>E122*VALUE(LEFT(G122, FIND(":", G122)-1))</f>
@@ -5769,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H123">
         <f>E123*VALUE(LEFT(G123, FIND(":", G123)-1))</f>
@@ -5795,7 +5883,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H124">
         <f>E124*VALUE(LEFT(G124, FIND(":", G124)-1))</f>
@@ -5821,7 +5909,7 @@
         <v>1</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H125">
         <f>E125*VALUE(LEFT(G125, FIND(":", G125)-1))</f>
@@ -5851,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H126">
         <f>E126*VALUE(LEFT(G126, FIND(":", G126)-1))</f>
@@ -5877,7 +5965,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H127">
         <f>E127*VALUE(LEFT(G127, FIND(":", G127)-1))</f>
@@ -5903,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H128">
         <f>E128*VALUE(LEFT(G128, FIND(":", G128)-1))</f>
@@ -5929,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="H129">
         <f>E129*VALUE(LEFT(G129, FIND(":", G129)-1))</f>
@@ -5955,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H130">
         <f>E130*VALUE(LEFT(G130, FIND(":", G130)-1))</f>
@@ -5998,13 +6086,13 @@
   </mergeCells>
   <dataValidations count="129">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: 0 items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5">
       <formula1>"0: None"</formula1>
@@ -6331,16 +6419,16 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G113">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G114">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G115">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G116">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G117">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
@@ -6349,7 +6437,7 @@
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G119">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G120">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="377">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -937,6 +937,18 @@
 * Plot scores over time to track maturity progress for priority scopes
 * Complete analysis on what contributed to or hindered progress across scopes or different areas of the assessment
 10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>1. Invite subject matter experts (SMEs) and leadership to determine which gaps to address first
+2. Determine owners for addressing each of the prioritized gaps
+3. Owners will work with relevant teams to scope out how to meet the target score for each gap
+4. Work is then scheduled in a roadmap with deadlines that can be tracked at the leadership level</t>
+  </si>
+  <si>
+    <t>* Schedule a cadence to report progress outcomes to key stakeholders.
+* Create reporting to show progress on key outcomes across all maturity initiatives.
+* After successful outcomes are achieved, move on to the next prioritized item in the roadmap.
+* Periodically reevaluate the gap analysis and priority list based on lessons learned and new business goals.</t>
   </si>
   <si>
     <t>* Define process for reviewing asking for credits from CSPs
@@ -1145,6 +1157,9 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 4, 'Condition': '1 item completed'}, {'Score': 7, 'Condition': '2 items completed'}, {'Score': 10, 'Condition': '3 items completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1, and 2 completed'}, {'Score': 8, 'Condition': 'items 1, 2, and 3 completed'}, {'Score': 10, 'Condition': 'items 1, 2, 3, and 4 completed'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': None}]</t>
   </si>
   <si>
@@ -1187,7 +1202,7 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 7, 'Condition': '4 items completed'}, {'Score': 9, 'Condition': '5 items completed'}, {'Score': 10, 'Condition': '6 items completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No alerting in workflow tools'}, {'Score': 1, 'Condition': 'Alerting in at least one tool'}, {'Score': 3, 'Condition': 'Alerting in some tooling [20%]'}, {'Score': 6, 'Condition': 'Alerting in most tooling [60%]'}, {'Score': 10, 'Condition': 'Alerting in all workflow tools [100%]'}]</t>
+    <t>[{'Score': 0, 'Condition': 'No alerting to any owners'}, {'Score': 1, 'Condition': 'Alerting in at least one owner'}, {'Score': 3, 'Condition': 'Alerting to some owners [&gt;20%]'}, {'Score': 6, 'Condition': 'Alerting to most owners [&gt;60%]'}, {'Score': 10, 'Condition': 'Alerting to all owners [100%]'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 3, 'Condition': '2 items completed'}, {'Score': 4, 'Condition': '3 items completed'}, {'Score': 5, 'Condition': '4 items completed'}, {'Score': 7, 'Condition': '5 items completed'}, {'Score': 8, 'Condition': '6 items completed'}, {'Score': 9, 'Condition': '7 items completed'}, {'Score': 10, 'Condition': '8 items completed'}]</t>
@@ -1199,6 +1214,9 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 items completed'}, {'Score': 3, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 6, 'Condition': '4 items completed'}, {'Score': 8, 'Condition': '5 items completed'}, {'Score': 9, 'Condition': '6 items completed'}, {'Score': 10, 'Condition': '7 items completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No alerting in workflow tools'}, {'Score': 1, 'Condition': 'Alerting in at least one tool'}, {'Score': 3, 'Condition': 'Alerting in some tooling [&gt;20%]'}, {'Score': 6, 'Condition': 'Alerting in most tooling [&gt;60%]'}, {'Score': 10, 'Condition': 'Alerting in all workflow tools [100%]'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'No review of trends'}, {'Score': 3, 'Condition': 'Manual review of trends'}, {'Score': 6, 'Condition': 'Automated trend detection'}, {'Score': 10, 'Condition': 'Manual review and automated trend detection'}]</t>
   </si>
   <si>
@@ -1211,7 +1229,7 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': 'item 1 completed'}, {'Score': 10, 'Condition': 'item 2 completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 10, 'Condition': 'set goal thresholds for kpis and unit costs'}]</t>
+    <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 10, 'Condition': 'communicates wins in KPI thresholds and unit costs'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'Not monitored'}, {'Score': 2, 'Condition': 'Reported'}, {'Score': 5, 'Condition': 'Manual remediation'}, {'Score': 10, 'Condition': 'Automated remediation'}]</t>
@@ -1244,10 +1262,13 @@
     <t>0: No teardown/shutdown policy</t>
   </si>
   <si>
+    <t>0: No alerting to any owners</t>
+  </si>
+  <si>
+    <t>0: Never</t>
+  </si>
+  <si>
     <t>0: No alerting in workflow tools</t>
-  </si>
-  <si>
-    <t>0: Never</t>
   </si>
   <si>
     <t>0: No review of trends</t>
@@ -2579,7 +2600,7 @@
         <v>300</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H2">
         <f>E2*VALUE(LEFT(G2, FIND(":", G2)-1))</f>
@@ -2608,7 +2629,7 @@
         <v>301</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H3">
         <f>E3*VALUE(LEFT(G3, FIND(":", G3)-1))</f>
@@ -2637,7 +2658,7 @@
         <v>302</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H4">
         <f>E4*VALUE(LEFT(G4, FIND(":", G4)-1))</f>
@@ -2660,10 +2681,13 @@
         <v>174</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H5">
         <f>E5*VALUE(LEFT(G5, FIND(":", G5)-1))</f>
@@ -2688,8 +2712,11 @@
       <c r="E6">
         <v>0</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>304</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H6">
         <f>E6*VALUE(LEFT(G6, FIND(":", G6)-1))</f>
@@ -2717,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H7">
         <f>E7*VALUE(LEFT(G7, FIND(":", G7)-1))</f>
@@ -2743,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H8">
         <f>E8*VALUE(LEFT(G8, FIND(":", G8)-1))</f>
@@ -2769,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H9">
         <f>E9*VALUE(LEFT(G9, FIND(":", G9)-1))</f>
@@ -2795,10 +2822,10 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H10">
         <f>E10*VALUE(LEFT(G10, FIND(":", G10)-1))</f>
@@ -2824,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H11">
         <f>E11*VALUE(LEFT(G11, FIND(":", G11)-1))</f>
@@ -2852,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H12">
         <f>E12*VALUE(LEFT(G12, FIND(":", G12)-1))</f>
@@ -2878,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H13">
         <f>E13*VALUE(LEFT(G13, FIND(":", G13)-1))</f>
@@ -2904,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H14">
         <f>E14*VALUE(LEFT(G14, FIND(":", G14)-1))</f>
@@ -2930,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H15">
         <f>E15*VALUE(LEFT(G15, FIND(":", G15)-1))</f>
@@ -2956,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H16">
         <f>E16*VALUE(LEFT(G16, FIND(":", G16)-1))</f>
@@ -2982,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H17">
         <f>E17*VALUE(LEFT(G17, FIND(":", G17)-1))</f>
@@ -3010,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H18">
         <f>E18*VALUE(LEFT(G18, FIND(":", G18)-1))</f>
@@ -3036,7 +3063,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H19">
         <f>E19*VALUE(LEFT(G19, FIND(":", G19)-1))</f>
@@ -3062,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H20">
         <f>E20*VALUE(LEFT(G20, FIND(":", G20)-1))</f>
@@ -3088,10 +3115,10 @@
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H21">
         <f>E21*VALUE(LEFT(G21, FIND(":", G21)-1))</f>
@@ -3117,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H22">
         <f>E22*VALUE(LEFT(G22, FIND(":", G22)-1))</f>
@@ -3145,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H23">
         <f>E23*VALUE(LEFT(G23, FIND(":", G23)-1))</f>
@@ -3171,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H24">
         <f>E24*VALUE(LEFT(G24, FIND(":", G24)-1))</f>
@@ -3197,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H25">
         <f>E25*VALUE(LEFT(G25, FIND(":", G25)-1))</f>
@@ -3223,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H26">
         <f>E26*VALUE(LEFT(G26, FIND(":", G26)-1))</f>
@@ -3249,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H27">
         <f>E27*VALUE(LEFT(G27, FIND(":", G27)-1))</f>
@@ -3275,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H28">
         <f>E28*VALUE(LEFT(G28, FIND(":", G28)-1))</f>
@@ -3303,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H29">
         <f>E29*VALUE(LEFT(G29, FIND(":", G29)-1))</f>
@@ -3329,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H30">
         <f>E30*VALUE(LEFT(G30, FIND(":", G30)-1))</f>
@@ -3355,7 +3382,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H31">
         <f>E31*VALUE(LEFT(G31, FIND(":", G31)-1))</f>
@@ -3381,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H32">
         <f>E32*VALUE(LEFT(G32, FIND(":", G32)-1))</f>
@@ -3407,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H33">
         <f>E33*VALUE(LEFT(G33, FIND(":", G33)-1))</f>
@@ -3433,7 +3460,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H34">
         <f>E34*VALUE(LEFT(G34, FIND(":", G34)-1))</f>
@@ -3461,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H35">
         <f>E35*VALUE(LEFT(G35, FIND(":", G35)-1))</f>
@@ -3487,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H36">
         <f>E36*VALUE(LEFT(G36, FIND(":", G36)-1))</f>
@@ -3513,10 +3540,10 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H37">
         <f>E37*VALUE(LEFT(G37, FIND(":", G37)-1))</f>
@@ -3542,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H38">
         <f>E38*VALUE(LEFT(G38, FIND(":", G38)-1))</f>
@@ -3568,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H39">
         <f>E39*VALUE(LEFT(G39, FIND(":", G39)-1))</f>
@@ -3594,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H40">
         <f>E40*VALUE(LEFT(G40, FIND(":", G40)-1))</f>
@@ -3624,7 +3651,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H41">
         <f>E41*VALUE(LEFT(G41, FIND(":", G41)-1))</f>
@@ -3650,10 +3677,10 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H42">
         <f>E42*VALUE(LEFT(G42, FIND(":", G42)-1))</f>
@@ -3679,7 +3706,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H43">
         <f>E43*VALUE(LEFT(G43, FIND(":", G43)-1))</f>
@@ -3705,7 +3732,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H44">
         <f>E44*VALUE(LEFT(G44, FIND(":", G44)-1))</f>
@@ -3731,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H45">
         <f>E45*VALUE(LEFT(G45, FIND(":", G45)-1))</f>
@@ -3757,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H46">
         <f>E46*VALUE(LEFT(G46, FIND(":", G46)-1))</f>
@@ -3785,7 +3812,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H47">
         <f>E47*VALUE(LEFT(G47, FIND(":", G47)-1))</f>
@@ -3811,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H48">
         <f>E48*VALUE(LEFT(G48, FIND(":", G48)-1))</f>
@@ -3837,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H49">
         <f>E49*VALUE(LEFT(G49, FIND(":", G49)-1))</f>
@@ -3863,7 +3890,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H50">
         <f>E50*VALUE(LEFT(G50, FIND(":", G50)-1))</f>
@@ -3889,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H51">
         <f>E51*VALUE(LEFT(G51, FIND(":", G51)-1))</f>
@@ -3915,7 +3942,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H52">
         <f>E52*VALUE(LEFT(G52, FIND(":", G52)-1))</f>
@@ -3943,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H53">
         <f>E53*VALUE(LEFT(G53, FIND(":", G53)-1))</f>
@@ -3969,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H54">
         <f>E54*VALUE(LEFT(G54, FIND(":", G54)-1))</f>
@@ -3995,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H55">
         <f>E55*VALUE(LEFT(G55, FIND(":", G55)-1))</f>
@@ -4021,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H56">
         <f>E56*VALUE(LEFT(G56, FIND(":", G56)-1))</f>
@@ -4047,7 +4074,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H57">
         <f>E57*VALUE(LEFT(G57, FIND(":", G57)-1))</f>
@@ -4073,10 +4100,10 @@
         <v>1</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H58">
         <f>E58*VALUE(LEFT(G58, FIND(":", G58)-1))</f>
@@ -4104,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H59">
         <f>E59*VALUE(LEFT(G59, FIND(":", G59)-1))</f>
@@ -4130,7 +4157,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H60">
         <f>E60*VALUE(LEFT(G60, FIND(":", G60)-1))</f>
@@ -4156,7 +4183,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H61">
         <f>E61*VALUE(LEFT(G61, FIND(":", G61)-1))</f>
@@ -4182,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H62">
         <f>E62*VALUE(LEFT(G62, FIND(":", G62)-1))</f>
@@ -4208,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H63">
         <f>E63*VALUE(LEFT(G63, FIND(":", G63)-1))</f>
@@ -4234,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H64">
         <f>E64*VALUE(LEFT(G64, FIND(":", G64)-1))</f>
@@ -4262,10 +4289,10 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H65">
         <f>E65*VALUE(LEFT(G65, FIND(":", G65)-1))</f>
@@ -4291,10 +4318,10 @@
         <v>1</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H66">
         <f>E66*VALUE(LEFT(G66, FIND(":", G66)-1))</f>
@@ -4320,10 +4347,10 @@
         <v>1</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H67">
         <f>E67*VALUE(LEFT(G67, FIND(":", G67)-1))</f>
@@ -4349,10 +4376,10 @@
         <v>1</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H68">
         <f>E68*VALUE(LEFT(G68, FIND(":", G68)-1))</f>
@@ -4378,10 +4405,10 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H69">
         <f>E69*VALUE(LEFT(G69, FIND(":", G69)-1))</f>
@@ -4407,10 +4434,10 @@
         <v>1</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H70">
         <f>E70*VALUE(LEFT(G70, FIND(":", G70)-1))</f>
@@ -4436,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H71">
         <f>E71*VALUE(LEFT(G71, FIND(":", G71)-1))</f>
@@ -4464,10 +4491,10 @@
         <v>1</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H72">
         <f>E72*VALUE(LEFT(G72, FIND(":", G72)-1))</f>
@@ -4493,10 +4520,10 @@
         <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H73">
         <f>E73*VALUE(LEFT(G73, FIND(":", G73)-1))</f>
@@ -4522,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="H74">
         <f>E74*VALUE(LEFT(G74, FIND(":", G74)-1))</f>
@@ -4548,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H75">
         <f>E75*VALUE(LEFT(G75, FIND(":", G75)-1))</f>
@@ -4574,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H76">
         <f>E76*VALUE(LEFT(G76, FIND(":", G76)-1))</f>
@@ -4600,10 +4627,10 @@
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H77">
         <f>E77*VALUE(LEFT(G77, FIND(":", G77)-1))</f>
@@ -4629,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H78">
         <f>E78*VALUE(LEFT(G78, FIND(":", G78)-1))</f>
@@ -4657,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H79">
         <f>E79*VALUE(LEFT(G79, FIND(":", G79)-1))</f>
@@ -4683,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H80">
         <f>E80*VALUE(LEFT(G80, FIND(":", G80)-1))</f>
@@ -4709,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H81">
         <f>E81*VALUE(LEFT(G81, FIND(":", G81)-1))</f>
@@ -4735,7 +4762,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H82">
         <f>E82*VALUE(LEFT(G82, FIND(":", G82)-1))</f>
@@ -4761,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H83">
         <f>E83*VALUE(LEFT(G83, FIND(":", G83)-1))</f>
@@ -4787,10 +4814,10 @@
         <v>1</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H84">
         <f>E84*VALUE(LEFT(G84, FIND(":", G84)-1))</f>
@@ -4816,10 +4843,10 @@
         <v>1</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H85">
         <f>E85*VALUE(LEFT(G85, FIND(":", G85)-1))</f>
@@ -4845,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H86">
         <f>E86*VALUE(LEFT(G86, FIND(":", G86)-1))</f>
@@ -4871,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H87">
         <f>E87*VALUE(LEFT(G87, FIND(":", G87)-1))</f>
@@ -4899,7 +4926,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H88">
         <f>E88*VALUE(LEFT(G88, FIND(":", G88)-1))</f>
@@ -4925,10 +4952,10 @@
         <v>1</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H89">
         <f>E89*VALUE(LEFT(G89, FIND(":", G89)-1))</f>
@@ -4954,10 +4981,10 @@
         <v>1</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H90">
         <f>E90*VALUE(LEFT(G90, FIND(":", G90)-1))</f>
@@ -4983,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H91">
         <f>E91*VALUE(LEFT(G91, FIND(":", G91)-1))</f>
@@ -5009,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="H92">
         <f>E92*VALUE(LEFT(G92, FIND(":", G92)-1))</f>
@@ -5035,7 +5062,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H93">
         <f>E93*VALUE(LEFT(G93, FIND(":", G93)-1))</f>
@@ -5061,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H94">
         <f>E94*VALUE(LEFT(G94, FIND(":", G94)-1))</f>
@@ -5091,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H95">
         <f>E95*VALUE(LEFT(G95, FIND(":", G95)-1))</f>
@@ -5117,7 +5144,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H96">
         <f>E96*VALUE(LEFT(G96, FIND(":", G96)-1))</f>
@@ -5143,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H97">
         <f>E97*VALUE(LEFT(G97, FIND(":", G97)-1))</f>
@@ -5169,7 +5196,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H98">
         <f>E98*VALUE(LEFT(G98, FIND(":", G98)-1))</f>
@@ -5195,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H99">
         <f>E99*VALUE(LEFT(G99, FIND(":", G99)-1))</f>
@@ -5221,7 +5248,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H100">
         <f>E100*VALUE(LEFT(G100, FIND(":", G100)-1))</f>
@@ -5249,7 +5276,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H101">
         <f>E101*VALUE(LEFT(G101, FIND(":", G101)-1))</f>
@@ -5275,7 +5302,7 @@
         <v>1</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H102">
         <f>E102*VALUE(LEFT(G102, FIND(":", G102)-1))</f>
@@ -5301,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H103">
         <f>E103*VALUE(LEFT(G103, FIND(":", G103)-1))</f>
@@ -5327,7 +5354,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H104">
         <f>E104*VALUE(LEFT(G104, FIND(":", G104)-1))</f>
@@ -5353,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H105">
         <f>E105*VALUE(LEFT(G105, FIND(":", G105)-1))</f>
@@ -5379,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H106">
         <f>E106*VALUE(LEFT(G106, FIND(":", G106)-1))</f>
@@ -5407,7 +5434,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H107">
         <f>E107*VALUE(LEFT(G107, FIND(":", G107)-1))</f>
@@ -5433,10 +5460,10 @@
         <v>1</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H108">
         <f>E108*VALUE(LEFT(G108, FIND(":", G108)-1))</f>
@@ -5462,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H109">
         <f>E109*VALUE(LEFT(G109, FIND(":", G109)-1))</f>
@@ -5488,10 +5515,10 @@
         <v>1</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H110">
         <f>E110*VALUE(LEFT(G110, FIND(":", G110)-1))</f>
@@ -5517,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H111">
         <f>E111*VALUE(LEFT(G111, FIND(":", G111)-1))</f>
@@ -5543,10 +5570,10 @@
         <v>1</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H112">
         <f>E112*VALUE(LEFT(G112, FIND(":", G112)-1))</f>
@@ -5574,10 +5601,10 @@
         <v>1</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H113">
         <f>E113*VALUE(LEFT(G113, FIND(":", G113)-1))</f>
@@ -5603,10 +5630,10 @@
         <v>1</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H114">
         <f>E114*VALUE(LEFT(G114, FIND(":", G114)-1))</f>
@@ -5632,10 +5659,10 @@
         <v>1</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H115">
         <f>E115*VALUE(LEFT(G115, FIND(":", G115)-1))</f>
@@ -5661,10 +5688,10 @@
         <v>1</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H116">
         <f>E116*VALUE(LEFT(G116, FIND(":", G116)-1))</f>
@@ -5690,10 +5717,10 @@
         <v>1</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H117">
         <f>E117*VALUE(LEFT(G117, FIND(":", G117)-1))</f>
@@ -5719,7 +5746,7 @@
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H118">
         <f>E118*VALUE(LEFT(G118, FIND(":", G118)-1))</f>
@@ -5745,10 +5772,10 @@
         <v>1</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H119">
         <f>E119*VALUE(LEFT(G119, FIND(":", G119)-1))</f>
@@ -5776,10 +5803,10 @@
         <v>1</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H120">
         <f>E120*VALUE(LEFT(G120, FIND(":", G120)-1))</f>
@@ -5805,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H121">
         <f>E121*VALUE(LEFT(G121, FIND(":", G121)-1))</f>
@@ -5831,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H122">
         <f>E122*VALUE(LEFT(G122, FIND(":", G122)-1))</f>
@@ -5857,7 +5884,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H123">
         <f>E123*VALUE(LEFT(G123, FIND(":", G123)-1))</f>
@@ -5883,7 +5910,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H124">
         <f>E124*VALUE(LEFT(G124, FIND(":", G124)-1))</f>
@@ -5909,7 +5936,7 @@
         <v>1</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H125">
         <f>E125*VALUE(LEFT(G125, FIND(":", G125)-1))</f>
@@ -5939,7 +5966,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H126">
         <f>E126*VALUE(LEFT(G126, FIND(":", G126)-1))</f>
@@ -5965,7 +5992,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H127">
         <f>E127*VALUE(LEFT(G127, FIND(":", G127)-1))</f>
@@ -5991,7 +6018,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H128">
         <f>E128*VALUE(LEFT(G128, FIND(":", G128)-1))</f>
@@ -6017,7 +6044,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="H129">
         <f>E129*VALUE(LEFT(G129, FIND(":", G129)-1))</f>
@@ -6043,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H130">
         <f>E130*VALUE(LEFT(G130, FIND(":", G130)-1))</f>
@@ -6095,10 +6122,10 @@
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,3: item 1 completed,5: items 1, and 2 completed,8: items 1, 2, and 3 completed,10: items 1, 2, 3, and 4 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7">
       <formula1>"0: None"</formula1>
@@ -6302,7 +6329,7 @@
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G74">
-      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [20%],6: Alerting in most tooling [60%],10: Alerting in all workflow tools [100%]"</formula1>
+      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G75">
       <formula1>"0: None"</formula1>
@@ -6356,7 +6383,7 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G92">
-      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [20%],6: Alerting in most tooling [60%],10: Alerting in all workflow tools [100%]"</formula1>
+      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G93">
       <formula1>"0: None"</formula1>
@@ -6455,7 +6482,7 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G125">
-      <formula1>"0: None,10: set goal thresholds for kpis and unit costs"</formula1>
+      <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G126">
       <formula1>"0: None"</formula1>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="382">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -118,6 +118,9 @@
     <t>serial number</t>
   </si>
   <si>
+    <t>version</t>
+  </si>
+  <si>
     <t>weights</t>
   </si>
   <si>
@@ -917,6 +920,18 @@
   </si>
   <si>
     <t>106</t>
+  </si>
+  <si>
+    <t>0.8.0</t>
+  </si>
+  <si>
+    <t>0.7.0</t>
+  </si>
+  <si>
+    <t>1.7.0</t>
+  </si>
+  <si>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>* Select which teams or groups are in scope for the planned assessments
@@ -2533,30 +2548,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="40.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.42578125" hidden="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.28515625" hidden="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.42578125" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.28515625" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>32</v>
@@ -2579,8 +2595,11 @@
       <c r="J1" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -2588,1053 +2607,1146 @@
         <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E2">
+        <v>172</v>
+      </c>
+      <c r="E2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="H2">
         <f>E2*VALUE(LEFT(G2, FIND(":", G2)-1))</f>
         <v>0</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E3">
+        <v>173</v>
+      </c>
+      <c r="E3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H3">
         <f>E3*VALUE(LEFT(G3, FIND(":", G3)-1))</f>
         <v>0</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>7</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E4">
+        <v>174</v>
+      </c>
+      <c r="E4" t="s">
+        <v>301</v>
+      </c>
+      <c r="F4" s="1">
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H4">
         <f>E4*VALUE(LEFT(G4, FIND(":", G4)-1))</f>
         <v>0</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E5">
+        <v>175</v>
+      </c>
+      <c r="E5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H5">
         <f>E5*VALUE(LEFT(G5, FIND(":", G5)-1))</f>
         <v>0</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>7</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>304</v>
+        <v>176</v>
+      </c>
+      <c r="E6" t="s">
+        <v>302</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H6">
         <f>E6*VALUE(LEFT(G6, FIND(":", G6)-1))</f>
         <v>0</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>7</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E7">
+        <v>177</v>
+      </c>
+      <c r="E7" t="s">
+        <v>302</v>
+      </c>
+      <c r="F7" s="1">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H7">
         <f>E7*VALUE(LEFT(G7, FIND(":", G7)-1))</f>
         <v>0</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>7</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E8">
+        <v>178</v>
+      </c>
+      <c r="E8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H8">
         <f>E8*VALUE(LEFT(G8, FIND(":", G8)-1))</f>
         <v>0</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>7</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E9">
+        <v>179</v>
+      </c>
+      <c r="E9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H9">
         <f>E9*VALUE(LEFT(G9, FIND(":", G9)-1))</f>
         <v>0</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>7</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E10">
+        <v>180</v>
+      </c>
+      <c r="E10" t="s">
+        <v>303</v>
+      </c>
+      <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H10">
         <f>E10*VALUE(LEFT(G10, FIND(":", G10)-1))</f>
         <v>0</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>7</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E11">
+        <v>181</v>
+      </c>
+      <c r="E11" t="s">
+        <v>302</v>
+      </c>
+      <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H11">
         <f>E11*VALUE(LEFT(G11, FIND(":", G11)-1))</f>
         <v>0</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>7</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E12">
+        <v>182</v>
+      </c>
+      <c r="E12" t="s">
+        <v>303</v>
+      </c>
+      <c r="F12" s="1">
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="H12">
         <f>E12*VALUE(LEFT(G12, FIND(":", G12)-1))</f>
         <v>0</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>7</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E13">
+        <v>183</v>
+      </c>
+      <c r="E13" t="s">
+        <v>302</v>
+      </c>
+      <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H13">
         <f>E13*VALUE(LEFT(G13, FIND(":", G13)-1))</f>
         <v>0</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>7</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:11">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E14">
+        <v>184</v>
+      </c>
+      <c r="E14" t="s">
+        <v>302</v>
+      </c>
+      <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H14">
         <f>E14*VALUE(LEFT(G14, FIND(":", G14)-1))</f>
         <v>0</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>7</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E15">
+        <v>185</v>
+      </c>
+      <c r="E15" t="s">
+        <v>302</v>
+      </c>
+      <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H15">
         <f>E15*VALUE(LEFT(G15, FIND(":", G15)-1))</f>
         <v>0</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>7</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E16">
+        <v>186</v>
+      </c>
+      <c r="E16" t="s">
+        <v>302</v>
+      </c>
+      <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H16">
         <f>E16*VALUE(LEFT(G16, FIND(":", G16)-1))</f>
         <v>0</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>7</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E17">
+        <v>187</v>
+      </c>
+      <c r="E17" t="s">
+        <v>302</v>
+      </c>
+      <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H17">
         <f>E17*VALUE(LEFT(G17, FIND(":", G17)-1))</f>
         <v>0</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>7</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E18">
+        <v>188</v>
+      </c>
+      <c r="E18" t="s">
+        <v>302</v>
+      </c>
+      <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H18">
         <f>E18*VALUE(LEFT(G18, FIND(":", G18)-1))</f>
         <v>0</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>7</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:11">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E19">
+        <v>189</v>
+      </c>
+      <c r="E19" t="s">
+        <v>303</v>
+      </c>
+      <c r="F19" s="1">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H19">
         <f>E19*VALUE(LEFT(G19, FIND(":", G19)-1))</f>
         <v>0</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>7</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:11">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E20">
+        <v>190</v>
+      </c>
+      <c r="E20" t="s">
+        <v>302</v>
+      </c>
+      <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H20">
         <f>E20*VALUE(LEFT(G20, FIND(":", G20)-1))</f>
         <v>0</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>7</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:11">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E21">
+        <v>191</v>
+      </c>
+      <c r="E21" t="s">
+        <v>303</v>
+      </c>
+      <c r="F21" s="1">
         <v>1</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="G21" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H21">
         <f>E21*VALUE(LEFT(G21, FIND(":", G21)-1))</f>
         <v>0</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>7</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E22">
+        <v>192</v>
+      </c>
+      <c r="E22" t="s">
+        <v>302</v>
+      </c>
+      <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H22">
         <f>E22*VALUE(LEFT(G22, FIND(":", G22)-1))</f>
         <v>0</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>7</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:11">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E23">
+        <v>193</v>
+      </c>
+      <c r="E23" t="s">
+        <v>302</v>
+      </c>
+      <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H23">
         <f>E23*VALUE(LEFT(G23, FIND(":", G23)-1))</f>
         <v>0</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>7</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E24">
+        <v>194</v>
+      </c>
+      <c r="E24" t="s">
+        <v>302</v>
+      </c>
+      <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H24">
         <f>E24*VALUE(LEFT(G24, FIND(":", G24)-1))</f>
         <v>0</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>7</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:11">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E25">
+        <v>195</v>
+      </c>
+      <c r="E25" t="s">
+        <v>302</v>
+      </c>
+      <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H25">
         <f>E25*VALUE(LEFT(G25, FIND(":", G25)-1))</f>
         <v>0</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>7</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:11">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E26">
+        <v>196</v>
+      </c>
+      <c r="E26" t="s">
+        <v>302</v>
+      </c>
+      <c r="F26" s="1">
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H26">
         <f>E26*VALUE(LEFT(G26, FIND(":", G26)-1))</f>
         <v>0</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>7</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:11">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E27">
+        <v>197</v>
+      </c>
+      <c r="E27" t="s">
+        <v>302</v>
+      </c>
+      <c r="F27" s="1">
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H27">
         <f>E27*VALUE(LEFT(G27, FIND(":", G27)-1))</f>
         <v>0</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>7</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E28">
+        <v>198</v>
+      </c>
+      <c r="E28" t="s">
+        <v>302</v>
+      </c>
+      <c r="F28" s="1">
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H28">
         <f>E28*VALUE(LEFT(G28, FIND(":", G28)-1))</f>
         <v>0</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>7</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E29">
+        <v>199</v>
+      </c>
+      <c r="E29" t="s">
+        <v>302</v>
+      </c>
+      <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H29">
         <f>E29*VALUE(LEFT(G29, FIND(":", G29)-1))</f>
         <v>0</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>7</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:11">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30">
+        <v>200</v>
+      </c>
+      <c r="E30" t="s">
+        <v>302</v>
+      </c>
+      <c r="F30" s="1">
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H30">
         <f>E30*VALUE(LEFT(G30, FIND(":", G30)-1))</f>
         <v>0</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>7</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:11">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31">
+        <v>201</v>
+      </c>
+      <c r="E31" t="s">
+        <v>303</v>
+      </c>
+      <c r="F31" s="1">
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="H31">
         <f>E31*VALUE(LEFT(G31, FIND(":", G31)-1))</f>
         <v>0</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>7</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:11">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E32">
+        <v>202</v>
+      </c>
+      <c r="E32" t="s">
+        <v>302</v>
+      </c>
+      <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H32">
         <f>E32*VALUE(LEFT(G32, FIND(":", G32)-1))</f>
         <v>0</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>7</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:11">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E33">
+        <v>203</v>
+      </c>
+      <c r="E33" t="s">
+        <v>302</v>
+      </c>
+      <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H33">
         <f>E33*VALUE(LEFT(G33, FIND(":", G33)-1))</f>
         <v>0</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>7</v>
       </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:11">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E34">
+        <v>204</v>
+      </c>
+      <c r="E34" t="s">
+        <v>303</v>
+      </c>
+      <c r="F34" s="1">
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="H34">
         <f>E34*VALUE(LEFT(G34, FIND(":", G34)-1))</f>
         <v>0</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>7</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:11">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E35">
+        <v>205</v>
+      </c>
+      <c r="E35" t="s">
+        <v>302</v>
+      </c>
+      <c r="F35" s="1">
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H35">
         <f>E35*VALUE(LEFT(G35, FIND(":", G35)-1))</f>
         <v>0</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>7</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:11">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E36">
+        <v>206</v>
+      </c>
+      <c r="E36" t="s">
+        <v>302</v>
+      </c>
+      <c r="F36" s="1">
         <v>0</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H36">
         <f>E36*VALUE(LEFT(G36, FIND(":", G36)-1))</f>
         <v>0</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>7</v>
       </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:11">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E37">
+        <v>207</v>
+      </c>
+      <c r="E37" t="s">
+        <v>303</v>
+      </c>
+      <c r="F37" s="1">
         <v>1</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="G37" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H37">
         <f>E37*VALUE(LEFT(G37, FIND(":", G37)-1))</f>
         <v>0</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>7</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:11">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E38">
+        <v>208</v>
+      </c>
+      <c r="E38" t="s">
+        <v>302</v>
+      </c>
+      <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H38">
         <f>E38*VALUE(LEFT(G38, FIND(":", G38)-1))</f>
         <v>0</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>7</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:11">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E39">
+        <v>209</v>
+      </c>
+      <c r="E39" t="s">
+        <v>302</v>
+      </c>
+      <c r="F39" s="1">
         <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H39">
         <f>E39*VALUE(LEFT(G39, FIND(":", G39)-1))</f>
         <v>0</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>7</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:11">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E40">
+        <v>210</v>
+      </c>
+      <c r="E40" t="s">
+        <v>302</v>
+      </c>
+      <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H40">
         <f>E40*VALUE(LEFT(G40, FIND(":", G40)-1))</f>
         <v>0</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>7</v>
       </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:11">
       <c r="A41" s="2" t="s">
         <v>9</v>
       </c>
@@ -3642,1466 +3754,1583 @@
         <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E41">
+        <v>211</v>
+      </c>
+      <c r="E41" t="s">
+        <v>303</v>
+      </c>
+      <c r="F41" s="1">
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="H41">
         <f>E41*VALUE(LEFT(G41, FIND(":", G41)-1))</f>
         <v>0</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>9</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:11">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E42">
+        <v>212</v>
+      </c>
+      <c r="E42" t="s">
+        <v>303</v>
+      </c>
+      <c r="F42" s="1">
         <v>1</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="G42" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H42">
         <f>E42*VALUE(LEFT(G42, FIND(":", G42)-1))</f>
         <v>0</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>9</v>
       </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:11">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E43">
+        <v>213</v>
+      </c>
+      <c r="E43" t="s">
+        <v>303</v>
+      </c>
+      <c r="F43" s="1">
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="H43">
         <f>E43*VALUE(LEFT(G43, FIND(":", G43)-1))</f>
         <v>0</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>9</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:11">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E44">
+        <v>214</v>
+      </c>
+      <c r="E44" t="s">
+        <v>302</v>
+      </c>
+      <c r="F44" s="1">
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H44">
         <f>E44*VALUE(LEFT(G44, FIND(":", G44)-1))</f>
         <v>0</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>9</v>
       </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:11">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E45">
+        <v>215</v>
+      </c>
+      <c r="E45" t="s">
+        <v>302</v>
+      </c>
+      <c r="F45" s="1">
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H45">
         <f>E45*VALUE(LEFT(G45, FIND(":", G45)-1))</f>
         <v>0</v>
       </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
         <v>9</v>
       </c>
-      <c r="J45" t="s">
+      <c r="K45" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:11">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E46">
+        <v>216</v>
+      </c>
+      <c r="E46" t="s">
+        <v>302</v>
+      </c>
+      <c r="F46" s="1">
         <v>0</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H46">
         <f>E46*VALUE(LEFT(G46, FIND(":", G46)-1))</f>
         <v>0</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>9</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:11">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E47">
+        <v>217</v>
+      </c>
+      <c r="E47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F47" s="1">
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H47">
         <f>E47*VALUE(LEFT(G47, FIND(":", G47)-1))</f>
         <v>0</v>
       </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>9</v>
       </c>
-      <c r="J47" t="s">
+      <c r="K47" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:11">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E48">
+        <v>218</v>
+      </c>
+      <c r="E48" t="s">
+        <v>302</v>
+      </c>
+      <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H48">
         <f>E48*VALUE(LEFT(G48, FIND(":", G48)-1))</f>
         <v>0</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>9</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:11">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E49">
+        <v>219</v>
+      </c>
+      <c r="E49" t="s">
+        <v>302</v>
+      </c>
+      <c r="F49" s="1">
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H49">
         <f>E49*VALUE(LEFT(G49, FIND(":", G49)-1))</f>
         <v>0</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>9</v>
       </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:11">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E50">
+        <v>220</v>
+      </c>
+      <c r="E50" t="s">
+        <v>303</v>
+      </c>
+      <c r="F50" s="1">
         <v>1</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="H50">
         <f>E50*VALUE(LEFT(G50, FIND(":", G50)-1))</f>
         <v>0</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>9</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:11">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E51">
+        <v>221</v>
+      </c>
+      <c r="E51" t="s">
+        <v>302</v>
+      </c>
+      <c r="F51" s="1">
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H51">
         <f>E51*VALUE(LEFT(G51, FIND(":", G51)-1))</f>
         <v>0</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>9</v>
       </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:11">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E52">
+        <v>222</v>
+      </c>
+      <c r="E52" t="s">
+        <v>302</v>
+      </c>
+      <c r="F52" s="1">
         <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H52">
         <f>E52*VALUE(LEFT(G52, FIND(":", G52)-1))</f>
         <v>0</v>
       </c>
-      <c r="I52" t="s">
+      <c r="J52" t="s">
         <v>9</v>
       </c>
-      <c r="J52" t="s">
+      <c r="K52" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:11">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E53">
+        <v>223</v>
+      </c>
+      <c r="E53" t="s">
+        <v>303</v>
+      </c>
+      <c r="F53" s="1">
         <v>1</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="H53">
         <f>E53*VALUE(LEFT(G53, FIND(":", G53)-1))</f>
         <v>0</v>
       </c>
-      <c r="I53" t="s">
+      <c r="J53" t="s">
         <v>9</v>
       </c>
-      <c r="J53" t="s">
+      <c r="K53" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:11">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E54">
+        <v>224</v>
+      </c>
+      <c r="E54" t="s">
+        <v>303</v>
+      </c>
+      <c r="F54" s="1">
         <v>1</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="H54">
         <f>E54*VALUE(LEFT(G54, FIND(":", G54)-1))</f>
         <v>0</v>
       </c>
-      <c r="I54" t="s">
+      <c r="J54" t="s">
         <v>9</v>
       </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:11">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E55">
+        <v>225</v>
+      </c>
+      <c r="E55" t="s">
+        <v>302</v>
+      </c>
+      <c r="F55" s="1">
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H55">
         <f>E55*VALUE(LEFT(G55, FIND(":", G55)-1))</f>
         <v>0</v>
       </c>
-      <c r="I55" t="s">
+      <c r="J55" t="s">
         <v>9</v>
       </c>
-      <c r="J55" t="s">
+      <c r="K55" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:11">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E56">
+        <v>226</v>
+      </c>
+      <c r="E56" t="s">
+        <v>302</v>
+      </c>
+      <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H56">
         <f>E56*VALUE(LEFT(G56, FIND(":", G56)-1))</f>
         <v>0</v>
       </c>
-      <c r="I56" t="s">
+      <c r="J56" t="s">
         <v>9</v>
       </c>
-      <c r="J56" t="s">
+      <c r="K56" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:11">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E57">
+        <v>227</v>
+      </c>
+      <c r="E57" t="s">
+        <v>302</v>
+      </c>
+      <c r="F57" s="1">
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H57">
         <f>E57*VALUE(LEFT(G57, FIND(":", G57)-1))</f>
         <v>0</v>
       </c>
-      <c r="I57" t="s">
+      <c r="J57" t="s">
         <v>9</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:11">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E58">
+        <v>228</v>
+      </c>
+      <c r="E58" t="s">
+        <v>303</v>
+      </c>
+      <c r="F58" s="1">
         <v>1</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="G58" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H58">
         <f>E58*VALUE(LEFT(G58, FIND(":", G58)-1))</f>
         <v>0</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" t="s">
         <v>9</v>
       </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:11">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E59">
+        <v>229</v>
+      </c>
+      <c r="E59" t="s">
+        <v>302</v>
+      </c>
+      <c r="F59" s="1">
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H59">
         <f>E59*VALUE(LEFT(G59, FIND(":", G59)-1))</f>
         <v>0</v>
       </c>
-      <c r="I59" t="s">
+      <c r="J59" t="s">
         <v>9</v>
       </c>
-      <c r="J59" t="s">
+      <c r="K59" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:11">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E60">
+        <v>230</v>
+      </c>
+      <c r="E60" t="s">
+        <v>303</v>
+      </c>
+      <c r="F60" s="1">
         <v>1</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H60">
         <f>E60*VALUE(LEFT(G60, FIND(":", G60)-1))</f>
         <v>0</v>
       </c>
-      <c r="I60" t="s">
+      <c r="J60" t="s">
         <v>9</v>
       </c>
-      <c r="J60" t="s">
+      <c r="K60" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:11">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E61">
+        <v>231</v>
+      </c>
+      <c r="E61" t="s">
+        <v>303</v>
+      </c>
+      <c r="F61" s="1">
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H61">
         <f>E61*VALUE(LEFT(G61, FIND(":", G61)-1))</f>
         <v>0</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61" t="s">
         <v>9</v>
       </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:11">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E62">
+        <v>232</v>
+      </c>
+      <c r="E62" t="s">
+        <v>302</v>
+      </c>
+      <c r="F62" s="1">
         <v>0</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H62">
         <f>E62*VALUE(LEFT(G62, FIND(":", G62)-1))</f>
         <v>0</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>9</v>
       </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:11">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E63">
+        <v>233</v>
+      </c>
+      <c r="E63" t="s">
+        <v>302</v>
+      </c>
+      <c r="F63" s="1">
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H63">
         <f>E63*VALUE(LEFT(G63, FIND(":", G63)-1))</f>
         <v>0</v>
       </c>
-      <c r="I63" t="s">
+      <c r="J63" t="s">
         <v>9</v>
       </c>
-      <c r="J63" t="s">
+      <c r="K63" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:11">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E64">
+        <v>234</v>
+      </c>
+      <c r="E64" t="s">
+        <v>302</v>
+      </c>
+      <c r="F64" s="1">
         <v>0</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H64">
         <f>E64*VALUE(LEFT(G64, FIND(":", G64)-1))</f>
         <v>0</v>
       </c>
-      <c r="I64" t="s">
+      <c r="J64" t="s">
         <v>9</v>
       </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:11">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E65">
+        <v>235</v>
+      </c>
+      <c r="E65" t="s">
+        <v>303</v>
+      </c>
+      <c r="F65" s="1">
         <v>1</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="G65" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H65">
         <f>E65*VALUE(LEFT(G65, FIND(":", G65)-1))</f>
         <v>0</v>
       </c>
-      <c r="I65" t="s">
+      <c r="J65" t="s">
         <v>9</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:11">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E66">
+        <v>236</v>
+      </c>
+      <c r="E66" t="s">
+        <v>303</v>
+      </c>
+      <c r="F66" s="1">
         <v>1</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="G66" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H66">
         <f>E66*VALUE(LEFT(G66, FIND(":", G66)-1))</f>
         <v>0</v>
       </c>
-      <c r="I66" t="s">
+      <c r="J66" t="s">
         <v>9</v>
       </c>
-      <c r="J66" t="s">
+      <c r="K66" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:11">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E67">
+        <v>237</v>
+      </c>
+      <c r="E67" t="s">
+        <v>303</v>
+      </c>
+      <c r="F67" s="1">
         <v>1</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="G67" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H67">
         <f>E67*VALUE(LEFT(G67, FIND(":", G67)-1))</f>
         <v>0</v>
       </c>
-      <c r="I67" t="s">
+      <c r="J67" t="s">
         <v>9</v>
       </c>
-      <c r="J67" t="s">
+      <c r="K67" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:11">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E68">
+        <v>238</v>
+      </c>
+      <c r="E68" t="s">
+        <v>303</v>
+      </c>
+      <c r="F68" s="1">
         <v>1</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="G68" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H68">
         <f>E68*VALUE(LEFT(G68, FIND(":", G68)-1))</f>
         <v>0</v>
       </c>
-      <c r="I68" t="s">
+      <c r="J68" t="s">
         <v>9</v>
       </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:11">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E69">
+        <v>239</v>
+      </c>
+      <c r="E69" t="s">
+        <v>303</v>
+      </c>
+      <c r="F69" s="1">
         <v>1</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="G69" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H69">
         <f>E69*VALUE(LEFT(G69, FIND(":", G69)-1))</f>
         <v>0</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
         <v>9</v>
       </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:11">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E70">
+        <v>240</v>
+      </c>
+      <c r="E70" t="s">
+        <v>303</v>
+      </c>
+      <c r="F70" s="1">
         <v>1</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="G70" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H70">
         <f>E70*VALUE(LEFT(G70, FIND(":", G70)-1))</f>
         <v>0</v>
       </c>
-      <c r="I70" t="s">
+      <c r="J70" t="s">
         <v>9</v>
       </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:11">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E71">
+        <v>241</v>
+      </c>
+      <c r="E71" t="s">
+        <v>302</v>
+      </c>
+      <c r="F71" s="1">
         <v>0</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H71">
         <f>E71*VALUE(LEFT(G71, FIND(":", G71)-1))</f>
         <v>0</v>
       </c>
-      <c r="I71" t="s">
+      <c r="J71" t="s">
         <v>9</v>
       </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:11">
       <c r="A72" s="2"/>
       <c r="B72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E72">
+        <v>242</v>
+      </c>
+      <c r="E72" t="s">
+        <v>303</v>
+      </c>
+      <c r="F72" s="1">
         <v>1</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="G72" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H72">
         <f>E72*VALUE(LEFT(G72, FIND(":", G72)-1))</f>
         <v>0</v>
       </c>
-      <c r="I72" t="s">
+      <c r="J72" t="s">
         <v>9</v>
       </c>
-      <c r="J72" t="s">
+      <c r="K72" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:11">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E73">
+        <v>243</v>
+      </c>
+      <c r="E73" t="s">
+        <v>303</v>
+      </c>
+      <c r="F73" s="1">
         <v>1</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="G73" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H73">
         <f>E73*VALUE(LEFT(G73, FIND(":", G73)-1))</f>
         <v>0</v>
       </c>
-      <c r="I73" t="s">
+      <c r="J73" t="s">
         <v>9</v>
       </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:11">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E74">
+        <v>244</v>
+      </c>
+      <c r="E74" t="s">
+        <v>303</v>
+      </c>
+      <c r="F74" s="1">
         <v>1</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="H74">
         <f>E74*VALUE(LEFT(G74, FIND(":", G74)-1))</f>
         <v>0</v>
       </c>
-      <c r="I74" t="s">
+      <c r="J74" t="s">
         <v>9</v>
       </c>
-      <c r="J74" t="s">
+      <c r="K74" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:11">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E75">
+        <v>245</v>
+      </c>
+      <c r="E75" t="s">
+        <v>302</v>
+      </c>
+      <c r="F75" s="1">
         <v>0</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H75">
         <f>E75*VALUE(LEFT(G75, FIND(":", G75)-1))</f>
         <v>0</v>
       </c>
-      <c r="I75" t="s">
+      <c r="J75" t="s">
         <v>9</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:11">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E76">
+        <v>246</v>
+      </c>
+      <c r="E76" t="s">
+        <v>302</v>
+      </c>
+      <c r="F76" s="1">
         <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H76">
         <f>E76*VALUE(LEFT(G76, FIND(":", G76)-1))</f>
         <v>0</v>
       </c>
-      <c r="I76" t="s">
+      <c r="J76" t="s">
         <v>9</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:11">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E77">
+        <v>247</v>
+      </c>
+      <c r="E77" t="s">
+        <v>303</v>
+      </c>
+      <c r="F77" s="1">
         <v>1</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="G77" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H77">
         <f>E77*VALUE(LEFT(G77, FIND(":", G77)-1))</f>
         <v>0</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>9</v>
       </c>
-      <c r="J77" t="s">
+      <c r="K77" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:11">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E78">
+        <v>248</v>
+      </c>
+      <c r="E78" t="s">
+        <v>302</v>
+      </c>
+      <c r="F78" s="1">
         <v>0</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H78">
         <f>E78*VALUE(LEFT(G78, FIND(":", G78)-1))</f>
         <v>0</v>
       </c>
-      <c r="I78" t="s">
+      <c r="J78" t="s">
         <v>9</v>
       </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:11">
       <c r="A79" s="2"/>
       <c r="B79" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E79">
+        <v>249</v>
+      </c>
+      <c r="E79" t="s">
+        <v>302</v>
+      </c>
+      <c r="F79" s="1">
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H79">
         <f>E79*VALUE(LEFT(G79, FIND(":", G79)-1))</f>
         <v>0</v>
       </c>
-      <c r="I79" t="s">
+      <c r="J79" t="s">
         <v>9</v>
       </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:11">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E80">
+        <v>250</v>
+      </c>
+      <c r="E80" t="s">
+        <v>302</v>
+      </c>
+      <c r="F80" s="1">
         <v>0</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H80">
         <f>E80*VALUE(LEFT(G80, FIND(":", G80)-1))</f>
         <v>0</v>
       </c>
-      <c r="I80" t="s">
+      <c r="J80" t="s">
         <v>9</v>
       </c>
-      <c r="J80" t="s">
+      <c r="K80" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:11">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E81">
+        <v>251</v>
+      </c>
+      <c r="E81" t="s">
+        <v>302</v>
+      </c>
+      <c r="F81" s="1">
         <v>0</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H81">
         <f>E81*VALUE(LEFT(G81, FIND(":", G81)-1))</f>
         <v>0</v>
       </c>
-      <c r="I81" t="s">
+      <c r="J81" t="s">
         <v>9</v>
       </c>
-      <c r="J81" t="s">
+      <c r="K81" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:11">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E82">
+        <v>252</v>
+      </c>
+      <c r="E82" t="s">
+        <v>303</v>
+      </c>
+      <c r="F82" s="1">
         <v>1</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="H82">
         <f>E82*VALUE(LEFT(G82, FIND(":", G82)-1))</f>
         <v>0</v>
       </c>
-      <c r="I82" t="s">
+      <c r="J82" t="s">
         <v>9</v>
       </c>
-      <c r="J82" t="s">
+      <c r="K82" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:11">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E83">
+        <v>253</v>
+      </c>
+      <c r="E83" t="s">
+        <v>302</v>
+      </c>
+      <c r="F83" s="1">
         <v>0</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H83">
         <f>E83*VALUE(LEFT(G83, FIND(":", G83)-1))</f>
         <v>0</v>
       </c>
-      <c r="I83" t="s">
+      <c r="J83" t="s">
         <v>9</v>
       </c>
-      <c r="J83" t="s">
+      <c r="K83" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:11">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E84">
+        <v>254</v>
+      </c>
+      <c r="E84" t="s">
+        <v>303</v>
+      </c>
+      <c r="F84" s="1">
         <v>1</v>
       </c>
-      <c r="F84" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="G84" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H84">
         <f>E84*VALUE(LEFT(G84, FIND(":", G84)-1))</f>
         <v>0</v>
       </c>
-      <c r="I84" t="s">
+      <c r="J84" t="s">
         <v>9</v>
       </c>
-      <c r="J84" t="s">
+      <c r="K84" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:11">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E85">
+        <v>255</v>
+      </c>
+      <c r="E85" t="s">
+        <v>303</v>
+      </c>
+      <c r="F85" s="1">
         <v>1</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="G85" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H85">
         <f>E85*VALUE(LEFT(G85, FIND(":", G85)-1))</f>
         <v>0</v>
       </c>
-      <c r="I85" t="s">
+      <c r="J85" t="s">
         <v>9</v>
       </c>
-      <c r="J85" t="s">
+      <c r="K85" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:11">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E86">
+        <v>256</v>
+      </c>
+      <c r="E86" t="s">
+        <v>302</v>
+      </c>
+      <c r="F86" s="1">
         <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H86">
         <f>E86*VALUE(LEFT(G86, FIND(":", G86)-1))</f>
         <v>0</v>
       </c>
-      <c r="I86" t="s">
+      <c r="J86" t="s">
         <v>9</v>
       </c>
-      <c r="J86" t="s">
+      <c r="K86" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:11">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E87">
+        <v>257</v>
+      </c>
+      <c r="E87" t="s">
+        <v>304</v>
+      </c>
+      <c r="F87" s="1">
         <v>1</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="H87">
         <f>E87*VALUE(LEFT(G87, FIND(":", G87)-1))</f>
         <v>0</v>
       </c>
-      <c r="I87" t="s">
+      <c r="J87" t="s">
         <v>9</v>
       </c>
-      <c r="J87" t="s">
+      <c r="K87" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:11">
       <c r="A88" s="2"/>
       <c r="B88" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E88">
+        <v>258</v>
+      </c>
+      <c r="E88" t="s">
+        <v>302</v>
+      </c>
+      <c r="F88" s="1">
         <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H88">
         <f>E88*VALUE(LEFT(G88, FIND(":", G88)-1))</f>
         <v>0</v>
       </c>
-      <c r="I88" t="s">
+      <c r="J88" t="s">
         <v>9</v>
       </c>
-      <c r="J88" t="s">
+      <c r="K88" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:11">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E89">
+        <v>259</v>
+      </c>
+      <c r="E89" t="s">
+        <v>303</v>
+      </c>
+      <c r="F89" s="1">
         <v>1</v>
       </c>
-      <c r="F89" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="G89" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H89">
         <f>E89*VALUE(LEFT(G89, FIND(":", G89)-1))</f>
         <v>0</v>
       </c>
-      <c r="I89" t="s">
+      <c r="J89" t="s">
         <v>9</v>
       </c>
-      <c r="J89" t="s">
+      <c r="K89" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:11">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E90">
+        <v>260</v>
+      </c>
+      <c r="E90" t="s">
+        <v>303</v>
+      </c>
+      <c r="F90" s="1">
         <v>1</v>
       </c>
-      <c r="F90" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="G90" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H90">
         <f>E90*VALUE(LEFT(G90, FIND(":", G90)-1))</f>
         <v>0</v>
       </c>
-      <c r="I90" t="s">
+      <c r="J90" t="s">
         <v>9</v>
       </c>
-      <c r="J90" t="s">
+      <c r="K90" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:11">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E91">
+        <v>261</v>
+      </c>
+      <c r="E91" t="s">
+        <v>302</v>
+      </c>
+      <c r="F91" s="1">
         <v>0</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H91">
         <f>E91*VALUE(LEFT(G91, FIND(":", G91)-1))</f>
         <v>0</v>
       </c>
-      <c r="I91" t="s">
+      <c r="J91" t="s">
         <v>9</v>
       </c>
-      <c r="J91" t="s">
+      <c r="K91" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:11">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E92">
+        <v>262</v>
+      </c>
+      <c r="E92" t="s">
+        <v>303</v>
+      </c>
+      <c r="F92" s="1">
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="H92">
         <f>E92*VALUE(LEFT(G92, FIND(":", G92)-1))</f>
         <v>0</v>
       </c>
-      <c r="I92" t="s">
+      <c r="J92" t="s">
         <v>9</v>
       </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:11">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E93">
+        <v>263</v>
+      </c>
+      <c r="E93" t="s">
+        <v>302</v>
+      </c>
+      <c r="F93" s="1">
         <v>0</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H93">
         <f>E93*VALUE(LEFT(G93, FIND(":", G93)-1))</f>
         <v>0</v>
       </c>
-      <c r="I93" t="s">
+      <c r="J93" t="s">
         <v>9</v>
       </c>
-      <c r="J93" t="s">
+      <c r="K93" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:11">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E94">
+        <v>264</v>
+      </c>
+      <c r="E94" t="s">
+        <v>302</v>
+      </c>
+      <c r="F94" s="1">
         <v>0</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H94">
         <f>E94*VALUE(LEFT(G94, FIND(":", G94)-1))</f>
         <v>0</v>
       </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>9</v>
       </c>
-      <c r="J94" t="s">
+      <c r="K94" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:11">
       <c r="A95" s="2" t="s">
         <v>8</v>
       </c>
@@ -5109,847 +5338,910 @@
         <v>14</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="E95">
+        <v>265</v>
+      </c>
+      <c r="E95" t="s">
+        <v>302</v>
+      </c>
+      <c r="F95" s="1">
         <v>0</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H95">
         <f>E95*VALUE(LEFT(G95, FIND(":", G95)-1))</f>
         <v>0</v>
       </c>
-      <c r="I95" t="s">
+      <c r="J95" t="s">
         <v>8</v>
       </c>
-      <c r="J95" t="s">
+      <c r="K95" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:11">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E96">
+        <v>266</v>
+      </c>
+      <c r="E96" t="s">
+        <v>302</v>
+      </c>
+      <c r="F96" s="1">
         <v>0</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H96">
         <f>E96*VALUE(LEFT(G96, FIND(":", G96)-1))</f>
         <v>0</v>
       </c>
-      <c r="I96" t="s">
+      <c r="J96" t="s">
         <v>8</v>
       </c>
-      <c r="J96" t="s">
+      <c r="K96" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:11">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="E97">
+        <v>267</v>
+      </c>
+      <c r="E97" t="s">
+        <v>302</v>
+      </c>
+      <c r="F97" s="1">
         <v>0</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H97">
         <f>E97*VALUE(LEFT(G97, FIND(":", G97)-1))</f>
         <v>0</v>
       </c>
-      <c r="I97" t="s">
+      <c r="J97" t="s">
         <v>8</v>
       </c>
-      <c r="J97" t="s">
+      <c r="K97" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:11">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E98">
+        <v>268</v>
+      </c>
+      <c r="E98" t="s">
+        <v>302</v>
+      </c>
+      <c r="F98" s="1">
         <v>0</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H98">
         <f>E98*VALUE(LEFT(G98, FIND(":", G98)-1))</f>
         <v>0</v>
       </c>
-      <c r="I98" t="s">
+      <c r="J98" t="s">
         <v>8</v>
       </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:11">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="E99">
+        <v>269</v>
+      </c>
+      <c r="E99" t="s">
+        <v>303</v>
+      </c>
+      <c r="F99" s="1">
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="H99">
         <f>E99*VALUE(LEFT(G99, FIND(":", G99)-1))</f>
         <v>0</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>8</v>
       </c>
-      <c r="J99" t="s">
+      <c r="K99" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:11">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="E100">
+        <v>270</v>
+      </c>
+      <c r="E100" t="s">
+        <v>302</v>
+      </c>
+      <c r="F100" s="1">
         <v>0</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H100">
         <f>E100*VALUE(LEFT(G100, FIND(":", G100)-1))</f>
         <v>0</v>
       </c>
-      <c r="I100" t="s">
+      <c r="J100" t="s">
         <v>8</v>
       </c>
-      <c r="J100" t="s">
+      <c r="K100" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:11">
       <c r="A101" s="2"/>
       <c r="B101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="E101">
+        <v>271</v>
+      </c>
+      <c r="E101" t="s">
+        <v>303</v>
+      </c>
+      <c r="F101" s="1">
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="H101">
         <f>E101*VALUE(LEFT(G101, FIND(":", G101)-1))</f>
         <v>0</v>
       </c>
-      <c r="I101" t="s">
+      <c r="J101" t="s">
         <v>8</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:11">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E102">
+        <v>272</v>
+      </c>
+      <c r="E102" t="s">
+        <v>303</v>
+      </c>
+      <c r="F102" s="1">
         <v>1</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="H102">
         <f>E102*VALUE(LEFT(G102, FIND(":", G102)-1))</f>
         <v>0</v>
       </c>
-      <c r="I102" t="s">
+      <c r="J102" t="s">
         <v>8</v>
       </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:11">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="E103">
+        <v>273</v>
+      </c>
+      <c r="E103" t="s">
+        <v>302</v>
+      </c>
+      <c r="F103" s="1">
         <v>0</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H103">
         <f>E103*VALUE(LEFT(G103, FIND(":", G103)-1))</f>
         <v>0</v>
       </c>
-      <c r="I103" t="s">
+      <c r="J103" t="s">
         <v>8</v>
       </c>
-      <c r="J103" t="s">
+      <c r="K103" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:11">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E104">
+        <v>274</v>
+      </c>
+      <c r="E104" t="s">
+        <v>302</v>
+      </c>
+      <c r="F104" s="1">
         <v>0</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H104">
         <f>E104*VALUE(LEFT(G104, FIND(":", G104)-1))</f>
         <v>0</v>
       </c>
-      <c r="I104" t="s">
+      <c r="J104" t="s">
         <v>8</v>
       </c>
-      <c r="J104" t="s">
+      <c r="K104" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:11">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="E105">
+        <v>275</v>
+      </c>
+      <c r="E105" t="s">
+        <v>302</v>
+      </c>
+      <c r="F105" s="1">
         <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H105">
         <f>E105*VALUE(LEFT(G105, FIND(":", G105)-1))</f>
         <v>0</v>
       </c>
-      <c r="I105" t="s">
+      <c r="J105" t="s">
         <v>8</v>
       </c>
-      <c r="J105" t="s">
+      <c r="K105" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:11">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="E106">
+        <v>276</v>
+      </c>
+      <c r="E106" t="s">
+        <v>302</v>
+      </c>
+      <c r="F106" s="1">
         <v>0</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H106">
         <f>E106*VALUE(LEFT(G106, FIND(":", G106)-1))</f>
         <v>0</v>
       </c>
-      <c r="I106" t="s">
+      <c r="J106" t="s">
         <v>8</v>
       </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:11">
       <c r="A107" s="2"/>
       <c r="B107" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E107">
+        <v>277</v>
+      </c>
+      <c r="E107" t="s">
+        <v>302</v>
+      </c>
+      <c r="F107" s="1">
         <v>0</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H107">
         <f>E107*VALUE(LEFT(G107, FIND(":", G107)-1))</f>
         <v>0</v>
       </c>
-      <c r="I107" t="s">
+      <c r="J107" t="s">
         <v>8</v>
       </c>
-      <c r="J107" t="s">
+      <c r="K107" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:11">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E108">
+        <v>278</v>
+      </c>
+      <c r="E108" t="s">
+        <v>303</v>
+      </c>
+      <c r="F108" s="1">
         <v>1</v>
       </c>
-      <c r="F108" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="G108" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H108">
         <f>E108*VALUE(LEFT(G108, FIND(":", G108)-1))</f>
         <v>0</v>
       </c>
-      <c r="I108" t="s">
+      <c r="J108" t="s">
         <v>8</v>
       </c>
-      <c r="J108" t="s">
+      <c r="K108" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:11">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E109">
+        <v>279</v>
+      </c>
+      <c r="E109" t="s">
+        <v>303</v>
+      </c>
+      <c r="F109" s="1">
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H109">
         <f>E109*VALUE(LEFT(G109, FIND(":", G109)-1))</f>
         <v>0</v>
       </c>
-      <c r="I109" t="s">
+      <c r="J109" t="s">
         <v>8</v>
       </c>
-      <c r="J109" t="s">
+      <c r="K109" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:11">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E110">
+        <v>280</v>
+      </c>
+      <c r="E110" t="s">
+        <v>303</v>
+      </c>
+      <c r="F110" s="1">
         <v>1</v>
       </c>
-      <c r="F110" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="G110" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H110">
         <f>E110*VALUE(LEFT(G110, FIND(":", G110)-1))</f>
         <v>0</v>
       </c>
-      <c r="I110" t="s">
+      <c r="J110" t="s">
         <v>8</v>
       </c>
-      <c r="J110" t="s">
+      <c r="K110" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:11">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E111">
+        <v>281</v>
+      </c>
+      <c r="E111" t="s">
+        <v>303</v>
+      </c>
+      <c r="F111" s="1">
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="H111">
         <f>E111*VALUE(LEFT(G111, FIND(":", G111)-1))</f>
         <v>0</v>
       </c>
-      <c r="I111" t="s">
+      <c r="J111" t="s">
         <v>8</v>
       </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:11">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E112">
+        <v>282</v>
+      </c>
+      <c r="E112" t="s">
+        <v>303</v>
+      </c>
+      <c r="F112" s="1">
         <v>1</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="G112" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H112">
         <f>E112*VALUE(LEFT(G112, FIND(":", G112)-1))</f>
         <v>0</v>
       </c>
-      <c r="I112" t="s">
+      <c r="J112" t="s">
         <v>8</v>
       </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:11">
       <c r="A113" s="2"/>
       <c r="B113" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E113">
+        <v>283</v>
+      </c>
+      <c r="E113" t="s">
+        <v>301</v>
+      </c>
+      <c r="F113" s="1">
         <v>1</v>
       </c>
-      <c r="F113" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="G113" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H113">
         <f>E113*VALUE(LEFT(G113, FIND(":", G113)-1))</f>
         <v>0</v>
       </c>
-      <c r="I113" t="s">
+      <c r="J113" t="s">
         <v>8</v>
       </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:11">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E114">
+        <v>284</v>
+      </c>
+      <c r="E114" t="s">
+        <v>301</v>
+      </c>
+      <c r="F114" s="1">
         <v>1</v>
       </c>
-      <c r="F114" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="G114" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H114">
         <f>E114*VALUE(LEFT(G114, FIND(":", G114)-1))</f>
         <v>0</v>
       </c>
-      <c r="I114" t="s">
+      <c r="J114" t="s">
         <v>8</v>
       </c>
-      <c r="J114" t="s">
+      <c r="K114" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:11">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E115">
+        <v>285</v>
+      </c>
+      <c r="E115" t="s">
+        <v>301</v>
+      </c>
+      <c r="F115" s="1">
         <v>1</v>
       </c>
-      <c r="F115" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="G115" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H115">
         <f>E115*VALUE(LEFT(G115, FIND(":", G115)-1))</f>
         <v>0</v>
       </c>
-      <c r="I115" t="s">
+      <c r="J115" t="s">
         <v>8</v>
       </c>
-      <c r="J115" t="s">
+      <c r="K115" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:11">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="E116">
+        <v>286</v>
+      </c>
+      <c r="E116" t="s">
+        <v>301</v>
+      </c>
+      <c r="F116" s="1">
         <v>1</v>
       </c>
-      <c r="F116" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="G116" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H116">
         <f>E116*VALUE(LEFT(G116, FIND(":", G116)-1))</f>
         <v>0</v>
       </c>
-      <c r="I116" t="s">
+      <c r="J116" t="s">
         <v>8</v>
       </c>
-      <c r="J116" t="s">
+      <c r="K116" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:11">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E117">
+        <v>287</v>
+      </c>
+      <c r="E117" t="s">
+        <v>303</v>
+      </c>
+      <c r="F117" s="1">
         <v>1</v>
       </c>
-      <c r="F117" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="G117" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H117">
         <f>E117*VALUE(LEFT(G117, FIND(":", G117)-1))</f>
         <v>0</v>
       </c>
-      <c r="I117" t="s">
+      <c r="J117" t="s">
         <v>8</v>
       </c>
-      <c r="J117" t="s">
+      <c r="K117" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:11">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="E118">
+        <v>288</v>
+      </c>
+      <c r="E118" t="s">
+        <v>303</v>
+      </c>
+      <c r="F118" s="1">
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H118">
         <f>E118*VALUE(LEFT(G118, FIND(":", G118)-1))</f>
         <v>0</v>
       </c>
-      <c r="I118" t="s">
+      <c r="J118" t="s">
         <v>8</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:11">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E119">
+        <v>289</v>
+      </c>
+      <c r="E119" t="s">
+        <v>301</v>
+      </c>
+      <c r="F119" s="1">
         <v>1</v>
       </c>
-      <c r="F119" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="G119" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H119">
         <f>E119*VALUE(LEFT(G119, FIND(":", G119)-1))</f>
         <v>0</v>
       </c>
-      <c r="I119" t="s">
+      <c r="J119" t="s">
         <v>8</v>
       </c>
-      <c r="J119" t="s">
+      <c r="K119" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:11">
       <c r="A120" s="2"/>
       <c r="B120" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E120">
+        <v>290</v>
+      </c>
+      <c r="E120" t="s">
+        <v>303</v>
+      </c>
+      <c r="F120" s="1">
         <v>1</v>
       </c>
-      <c r="F120" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="G120" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H120">
         <f>E120*VALUE(LEFT(G120, FIND(":", G120)-1))</f>
         <v>0</v>
       </c>
-      <c r="I120" t="s">
+      <c r="J120" t="s">
         <v>8</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:11">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E121">
+        <v>291</v>
+      </c>
+      <c r="E121" t="s">
+        <v>302</v>
+      </c>
+      <c r="F121" s="1">
         <v>0</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H121">
         <f>E121*VALUE(LEFT(G121, FIND(":", G121)-1))</f>
         <v>0</v>
       </c>
-      <c r="I121" t="s">
+      <c r="J121" t="s">
         <v>8</v>
       </c>
-      <c r="J121" t="s">
+      <c r="K121" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:11">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E122">
+        <v>292</v>
+      </c>
+      <c r="E122" t="s">
+        <v>302</v>
+      </c>
+      <c r="F122" s="1">
         <v>0</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H122">
         <f>E122*VALUE(LEFT(G122, FIND(":", G122)-1))</f>
         <v>0</v>
       </c>
-      <c r="I122" t="s">
+      <c r="J122" t="s">
         <v>8</v>
       </c>
-      <c r="J122" t="s">
+      <c r="K122" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:11">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="E123">
+        <v>293</v>
+      </c>
+      <c r="E123" t="s">
+        <v>302</v>
+      </c>
+      <c r="F123" s="1">
         <v>0</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H123">
         <f>E123*VALUE(LEFT(G123, FIND(":", G123)-1))</f>
         <v>0</v>
       </c>
-      <c r="I123" t="s">
+      <c r="J123" t="s">
         <v>8</v>
       </c>
-      <c r="J123" t="s">
+      <c r="K123" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:11">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="E124">
+        <v>294</v>
+      </c>
+      <c r="E124" t="s">
+        <v>302</v>
+      </c>
+      <c r="F124" s="1">
         <v>0</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H124">
         <f>E124*VALUE(LEFT(G124, FIND(":", G124)-1))</f>
         <v>0</v>
       </c>
-      <c r="I124" t="s">
+      <c r="J124" t="s">
         <v>8</v>
       </c>
-      <c r="J124" t="s">
+      <c r="K124" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:11">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E125">
+        <v>295</v>
+      </c>
+      <c r="E125" t="s">
+        <v>303</v>
+      </c>
+      <c r="F125" s="1">
         <v>1</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H125">
         <f>E125*VALUE(LEFT(G125, FIND(":", G125)-1))</f>
         <v>0</v>
       </c>
-      <c r="I125" t="s">
+      <c r="J125" t="s">
         <v>8</v>
       </c>
-      <c r="J125" t="s">
+      <c r="K125" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:11">
       <c r="A126" s="2" t="s">
         <v>6</v>
       </c>
@@ -5957,129 +6249,144 @@
         <v>27</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E126">
+        <v>296</v>
+      </c>
+      <c r="E126" t="s">
+        <v>302</v>
+      </c>
+      <c r="F126" s="1">
         <v>0</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H126">
         <f>E126*VALUE(LEFT(G126, FIND(":", G126)-1))</f>
         <v>0</v>
       </c>
-      <c r="I126" t="s">
+      <c r="J126" t="s">
         <v>6</v>
       </c>
-      <c r="J126" t="s">
+      <c r="K126" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:11">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E127">
+        <v>297</v>
+      </c>
+      <c r="E127" t="s">
+        <v>302</v>
+      </c>
+      <c r="F127" s="1">
         <v>0</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H127">
         <f>E127*VALUE(LEFT(G127, FIND(":", G127)-1))</f>
         <v>0</v>
       </c>
-      <c r="I127" t="s">
+      <c r="J127" t="s">
         <v>6</v>
       </c>
-      <c r="J127" t="s">
+      <c r="K127" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:11">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E128">
+        <v>298</v>
+      </c>
+      <c r="E128" t="s">
+        <v>302</v>
+      </c>
+      <c r="F128" s="1">
         <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H128">
         <f>E128*VALUE(LEFT(G128, FIND(":", G128)-1))</f>
         <v>0</v>
       </c>
-      <c r="I128" t="s">
+      <c r="J128" t="s">
         <v>6</v>
       </c>
-      <c r="J128" t="s">
+      <c r="K128" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:11">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="E129">
+        <v>299</v>
+      </c>
+      <c r="E129" t="s">
+        <v>303</v>
+      </c>
+      <c r="F129" s="1">
         <v>1</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="H129">
         <f>E129*VALUE(LEFT(G129, FIND(":", G129)-1))</f>
         <v>0</v>
       </c>
-      <c r="I129" t="s">
+      <c r="J129" t="s">
         <v>6</v>
       </c>
-      <c r="J129" t="s">
+      <c r="K129" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:11">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E130">
+        <v>300</v>
+      </c>
+      <c r="E130" t="s">
+        <v>302</v>
+      </c>
+      <c r="F130" s="1">
         <v>0</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H130">
         <f>E130*VALUE(LEFT(G130, FIND(":", G130)-1))</f>
         <v>0</v>
       </c>
-      <c r="I130" t="s">
+      <c r="J130" t="s">
         <v>6</v>
       </c>
-      <c r="J130" t="s">
+      <c r="K130" t="s">
         <v>27</v>
       </c>
     </row>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="381">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -58,10 +58,10 @@
     <t>Anomaly Management</t>
   </si>
   <si>
-    <t>Architecting for Cloud</t>
-  </si>
-  <si>
-    <t>Benchmarking</t>
+    <t>Architecting &amp; Workload Placement</t>
+  </si>
+  <si>
+    <t>Automation, Tools &amp; Services</t>
   </si>
   <si>
     <t>Budgeting</t>
@@ -79,9 +79,6 @@
     <t>FinOps Practice Operations</t>
   </si>
   <si>
-    <t>FinOps Tools &amp; Services</t>
-  </si>
-  <si>
     <t>Forecasting</t>
   </si>
   <si>
@@ -91,12 +88,12 @@
     <t>Invoicing &amp; Chargeback</t>
   </si>
   <si>
+    <t>KPIs &amp; Benchmarking</t>
+  </si>
+  <si>
     <t>Licensing &amp; SaaS</t>
   </si>
   <si>
-    <t>Onboarding Workloads</t>
-  </si>
-  <si>
     <t>Planning &amp; Estimating</t>
   </si>
   <si>
@@ -112,7 +109,7 @@
     <t>Unit Economics</t>
   </si>
   <si>
-    <t>Workload Optimization</t>
+    <t>Usage Optimization</t>
   </si>
   <si>
     <t>serial number</t>
@@ -247,6 +244,24 @@
     <t>Resolve Variances &amp; Increase Coverage</t>
   </si>
   <si>
+    <t>Establish Architecture Review Process</t>
+  </si>
+  <si>
+    <t>Assess Workloads for Modernization</t>
+  </si>
+  <si>
+    <t>Estimate Trade-Offs &amp; Document Cases</t>
+  </si>
+  <si>
+    <t>Implement Iteratively &amp; Measure Results</t>
+  </si>
+  <si>
+    <t>Publish Benefits &amp; Update References</t>
+  </si>
+  <si>
+    <t>Strengthen Architecture Collaboration</t>
+  </si>
+  <si>
     <t>Create Workload Selection Criteria</t>
   </si>
   <si>
@@ -265,24 +280,6 @@
     <t>Review Outcomes &amp; Adjust Patterns</t>
   </si>
   <si>
-    <t>Establish Architecture Review Process</t>
-  </si>
-  <si>
-    <t>Assess Workloads for Modernization</t>
-  </si>
-  <si>
-    <t>Estimate Trade-Offs &amp; Document Cases</t>
-  </si>
-  <si>
-    <t>Implement Iteratively &amp; Measure Results</t>
-  </si>
-  <si>
-    <t>Publish Benefits &amp; Update References</t>
-  </si>
-  <si>
-    <t>Strengthen Architecture Collaboration</t>
-  </si>
-  <si>
     <t>Inventory Licenses &amp; Map Resources</t>
   </si>
   <si>
@@ -634,6 +631,24 @@
     <t>112</t>
   </si>
   <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
     <t>118</t>
   </si>
   <si>
@@ -650,24 +665,6 @@
   </si>
   <si>
     <t>123</t>
-  </si>
-  <si>
-    <t>061</t>
-  </si>
-  <si>
-    <t>062</t>
-  </si>
-  <si>
-    <t>063</t>
-  </si>
-  <si>
-    <t>064</t>
-  </si>
-  <si>
-    <t>065</t>
-  </si>
-  <si>
-    <t>066</t>
   </si>
   <si>
     <t>073</t>
@@ -979,18 +976,18 @@
 10*Ceil(x/5)</t>
   </si>
   <si>
-    <t>* Process defined for new accounts and resources deployed
-* Train teams on process
-* Automate process
-10*Ceil(x/3)</t>
-  </si>
-  <si>
     <t>* Define process to address notifications from CSPs
 * Define cadence for review
 * Define exception criteria
 * Define thresholds to change
 * Combine with architecture analysis for SP &amp; RIs
 10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Process defined for new accounts and resources deployed
+* Train teams on process
+* Automate process
+10*Ceil(x/3)</t>
   </si>
   <si>
     <t>* Process for evaluating spot periodically
@@ -1566,9 +1563,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Overview!$A$12:$A$32</c:f>
+              <c:f>Overview!$A$12:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>Allocation</c:v>
                 </c:pt>
@@ -1576,10 +1573,10 @@
                   <c:v>Anomaly Management</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Architecting for Cloud</c:v>
+                  <c:v>Architecting &amp; Workload Placement</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Benchmarking</c:v>
+                  <c:v>Automation, Tools &amp; Services</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Budgeting</c:v>
@@ -1597,50 +1594,47 @@
                   <c:v>FinOps Practice Operations</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>FinOps Tools &amp; Services</c:v>
+                  <c:v>Forecasting</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Forecasting</c:v>
+                  <c:v>Intersecting Disciplines</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Intersecting Disciplines</c:v>
+                  <c:v>Invoicing &amp; Chargeback</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Invoicing &amp; Chargeback</c:v>
+                  <c:v>KPIs &amp; Benchmarking</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Licensing &amp; SaaS</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Onboarding Workloads</c:v>
+                  <c:v>Planning &amp; Estimating</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Planning &amp; Estimating</c:v>
+                  <c:v>Policy</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>Policy</c:v>
+                  <c:v>Rate Optimization</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>Rate Optimization</c:v>
+                  <c:v>Reporting &amp; Analytics</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>Reporting &amp; Analytics</c:v>
+                  <c:v>Unit Economics</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>Unit Economics</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Workload Optimization</c:v>
+                  <c:v>Usage Optimization</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Overview!$U$12:$U$32</c:f>
+              <c:f>Overview!$U$12:$U$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1699,9 +1693,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1873,7 +1864,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A11:B32" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A11:B31" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Capability"/>
     <tableColumn id="2" name="Action Count"/>
@@ -2167,10 +2158,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
@@ -2232,7 +2223,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="U6">
         <f>SUMIF(Scoring!I2:I130,A6,Scoring!H2:H130)/SUMIF(Scoring!I2:I130,A6,Scoring!E2:E130)</f>
@@ -2256,7 +2247,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="U8">
         <f>SUMIF(Scoring!I2:I130,A8,Scoring!H2:H130)/SUMIF(Scoring!I2:I130,A8,Scoring!E2:E130)</f>
@@ -2306,7 +2297,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U14">
         <f>SUMIF(Scoring!J2:J130,A14,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A14,Scoring!E2:E130)</f>
@@ -2318,7 +2309,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <f>SUMIF(Scoring!J2:J130,A15,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A15,Scoring!E2:E130)</f>
@@ -2390,7 +2381,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <f>SUMIF(Scoring!J2:J130,A21,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A21,Scoring!E2:E130)</f>
@@ -2450,7 +2441,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <f>SUMIF(Scoring!J2:J130,A26,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A26,Scoring!E2:E130)</f>
@@ -2462,7 +2453,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <f>SUMIF(Scoring!J2:J130,A27,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A27,Scoring!E2:E130)</f>
@@ -2474,7 +2465,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <f>SUMIF(Scoring!J2:J130,A28,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A28,Scoring!E2:E130)</f>
@@ -2486,7 +2477,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <f>SUMIF(Scoring!J2:J130,A29,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A29,Scoring!E2:E130)</f>
@@ -2498,7 +2489,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <f>SUMIF(Scoring!J2:J130,A30,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A30,Scoring!E2:E130)</f>
@@ -2518,20 +2509,8 @@
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
       <c r="B32">
-        <v>6</v>
-      </c>
-      <c r="U32">
-        <f>SUMIF(Scoring!J2:J130,A32,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A32,Scoring!E2:E130)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33">
-        <f>SUM(Overview!$B$12:$B$32)</f>
+        <f>SUM(Overview!$B$12:$B$31)</f>
         <v>0</v>
       </c>
     </row>
@@ -2552,7 +2531,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -2560,43 +2539,43 @@
     <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.5703125" hidden="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.42578125" hidden="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.28515625" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.42578125" hidden="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="D1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2607,19 +2586,19 @@
         <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H2">
         <f>E2*VALUE(LEFT(G2, FIND(":", G2)-1))</f>
@@ -2636,19 +2615,19 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H3">
         <f>E3*VALUE(LEFT(G3, FIND(":", G3)-1))</f>
@@ -2665,19 +2644,19 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H4">
         <f>E4*VALUE(LEFT(G4, FIND(":", G4)-1))</f>
@@ -2694,19 +2673,19 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H5">
         <f>E5*VALUE(LEFT(G5, FIND(":", G5)-1))</f>
@@ -2723,19 +2702,19 @@
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H6">
         <f>E6*VALUE(LEFT(G6, FIND(":", G6)-1))</f>
@@ -2754,19 +2733,19 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H7">
         <f>E7*VALUE(LEFT(G7, FIND(":", G7)-1))</f>
@@ -2783,19 +2762,19 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H8">
         <f>E8*VALUE(LEFT(G8, FIND(":", G8)-1))</f>
@@ -2812,19 +2791,19 @@
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H9">
         <f>E9*VALUE(LEFT(G9, FIND(":", G9)-1))</f>
@@ -2841,19 +2820,19 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H10">
         <f>E10*VALUE(LEFT(G10, FIND(":", G10)-1))</f>
@@ -2870,19 +2849,19 @@
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H11">
         <f>E11*VALUE(LEFT(G11, FIND(":", G11)-1))</f>
@@ -2901,19 +2880,19 @@
         <v>19</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E12" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H12">
         <f>E12*VALUE(LEFT(G12, FIND(":", G12)-1))</f>
@@ -2930,19 +2909,19 @@
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H13">
         <f>E13*VALUE(LEFT(G13, FIND(":", G13)-1))</f>
@@ -2959,19 +2938,19 @@
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H14">
         <f>E14*VALUE(LEFT(G14, FIND(":", G14)-1))</f>
@@ -2988,19 +2967,19 @@
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H15">
         <f>E15*VALUE(LEFT(G15, FIND(":", G15)-1))</f>
@@ -3017,19 +2996,19 @@
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H16">
         <f>E16*VALUE(LEFT(G16, FIND(":", G16)-1))</f>
@@ -3046,19 +3025,19 @@
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E17" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H17">
         <f>E17*VALUE(LEFT(G17, FIND(":", G17)-1))</f>
@@ -3074,22 +3053,22 @@
     <row r="18" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E18" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H18">
         <f>E18*VALUE(LEFT(G18, FIND(":", G18)-1))</f>
@@ -3099,26 +3078,26 @@
         <v>7</v>
       </c>
       <c r="K18" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F19" s="1">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H19">
         <f>E19*VALUE(LEFT(G19, FIND(":", G19)-1))</f>
@@ -3128,26 +3107,26 @@
         <v>7</v>
       </c>
       <c r="K19" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H20">
         <f>E20*VALUE(LEFT(G20, FIND(":", G20)-1))</f>
@@ -3157,26 +3136,26 @@
         <v>7</v>
       </c>
       <c r="K20" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H21">
         <f>E21*VALUE(LEFT(G21, FIND(":", G21)-1))</f>
@@ -3186,26 +3165,26 @@
         <v>7</v>
       </c>
       <c r="K21" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E22" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H22">
         <f>E22*VALUE(LEFT(G22, FIND(":", G22)-1))</f>
@@ -3215,28 +3194,28 @@
         <v>7</v>
       </c>
       <c r="K22" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E23" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H23">
         <f>E23*VALUE(LEFT(G23, FIND(":", G23)-1))</f>
@@ -3246,26 +3225,26 @@
         <v>7</v>
       </c>
       <c r="K23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E24" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H24">
         <f>E24*VALUE(LEFT(G24, FIND(":", G24)-1))</f>
@@ -3275,26 +3254,26 @@
         <v>7</v>
       </c>
       <c r="K24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E25" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H25">
         <f>E25*VALUE(LEFT(G25, FIND(":", G25)-1))</f>
@@ -3304,26 +3283,26 @@
         <v>7</v>
       </c>
       <c r="K25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E26" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H26">
         <f>E26*VALUE(LEFT(G26, FIND(":", G26)-1))</f>
@@ -3333,26 +3312,26 @@
         <v>7</v>
       </c>
       <c r="K26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E27" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H27">
         <f>E27*VALUE(LEFT(G27, FIND(":", G27)-1))</f>
@@ -3362,26 +3341,26 @@
         <v>7</v>
       </c>
       <c r="K27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E28" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H28">
         <f>E28*VALUE(LEFT(G28, FIND(":", G28)-1))</f>
@@ -3391,28 +3370,28 @@
         <v>7</v>
       </c>
       <c r="K28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E29" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H29">
         <f>E29*VALUE(LEFT(G29, FIND(":", G29)-1))</f>
@@ -3422,26 +3401,26 @@
         <v>7</v>
       </c>
       <c r="K29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E30" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H30">
         <f>E30*VALUE(LEFT(G30, FIND(":", G30)-1))</f>
@@ -3451,26 +3430,26 @@
         <v>7</v>
       </c>
       <c r="K30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E31" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F31" s="1">
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H31">
         <f>E31*VALUE(LEFT(G31, FIND(":", G31)-1))</f>
@@ -3480,26 +3459,26 @@
         <v>7</v>
       </c>
       <c r="K31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E32" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H32">
         <f>E32*VALUE(LEFT(G32, FIND(":", G32)-1))</f>
@@ -3509,26 +3488,26 @@
         <v>7</v>
       </c>
       <c r="K32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E33" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H33">
         <f>E33*VALUE(LEFT(G33, FIND(":", G33)-1))</f>
@@ -3538,26 +3517,26 @@
         <v>7</v>
       </c>
       <c r="K33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E34" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F34" s="1">
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H34">
         <f>E34*VALUE(LEFT(G34, FIND(":", G34)-1))</f>
@@ -3567,206 +3546,204 @@
         <v>7</v>
       </c>
       <c r="K34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="2"/>
+      <c r="A35" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="B35" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E35" t="s">
         <v>302</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H35">
         <f>E35*VALUE(LEFT(G35, FIND(":", G35)-1))</f>
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K35" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E36" t="s">
         <v>302</v>
       </c>
       <c r="F36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H36">
         <f>E36*VALUE(LEFT(G36, FIND(":", G36)-1))</f>
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K36" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F37" s="1">
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H37">
         <f>E37*VALUE(LEFT(G37, FIND(":", G37)-1))</f>
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K37" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E38" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H38">
         <f>E38*VALUE(LEFT(G38, FIND(":", G38)-1))</f>
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K38" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E39" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H39">
         <f>E39*VALUE(LEFT(G39, FIND(":", G39)-1))</f>
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K39" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E40" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H40">
         <f>E40*VALUE(LEFT(G40, FIND(":", G40)-1))</f>
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K40" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
       <c r="C41" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E41" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="H41">
         <f>E41*VALUE(LEFT(G41, FIND(":", G41)-1))</f>
@@ -3783,16 +3760,16 @@
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E42" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>368</v>
@@ -3812,19 +3789,19 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E43" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F43" s="1">
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="H43">
         <f>E43*VALUE(LEFT(G43, FIND(":", G43)-1))</f>
@@ -3841,19 +3818,19 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H44">
         <f>E44*VALUE(LEFT(G44, FIND(":", G44)-1))</f>
@@ -3870,19 +3847,19 @@
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E45" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H45">
         <f>E45*VALUE(LEFT(G45, FIND(":", G45)-1))</f>
@@ -3899,19 +3876,19 @@
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E46" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H46">
         <f>E46*VALUE(LEFT(G46, FIND(":", G46)-1))</f>
@@ -3930,19 +3907,19 @@
         <v>24</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E47" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H47">
         <f>E47*VALUE(LEFT(G47, FIND(":", G47)-1))</f>
@@ -3959,19 +3936,19 @@
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E48" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H48">
         <f>E48*VALUE(LEFT(G48, FIND(":", G48)-1))</f>
@@ -3988,19 +3965,19 @@
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E49" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H49">
         <f>E49*VALUE(LEFT(G49, FIND(":", G49)-1))</f>
@@ -4017,19 +3994,19 @@
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E50" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F50" s="1">
         <v>1</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H50">
         <f>E50*VALUE(LEFT(G50, FIND(":", G50)-1))</f>
@@ -4046,19 +4023,19 @@
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E51" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H51">
         <f>E51*VALUE(LEFT(G51, FIND(":", G51)-1))</f>
@@ -4075,19 +4052,19 @@
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H52">
         <f>E52*VALUE(LEFT(G52, FIND(":", G52)-1))</f>
@@ -4103,22 +4080,22 @@
     <row r="53" spans="1:11">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E53" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F53" s="1">
         <v>1</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H53">
         <f>E53*VALUE(LEFT(G53, FIND(":", G53)-1))</f>
@@ -4128,26 +4105,26 @@
         <v>9</v>
       </c>
       <c r="K53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E54" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F54" s="1">
         <v>1</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H54">
         <f>E54*VALUE(LEFT(G54, FIND(":", G54)-1))</f>
@@ -4157,26 +4134,26 @@
         <v>9</v>
       </c>
       <c r="K54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E55" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H55">
         <f>E55*VALUE(LEFT(G55, FIND(":", G55)-1))</f>
@@ -4186,26 +4163,26 @@
         <v>9</v>
       </c>
       <c r="K55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E56" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H56">
         <f>E56*VALUE(LEFT(G56, FIND(":", G56)-1))</f>
@@ -4215,26 +4192,26 @@
         <v>9</v>
       </c>
       <c r="K56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E57" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H57">
         <f>E57*VALUE(LEFT(G57, FIND(":", G57)-1))</f>
@@ -4244,26 +4221,26 @@
         <v>9</v>
       </c>
       <c r="K57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E58" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F58" s="1">
         <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H58">
         <f>E58*VALUE(LEFT(G58, FIND(":", G58)-1))</f>
@@ -4273,28 +4250,28 @@
         <v>9</v>
       </c>
       <c r="K58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E59" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H59">
         <f>E59*VALUE(LEFT(G59, FIND(":", G59)-1))</f>
@@ -4304,26 +4281,26 @@
         <v>9</v>
       </c>
       <c r="K59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E60" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F60" s="1">
         <v>1</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H60">
         <f>E60*VALUE(LEFT(G60, FIND(":", G60)-1))</f>
@@ -4333,26 +4310,26 @@
         <v>9</v>
       </c>
       <c r="K60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E61" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F61" s="1">
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H61">
         <f>E61*VALUE(LEFT(G61, FIND(":", G61)-1))</f>
@@ -4362,26 +4339,26 @@
         <v>9</v>
       </c>
       <c r="K61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E62" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H62">
         <f>E62*VALUE(LEFT(G62, FIND(":", G62)-1))</f>
@@ -4391,26 +4368,26 @@
         <v>9</v>
       </c>
       <c r="K62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E63" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H63">
         <f>E63*VALUE(LEFT(G63, FIND(":", G63)-1))</f>
@@ -4420,26 +4397,26 @@
         <v>9</v>
       </c>
       <c r="K63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E64" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H64">
         <f>E64*VALUE(LEFT(G64, FIND(":", G64)-1))</f>
@@ -4449,7 +4426,7 @@
         <v>9</v>
       </c>
       <c r="K64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -4458,19 +4435,19 @@
         <v>11</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E65" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F65" s="1">
         <v>1</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H65">
         <f>E65*VALUE(LEFT(G65, FIND(":", G65)-1))</f>
@@ -4487,19 +4464,19 @@
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E66" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F66" s="1">
         <v>1</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H66">
         <f>E66*VALUE(LEFT(G66, FIND(":", G66)-1))</f>
@@ -4516,19 +4493,19 @@
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E67" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F67" s="1">
         <v>1</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H67">
         <f>E67*VALUE(LEFT(G67, FIND(":", G67)-1))</f>
@@ -4545,19 +4522,19 @@
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E68" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F68" s="1">
         <v>1</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H68">
         <f>E68*VALUE(LEFT(G68, FIND(":", G68)-1))</f>
@@ -4574,19 +4551,19 @@
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E69" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F69" s="1">
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H69">
         <f>E69*VALUE(LEFT(G69, FIND(":", G69)-1))</f>
@@ -4603,19 +4580,19 @@
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E70" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F70" s="1">
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H70">
         <f>E70*VALUE(LEFT(G70, FIND(":", G70)-1))</f>
@@ -4632,19 +4609,19 @@
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E71" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H71">
         <f>E71*VALUE(LEFT(G71, FIND(":", G71)-1))</f>
@@ -4663,19 +4640,19 @@
         <v>12</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E72" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F72" s="1">
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H72">
         <f>E72*VALUE(LEFT(G72, FIND(":", G72)-1))</f>
@@ -4692,19 +4669,19 @@
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E73" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F73" s="1">
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H73">
         <f>E73*VALUE(LEFT(G73, FIND(":", G73)-1))</f>
@@ -4721,19 +4698,19 @@
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F74" s="1">
         <v>1</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H74">
         <f>E74*VALUE(LEFT(G74, FIND(":", G74)-1))</f>
@@ -4750,19 +4727,19 @@
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E75" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H75">
         <f>E75*VALUE(LEFT(G75, FIND(":", G75)-1))</f>
@@ -4779,19 +4756,19 @@
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E76" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H76">
         <f>E76*VALUE(LEFT(G76, FIND(":", G76)-1))</f>
@@ -4808,19 +4785,19 @@
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E77" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F77" s="1">
         <v>1</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H77">
         <f>E77*VALUE(LEFT(G77, FIND(":", G77)-1))</f>
@@ -4837,19 +4814,19 @@
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E78" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H78">
         <f>E78*VALUE(LEFT(G78, FIND(":", G78)-1))</f>
@@ -4868,19 +4845,19 @@
         <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E79" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H79">
         <f>E79*VALUE(LEFT(G79, FIND(":", G79)-1))</f>
@@ -4897,19 +4874,19 @@
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E80" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H80">
         <f>E80*VALUE(LEFT(G80, FIND(":", G80)-1))</f>
@@ -4926,19 +4903,19 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E81" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H81">
         <f>E81*VALUE(LEFT(G81, FIND(":", G81)-1))</f>
@@ -4955,19 +4932,19 @@
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F82" s="1">
         <v>1</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H82">
         <f>E82*VALUE(LEFT(G82, FIND(":", G82)-1))</f>
@@ -4984,19 +4961,19 @@
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E83" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H83">
         <f>E83*VALUE(LEFT(G83, FIND(":", G83)-1))</f>
@@ -5013,19 +4990,19 @@
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E84" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F84" s="1">
         <v>1</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H84">
         <f>E84*VALUE(LEFT(G84, FIND(":", G84)-1))</f>
@@ -5042,19 +5019,19 @@
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E85" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F85" s="1">
         <v>1</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H85">
         <f>E85*VALUE(LEFT(G85, FIND(":", G85)-1))</f>
@@ -5071,19 +5048,19 @@
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E86" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H86">
         <f>E86*VALUE(LEFT(G86, FIND(":", G86)-1))</f>
@@ -5100,19 +5077,19 @@
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E87" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F87" s="1">
         <v>1</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H87">
         <f>E87*VALUE(LEFT(G87, FIND(":", G87)-1))</f>
@@ -5128,22 +5105,22 @@
     <row r="88" spans="1:11">
       <c r="A88" s="2"/>
       <c r="B88" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E88" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H88">
         <f>E88*VALUE(LEFT(G88, FIND(":", G88)-1))</f>
@@ -5153,26 +5130,26 @@
         <v>9</v>
       </c>
       <c r="K88" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E89" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F89" s="1">
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H89">
         <f>E89*VALUE(LEFT(G89, FIND(":", G89)-1))</f>
@@ -5182,26 +5159,26 @@
         <v>9</v>
       </c>
       <c r="K89" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E90" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F90" s="1">
         <v>1</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H90">
         <f>E90*VALUE(LEFT(G90, FIND(":", G90)-1))</f>
@@ -5211,26 +5188,26 @@
         <v>9</v>
       </c>
       <c r="K90" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E91" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H91">
         <f>E91*VALUE(LEFT(G91, FIND(":", G91)-1))</f>
@@ -5240,26 +5217,26 @@
         <v>9</v>
       </c>
       <c r="K91" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E92" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F92" s="1">
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H92">
         <f>E92*VALUE(LEFT(G92, FIND(":", G92)-1))</f>
@@ -5269,26 +5246,26 @@
         <v>9</v>
       </c>
       <c r="K92" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E93" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H93">
         <f>E93*VALUE(LEFT(G93, FIND(":", G93)-1))</f>
@@ -5298,26 +5275,26 @@
         <v>9</v>
       </c>
       <c r="K93" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E94" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H94">
         <f>E94*VALUE(LEFT(G94, FIND(":", G94)-1))</f>
@@ -5327,7 +5304,7 @@
         <v>9</v>
       </c>
       <c r="K94" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -5335,22 +5312,22 @@
         <v>8</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E95" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H95">
         <f>E95*VALUE(LEFT(G95, FIND(":", G95)-1))</f>
@@ -5360,26 +5337,26 @@
         <v>8</v>
       </c>
       <c r="K95" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E96" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F96" s="1">
         <v>0</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H96">
         <f>E96*VALUE(LEFT(G96, FIND(":", G96)-1))</f>
@@ -5389,26 +5366,26 @@
         <v>8</v>
       </c>
       <c r="K96" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E97" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H97">
         <f>E97*VALUE(LEFT(G97, FIND(":", G97)-1))</f>
@@ -5418,26 +5395,26 @@
         <v>8</v>
       </c>
       <c r="K97" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E98" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H98">
         <f>E98*VALUE(LEFT(G98, FIND(":", G98)-1))</f>
@@ -5447,26 +5424,26 @@
         <v>8</v>
       </c>
       <c r="K98" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E99" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F99" s="1">
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H99">
         <f>E99*VALUE(LEFT(G99, FIND(":", G99)-1))</f>
@@ -5476,26 +5453,26 @@
         <v>8</v>
       </c>
       <c r="K99" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H100">
         <f>E100*VALUE(LEFT(G100, FIND(":", G100)-1))</f>
@@ -5505,7 +5482,7 @@
         <v>8</v>
       </c>
       <c r="K100" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -5514,19 +5491,19 @@
         <v>15</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E101" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F101" s="1">
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H101">
         <f>E101*VALUE(LEFT(G101, FIND(":", G101)-1))</f>
@@ -5543,19 +5520,19 @@
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E102" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F102" s="1">
         <v>1</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H102">
         <f>E102*VALUE(LEFT(G102, FIND(":", G102)-1))</f>
@@ -5572,19 +5549,19 @@
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E103" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H103">
         <f>E103*VALUE(LEFT(G103, FIND(":", G103)-1))</f>
@@ -5601,19 +5578,19 @@
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E104" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H104">
         <f>E104*VALUE(LEFT(G104, FIND(":", G104)-1))</f>
@@ -5630,19 +5607,19 @@
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E105" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H105">
         <f>E105*VALUE(LEFT(G105, FIND(":", G105)-1))</f>
@@ -5659,19 +5636,19 @@
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E106" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H106">
         <f>E106*VALUE(LEFT(G106, FIND(":", G106)-1))</f>
@@ -5687,22 +5664,22 @@
     <row r="107" spans="1:11">
       <c r="A107" s="2"/>
       <c r="B107" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E107" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H107">
         <f>E107*VALUE(LEFT(G107, FIND(":", G107)-1))</f>
@@ -5712,26 +5689,26 @@
         <v>8</v>
       </c>
       <c r="K107" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E108" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F108" s="1">
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H108">
         <f>E108*VALUE(LEFT(G108, FIND(":", G108)-1))</f>
@@ -5741,26 +5718,26 @@
         <v>8</v>
       </c>
       <c r="K108" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E109" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F109" s="1">
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H109">
         <f>E109*VALUE(LEFT(G109, FIND(":", G109)-1))</f>
@@ -5770,26 +5747,26 @@
         <v>8</v>
       </c>
       <c r="K109" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E110" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H110">
         <f>E110*VALUE(LEFT(G110, FIND(":", G110)-1))</f>
@@ -5799,26 +5776,26 @@
         <v>8</v>
       </c>
       <c r="K110" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E111" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F111" s="1">
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H111">
         <f>E111*VALUE(LEFT(G111, FIND(":", G111)-1))</f>
@@ -5828,26 +5805,26 @@
         <v>8</v>
       </c>
       <c r="K111" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E112" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F112" s="1">
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H112">
         <f>E112*VALUE(LEFT(G112, FIND(":", G112)-1))</f>
@@ -5857,28 +5834,28 @@
         <v>8</v>
       </c>
       <c r="K112" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="2"/>
       <c r="B113" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E113" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F113" s="1">
         <v>1</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H113">
         <f>E113*VALUE(LEFT(G113, FIND(":", G113)-1))</f>
@@ -5888,26 +5865,26 @@
         <v>8</v>
       </c>
       <c r="K113" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E114" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F114" s="1">
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H114">
         <f>E114*VALUE(LEFT(G114, FIND(":", G114)-1))</f>
@@ -5917,26 +5894,26 @@
         <v>8</v>
       </c>
       <c r="K114" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E115" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F115" s="1">
         <v>1</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H115">
         <f>E115*VALUE(LEFT(G115, FIND(":", G115)-1))</f>
@@ -5946,26 +5923,26 @@
         <v>8</v>
       </c>
       <c r="K115" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E116" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F116" s="1">
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H116">
         <f>E116*VALUE(LEFT(G116, FIND(":", G116)-1))</f>
@@ -5975,26 +5952,26 @@
         <v>8</v>
       </c>
       <c r="K116" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E117" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F117" s="1">
         <v>1</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H117">
         <f>E117*VALUE(LEFT(G117, FIND(":", G117)-1))</f>
@@ -6004,26 +5981,26 @@
         <v>8</v>
       </c>
       <c r="K117" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E118" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F118" s="1">
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H118">
         <f>E118*VALUE(LEFT(G118, FIND(":", G118)-1))</f>
@@ -6033,26 +6010,26 @@
         <v>8</v>
       </c>
       <c r="K118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E119" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F119" s="1">
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H119">
         <f>E119*VALUE(LEFT(G119, FIND(":", G119)-1))</f>
@@ -6062,28 +6039,28 @@
         <v>8</v>
       </c>
       <c r="K119" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="2"/>
       <c r="B120" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E120" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F120" s="1">
         <v>1</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H120">
         <f>E120*VALUE(LEFT(G120, FIND(":", G120)-1))</f>
@@ -6093,26 +6070,26 @@
         <v>8</v>
       </c>
       <c r="K120" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E121" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F121" s="1">
         <v>0</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H121">
         <f>E121*VALUE(LEFT(G121, FIND(":", G121)-1))</f>
@@ -6122,26 +6099,26 @@
         <v>8</v>
       </c>
       <c r="K121" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E122" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F122" s="1">
         <v>0</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H122">
         <f>E122*VALUE(LEFT(G122, FIND(":", G122)-1))</f>
@@ -6151,26 +6128,26 @@
         <v>8</v>
       </c>
       <c r="K122" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E123" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H123">
         <f>E123*VALUE(LEFT(G123, FIND(":", G123)-1))</f>
@@ -6180,26 +6157,26 @@
         <v>8</v>
       </c>
       <c r="K123" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F124" s="1">
         <v>0</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H124">
         <f>E124*VALUE(LEFT(G124, FIND(":", G124)-1))</f>
@@ -6209,26 +6186,26 @@
         <v>8</v>
       </c>
       <c r="K124" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H125">
         <f>E125*VALUE(LEFT(G125, FIND(":", G125)-1))</f>
@@ -6238,7 +6215,7 @@
         <v>8</v>
       </c>
       <c r="K125" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -6246,22 +6223,22 @@
         <v>6</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E126" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H126">
         <f>E126*VALUE(LEFT(G126, FIND(":", G126)-1))</f>
@@ -6271,26 +6248,26 @@
         <v>6</v>
       </c>
       <c r="K126" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E127" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H127">
         <f>E127*VALUE(LEFT(G127, FIND(":", G127)-1))</f>
@@ -6300,26 +6277,26 @@
         <v>6</v>
       </c>
       <c r="K127" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E128" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H128">
         <f>E128*VALUE(LEFT(G128, FIND(":", G128)-1))</f>
@@ -6329,26 +6306,26 @@
         <v>6</v>
       </c>
       <c r="K128" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E129" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F129" s="1">
         <v>1</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H129">
         <f>E129*VALUE(LEFT(G129, FIND(":", G129)-1))</f>
@@ -6358,26 +6335,26 @@
         <v>6</v>
       </c>
       <c r="K129" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E130" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H130">
         <f>E130*VALUE(LEFT(G130, FIND(":", G130)-1))</f>
@@ -6387,13 +6364,13 @@
         <v>6</v>
       </c>
       <c r="K130" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A2:A40"/>
-    <mergeCell ref="A41:A94"/>
+  <mergeCells count="24">
+    <mergeCell ref="A2:A34"/>
+    <mergeCell ref="A35:A94"/>
     <mergeCell ref="A95:A125"/>
     <mergeCell ref="A126:A130"/>
     <mergeCell ref="B2:B6"/>
@@ -6402,8 +6379,7 @@
     <mergeCell ref="B18:B22"/>
     <mergeCell ref="B23:B28"/>
     <mergeCell ref="B29:B34"/>
-    <mergeCell ref="B35:B40"/>
-    <mergeCell ref="B41:B46"/>
+    <mergeCell ref="B35:B46"/>
     <mergeCell ref="B47:B52"/>
     <mergeCell ref="B53:B58"/>
     <mergeCell ref="B59:B64"/>
@@ -6519,31 +6495,31 @@
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G35">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G36">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G37">
+      <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G38">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G39">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G40">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G41">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G42">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G43">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G38">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G39">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G40">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G41">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G42">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G43">
-      <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G44">
       <formula1>"0: None"</formula1>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="382">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -926,6 +926,9 @@
   </si>
   <si>
     <t>1.7.0</t>
+  </si>
+  <si>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>1.5.0</t>
@@ -2183,14 +2186,14 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2">
-        <f>SUM(Scoring!E2:E130)</f>
+        <f>SUM(Scoring!F2:F130)</f>
         <v>0</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2">
-        <f>SUM(Scoring!H2:H130)/A2</f>
+        <f>SUM(Scoring!I2:I130)/A2</f>
         <v>0</v>
       </c>
       <c r="D2">
@@ -2214,7 +2217,7 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <f>SUMIF(Scoring!I2:I130,A5,Scoring!H2:H130)/SUMIF(Scoring!I2:I130,A5,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!J2:J130,A5,Scoring!I2:I130)/SUMIF(Scoring!J2:J130,A5,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2226,7 +2229,7 @@
         <v>33</v>
       </c>
       <c r="U6">
-        <f>SUMIF(Scoring!I2:I130,A6,Scoring!H2:H130)/SUMIF(Scoring!I2:I130,A6,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!J2:J130,A6,Scoring!I2:I130)/SUMIF(Scoring!J2:J130,A6,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2238,7 +2241,7 @@
         <v>31</v>
       </c>
       <c r="U7">
-        <f>SUMIF(Scoring!I2:I130,A7,Scoring!H2:H130)/SUMIF(Scoring!I2:I130,A7,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!J2:J130,A7,Scoring!I2:I130)/SUMIF(Scoring!J2:J130,A7,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2250,7 +2253,7 @@
         <v>60</v>
       </c>
       <c r="U8">
-        <f>SUMIF(Scoring!I2:I130,A8,Scoring!H2:H130)/SUMIF(Scoring!I2:I130,A8,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!J2:J130,A8,Scoring!I2:I130)/SUMIF(Scoring!J2:J130,A8,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2276,7 +2279,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <f>SUMIF(Scoring!J2:J130,A12,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A12,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A12,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A12,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2288,7 +2291,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <f>SUMIF(Scoring!J2:J130,A13,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A13,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A13,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A13,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2300,7 +2303,7 @@
         <v>12</v>
       </c>
       <c r="U14">
-        <f>SUMIF(Scoring!J2:J130,A14,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A14,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A14,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A14,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2312,7 +2315,7 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <f>SUMIF(Scoring!J2:J130,A15,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A15,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A15,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A15,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2324,7 +2327,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <f>SUMIF(Scoring!J2:J130,A16,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A16,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A16,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A16,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2336,7 +2339,7 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <f>SUMIF(Scoring!J2:J130,A17,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A17,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A17,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A17,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2348,7 +2351,7 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <f>SUMIF(Scoring!J2:J130,A18,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A18,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A18,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A18,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2360,7 +2363,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <f>SUMIF(Scoring!J2:J130,A19,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A19,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A19,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A19,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2372,7 +2375,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <f>SUMIF(Scoring!J2:J130,A20,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A20,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A20,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A20,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2384,7 +2387,7 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <f>SUMIF(Scoring!J2:J130,A21,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A21,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A21,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A21,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2396,7 +2399,7 @@
         <v>6</v>
       </c>
       <c r="U22">
-        <f>SUMIF(Scoring!J2:J130,A22,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A22,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A22,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A22,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2408,7 +2411,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <f>SUMIF(Scoring!J2:J130,A23,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A23,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A23,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A23,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2420,7 +2423,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <f>SUMIF(Scoring!J2:J130,A24,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A24,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A24,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A24,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2432,7 +2435,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <f>SUMIF(Scoring!J2:J130,A25,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A25,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A25,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A25,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2444,7 +2447,7 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <f>SUMIF(Scoring!J2:J130,A26,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A26,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A26,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A26,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2456,7 +2459,7 @@
         <v>5</v>
       </c>
       <c r="U27">
-        <f>SUMIF(Scoring!J2:J130,A27,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A27,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A27,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A27,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2468,7 +2471,7 @@
         <v>6</v>
       </c>
       <c r="U28">
-        <f>SUMIF(Scoring!J2:J130,A28,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A28,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A28,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A28,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2480,7 +2483,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <f>SUMIF(Scoring!J2:J130,A29,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A29,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A29,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A29,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2492,7 +2495,7 @@
         <v>6</v>
       </c>
       <c r="U30">
-        <f>SUMIF(Scoring!J2:J130,A30,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A30,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A30,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A30,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2504,7 +2507,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <f>SUMIF(Scoring!J2:J130,A31,Scoring!H2:H130)/SUMIF(Scoring!J2:J130,A31,Scoring!E2:E130)</f>
+        <f>SUMIF(Scoring!K2:K130,A31,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A31,Scoring!F2:F130)</f>
         <v>0</v>
       </c>
     </row>
@@ -2535,9 +2538,9 @@
     <col min="3" max="3" width="52.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="40.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="40.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.42578125" hidden="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="32.42578125" hidden="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="0" hidden="1" customWidth="1"/>
@@ -2594,14 +2597,17 @@
       <c r="E2" t="s">
         <v>300</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="H2">
-        <f>E2*VALUE(LEFT(G2, FIND(":", G2)-1))</f>
+        <v>305</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="I2">
+        <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
         <v>0</v>
       </c>
       <c r="J2" t="s">
@@ -2623,14 +2629,17 @@
       <c r="E3" t="s">
         <v>300</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H3">
-        <f>E3*VALUE(LEFT(G3, FIND(":", G3)-1))</f>
+        <v>306</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I3">
+        <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
         <v>0</v>
       </c>
       <c r="J3" t="s">
@@ -2652,14 +2661,17 @@
       <c r="E4" t="s">
         <v>300</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H4">
-        <f>E4*VALUE(LEFT(G4, FIND(":", G4)-1))</f>
+        <v>307</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I4">
+        <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
         <v>0</v>
       </c>
       <c r="J4" t="s">
@@ -2681,14 +2693,17 @@
       <c r="E5" t="s">
         <v>301</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H5">
-        <f>E5*VALUE(LEFT(G5, FIND(":", G5)-1))</f>
+        <v>308</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I5">
+        <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
         <v>0</v>
       </c>
       <c r="J5" t="s">
@@ -2710,14 +2725,17 @@
       <c r="E6" t="s">
         <v>301</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H6">
-        <f>E6*VALUE(LEFT(G6, FIND(":", G6)-1))</f>
+        <v>309</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I6">
+        <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
         <v>0</v>
       </c>
       <c r="J6" t="s">
@@ -2741,14 +2759,14 @@
       <c r="E7" t="s">
         <v>301</v>
       </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H7">
-        <f>E7*VALUE(LEFT(G7, FIND(":", G7)-1))</f>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I7">
+        <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
         <v>0</v>
       </c>
       <c r="J7" t="s">
@@ -2770,14 +2788,14 @@
       <c r="E8" t="s">
         <v>301</v>
       </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H8">
-        <f>E8*VALUE(LEFT(G8, FIND(":", G8)-1))</f>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I8">
+        <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
         <v>0</v>
       </c>
       <c r="J8" t="s">
@@ -2799,14 +2817,14 @@
       <c r="E9" t="s">
         <v>301</v>
       </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H9">
-        <f>E9*VALUE(LEFT(G9, FIND(":", G9)-1))</f>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I9">
+        <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
         <v>0</v>
       </c>
       <c r="J9" t="s">
@@ -2828,14 +2846,17 @@
       <c r="E10" t="s">
         <v>302</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H10">
-        <f>E10*VALUE(LEFT(G10, FIND(":", G10)-1))</f>
+        <v>310</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I10">
+        <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
         <v>0</v>
       </c>
       <c r="J10" t="s">
@@ -2857,14 +2878,14 @@
       <c r="E11" t="s">
         <v>301</v>
       </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H11">
-        <f>E11*VALUE(LEFT(G11, FIND(":", G11)-1))</f>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I11">
+        <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
         <v>0</v>
       </c>
       <c r="J11" t="s">
@@ -2888,14 +2909,14 @@
       <c r="E12" t="s">
         <v>302</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="H12">
-        <f>E12*VALUE(LEFT(G12, FIND(":", G12)-1))</f>
+      <c r="H12" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="I12">
+        <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
         <v>0</v>
       </c>
       <c r="J12" t="s">
@@ -2917,14 +2938,14 @@
       <c r="E13" t="s">
         <v>301</v>
       </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H13">
-        <f>E13*VALUE(LEFT(G13, FIND(":", G13)-1))</f>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I13">
+        <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
         <v>0</v>
       </c>
       <c r="J13" t="s">
@@ -2946,14 +2967,14 @@
       <c r="E14" t="s">
         <v>301</v>
       </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H14">
-        <f>E14*VALUE(LEFT(G14, FIND(":", G14)-1))</f>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I14">
+        <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
         <v>0</v>
       </c>
       <c r="J14" t="s">
@@ -2975,14 +2996,14 @@
       <c r="E15" t="s">
         <v>301</v>
       </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H15">
-        <f>E15*VALUE(LEFT(G15, FIND(":", G15)-1))</f>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I15">
+        <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
         <v>0</v>
       </c>
       <c r="J15" t="s">
@@ -3004,14 +3025,14 @@
       <c r="E16" t="s">
         <v>301</v>
       </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H16">
-        <f>E16*VALUE(LEFT(G16, FIND(":", G16)-1))</f>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I16">
+        <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
         <v>0</v>
       </c>
       <c r="J16" t="s">
@@ -3033,14 +3054,14 @@
       <c r="E17" t="s">
         <v>301</v>
       </c>
-      <c r="F17" s="1">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H17">
-        <f>E17*VALUE(LEFT(G17, FIND(":", G17)-1))</f>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I17">
+        <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
         <v>0</v>
       </c>
       <c r="J17" t="s">
@@ -3064,14 +3085,14 @@
       <c r="E18" t="s">
         <v>301</v>
       </c>
-      <c r="F18" s="1">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H18">
-        <f>E18*VALUE(LEFT(G18, FIND(":", G18)-1))</f>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I18">
+        <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
         <v>0</v>
       </c>
       <c r="J18" t="s">
@@ -3093,14 +3114,14 @@
       <c r="E19" t="s">
         <v>302</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19">
         <v>1</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="H19">
-        <f>E19*VALUE(LEFT(G19, FIND(":", G19)-1))</f>
+      <c r="H19" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="I19">
+        <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
         <v>0</v>
       </c>
       <c r="J19" t="s">
@@ -3122,14 +3143,14 @@
       <c r="E20" t="s">
         <v>301</v>
       </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H20">
-        <f>E20*VALUE(LEFT(G20, FIND(":", G20)-1))</f>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I20">
+        <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
         <v>0</v>
       </c>
       <c r="J20" t="s">
@@ -3151,14 +3172,17 @@
       <c r="E21" t="s">
         <v>302</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H21">
-        <f>E21*VALUE(LEFT(G21, FIND(":", G21)-1))</f>
+        <v>311</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I21">
+        <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
         <v>0</v>
       </c>
       <c r="J21" t="s">
@@ -3180,14 +3204,14 @@
       <c r="E22" t="s">
         <v>301</v>
       </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H22">
-        <f>E22*VALUE(LEFT(G22, FIND(":", G22)-1))</f>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I22">
+        <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
         <v>0</v>
       </c>
       <c r="J22" t="s">
@@ -3211,14 +3235,14 @@
       <c r="E23" t="s">
         <v>301</v>
       </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H23">
-        <f>E23*VALUE(LEFT(G23, FIND(":", G23)-1))</f>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I23">
+        <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
         <v>0</v>
       </c>
       <c r="J23" t="s">
@@ -3240,14 +3264,14 @@
       <c r="E24" t="s">
         <v>301</v>
       </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H24">
-        <f>E24*VALUE(LEFT(G24, FIND(":", G24)-1))</f>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I24">
+        <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
         <v>0</v>
       </c>
       <c r="J24" t="s">
@@ -3269,14 +3293,14 @@
       <c r="E25" t="s">
         <v>301</v>
       </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H25">
-        <f>E25*VALUE(LEFT(G25, FIND(":", G25)-1))</f>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I25">
+        <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
         <v>0</v>
       </c>
       <c r="J25" t="s">
@@ -3298,14 +3322,14 @@
       <c r="E26" t="s">
         <v>301</v>
       </c>
-      <c r="F26" s="1">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H26">
-        <f>E26*VALUE(LEFT(G26, FIND(":", G26)-1))</f>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I26">
+        <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
         <v>0</v>
       </c>
       <c r="J26" t="s">
@@ -3327,14 +3351,14 @@
       <c r="E27" t="s">
         <v>301</v>
       </c>
-      <c r="F27" s="1">
-        <v>0</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H27">
-        <f>E27*VALUE(LEFT(G27, FIND(":", G27)-1))</f>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I27">
+        <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
         <v>0</v>
       </c>
       <c r="J27" t="s">
@@ -3356,14 +3380,14 @@
       <c r="E28" t="s">
         <v>301</v>
       </c>
-      <c r="F28" s="1">
-        <v>0</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H28">
-        <f>E28*VALUE(LEFT(G28, FIND(":", G28)-1))</f>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I28">
+        <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
         <v>0</v>
       </c>
       <c r="J28" t="s">
@@ -3387,14 +3411,14 @@
       <c r="E29" t="s">
         <v>301</v>
       </c>
-      <c r="F29" s="1">
-        <v>0</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H29">
-        <f>E29*VALUE(LEFT(G29, FIND(":", G29)-1))</f>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I29">
+        <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
         <v>0</v>
       </c>
       <c r="J29" t="s">
@@ -3416,14 +3440,14 @@
       <c r="E30" t="s">
         <v>301</v>
       </c>
-      <c r="F30" s="1">
-        <v>0</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H30">
-        <f>E30*VALUE(LEFT(G30, FIND(":", G30)-1))</f>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I30">
+        <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
         <v>0</v>
       </c>
       <c r="J30" t="s">
@@ -3445,14 +3469,14 @@
       <c r="E31" t="s">
         <v>302</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31">
         <v>1</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="H31">
-        <f>E31*VALUE(LEFT(G31, FIND(":", G31)-1))</f>
+      <c r="H31" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="I31">
+        <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
         <v>0</v>
       </c>
       <c r="J31" t="s">
@@ -3474,14 +3498,14 @@
       <c r="E32" t="s">
         <v>301</v>
       </c>
-      <c r="F32" s="1">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H32">
-        <f>E32*VALUE(LEFT(G32, FIND(":", G32)-1))</f>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I32">
+        <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
         <v>0</v>
       </c>
       <c r="J32" t="s">
@@ -3503,14 +3527,14 @@
       <c r="E33" t="s">
         <v>301</v>
       </c>
-      <c r="F33" s="1">
-        <v>0</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H33">
-        <f>E33*VALUE(LEFT(G33, FIND(":", G33)-1))</f>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I33">
+        <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
         <v>0</v>
       </c>
       <c r="J33" t="s">
@@ -3532,14 +3556,14 @@
       <c r="E34" t="s">
         <v>302</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34">
         <v>1</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="H34">
-        <f>E34*VALUE(LEFT(G34, FIND(":", G34)-1))</f>
+      <c r="H34" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="I34">
+        <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
         <v>0</v>
       </c>
       <c r="J34" t="s">
@@ -3565,14 +3589,14 @@
       <c r="E35" t="s">
         <v>302</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35">
         <v>1</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="H35">
-        <f>E35*VALUE(LEFT(G35, FIND(":", G35)-1))</f>
+      <c r="H35" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="I35">
+        <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
         <v>0</v>
       </c>
       <c r="J35" t="s">
@@ -3594,14 +3618,17 @@
       <c r="E36" t="s">
         <v>302</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H36">
-        <f>E36*VALUE(LEFT(G36, FIND(":", G36)-1))</f>
+        <v>312</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I36">
+        <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
         <v>0</v>
       </c>
       <c r="J36" t="s">
@@ -3623,14 +3650,14 @@
       <c r="E37" t="s">
         <v>302</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37">
         <v>1</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="H37">
-        <f>E37*VALUE(LEFT(G37, FIND(":", G37)-1))</f>
+      <c r="H37" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="I37">
+        <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
         <v>0</v>
       </c>
       <c r="J37" t="s">
@@ -3652,14 +3679,14 @@
       <c r="E38" t="s">
         <v>301</v>
       </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H38">
-        <f>E38*VALUE(LEFT(G38, FIND(":", G38)-1))</f>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I38">
+        <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
         <v>0</v>
       </c>
       <c r="J38" t="s">
@@ -3681,14 +3708,14 @@
       <c r="E39" t="s">
         <v>301</v>
       </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H39">
-        <f>E39*VALUE(LEFT(G39, FIND(":", G39)-1))</f>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I39">
+        <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
         <v>0</v>
       </c>
       <c r="J39" t="s">
@@ -3710,14 +3737,14 @@
       <c r="E40" t="s">
         <v>301</v>
       </c>
-      <c r="F40" s="1">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H40">
-        <f>E40*VALUE(LEFT(G40, FIND(":", G40)-1))</f>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I40">
+        <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
         <v>0</v>
       </c>
       <c r="J40" t="s">
@@ -3739,14 +3766,14 @@
       <c r="E41" t="s">
         <v>301</v>
       </c>
-      <c r="F41" s="1">
-        <v>0</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H41">
-        <f>E41*VALUE(LEFT(G41, FIND(":", G41)-1))</f>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I41">
+        <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
         <v>0</v>
       </c>
       <c r="J41" t="s">
@@ -3768,14 +3795,14 @@
       <c r="E42" t="s">
         <v>301</v>
       </c>
-      <c r="F42" s="1">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H42">
-        <f>E42*VALUE(LEFT(G42, FIND(":", G42)-1))</f>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I42">
+        <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
         <v>0</v>
       </c>
       <c r="J42" t="s">
@@ -3797,14 +3824,17 @@
       <c r="E43" t="s">
         <v>302</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H43">
-        <f>E43*VALUE(LEFT(G43, FIND(":", G43)-1))</f>
+        <v>313</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I43">
+        <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
         <v>0</v>
       </c>
       <c r="J43" t="s">
@@ -3826,14 +3856,14 @@
       <c r="E44" t="s">
         <v>301</v>
       </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H44">
-        <f>E44*VALUE(LEFT(G44, FIND(":", G44)-1))</f>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I44">
+        <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
         <v>0</v>
       </c>
       <c r="J44" t="s">
@@ -3855,14 +3885,14 @@
       <c r="E45" t="s">
         <v>301</v>
       </c>
-      <c r="F45" s="1">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H45">
-        <f>E45*VALUE(LEFT(G45, FIND(":", G45)-1))</f>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I45">
+        <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
         <v>0</v>
       </c>
       <c r="J45" t="s">
@@ -3884,14 +3914,14 @@
       <c r="E46" t="s">
         <v>301</v>
       </c>
-      <c r="F46" s="1">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H46">
-        <f>E46*VALUE(LEFT(G46, FIND(":", G46)-1))</f>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I46">
+        <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
         <v>0</v>
       </c>
       <c r="J46" t="s">
@@ -3915,14 +3945,14 @@
       <c r="E47" t="s">
         <v>302</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47">
         <v>1</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="H47">
-        <f>E47*VALUE(LEFT(G47, FIND(":", G47)-1))</f>
+      <c r="H47" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I47">
+        <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
         <v>0</v>
       </c>
       <c r="J47" t="s">
@@ -3944,14 +3974,14 @@
       <c r="E48" t="s">
         <v>301</v>
       </c>
-      <c r="F48" s="1">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H48">
-        <f>E48*VALUE(LEFT(G48, FIND(":", G48)-1))</f>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I48">
+        <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
         <v>0</v>
       </c>
       <c r="J48" t="s">
@@ -3973,14 +4003,14 @@
       <c r="E49" t="s">
         <v>301</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H49">
-        <f>E49*VALUE(LEFT(G49, FIND(":", G49)-1))</f>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I49">
+        <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
         <v>0</v>
       </c>
       <c r="J49" t="s">
@@ -4002,14 +4032,14 @@
       <c r="E50" t="s">
         <v>302</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50">
         <v>1</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="H50">
-        <f>E50*VALUE(LEFT(G50, FIND(":", G50)-1))</f>
+      <c r="H50" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="I50">
+        <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
         <v>0</v>
       </c>
       <c r="J50" t="s">
@@ -4031,14 +4061,14 @@
       <c r="E51" t="s">
         <v>301</v>
       </c>
-      <c r="F51" s="1">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H51">
-        <f>E51*VALUE(LEFT(G51, FIND(":", G51)-1))</f>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I51">
+        <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
         <v>0</v>
       </c>
       <c r="J51" t="s">
@@ -4060,14 +4090,14 @@
       <c r="E52" t="s">
         <v>301</v>
       </c>
-      <c r="F52" s="1">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H52">
-        <f>E52*VALUE(LEFT(G52, FIND(":", G52)-1))</f>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I52">
+        <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
         <v>0</v>
       </c>
       <c r="J52" t="s">
@@ -4091,14 +4121,14 @@
       <c r="E53" t="s">
         <v>302</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53">
         <v>1</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="H53">
-        <f>E53*VALUE(LEFT(G53, FIND(":", G53)-1))</f>
+      <c r="H53" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="I53">
+        <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
         <v>0</v>
       </c>
       <c r="J53" t="s">
@@ -4120,14 +4150,14 @@
       <c r="E54" t="s">
         <v>302</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54">
         <v>1</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="H54">
-        <f>E54*VALUE(LEFT(G54, FIND(":", G54)-1))</f>
+      <c r="H54" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="I54">
+        <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
         <v>0</v>
       </c>
       <c r="J54" t="s">
@@ -4149,14 +4179,14 @@
       <c r="E55" t="s">
         <v>301</v>
       </c>
-      <c r="F55" s="1">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H55">
-        <f>E55*VALUE(LEFT(G55, FIND(":", G55)-1))</f>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I55">
+        <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
         <v>0</v>
       </c>
       <c r="J55" t="s">
@@ -4178,14 +4208,14 @@
       <c r="E56" t="s">
         <v>301</v>
       </c>
-      <c r="F56" s="1">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H56">
-        <f>E56*VALUE(LEFT(G56, FIND(":", G56)-1))</f>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I56">
+        <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
         <v>0</v>
       </c>
       <c r="J56" t="s">
@@ -4207,14 +4237,14 @@
       <c r="E57" t="s">
         <v>301</v>
       </c>
-      <c r="F57" s="1">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H57">
-        <f>E57*VALUE(LEFT(G57, FIND(":", G57)-1))</f>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I57">
+        <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
         <v>0</v>
       </c>
       <c r="J57" t="s">
@@ -4236,14 +4266,17 @@
       <c r="E58" t="s">
         <v>302</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H58">
-        <f>E58*VALUE(LEFT(G58, FIND(":", G58)-1))</f>
+        <v>314</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I58">
+        <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
         <v>0</v>
       </c>
       <c r="J58" t="s">
@@ -4267,14 +4300,14 @@
       <c r="E59" t="s">
         <v>301</v>
       </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H59">
-        <f>E59*VALUE(LEFT(G59, FIND(":", G59)-1))</f>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I59">
+        <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
         <v>0</v>
       </c>
       <c r="J59" t="s">
@@ -4296,14 +4329,14 @@
       <c r="E60" t="s">
         <v>302</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60">
         <v>1</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="H60">
-        <f>E60*VALUE(LEFT(G60, FIND(":", G60)-1))</f>
+      <c r="H60" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="I60">
+        <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
         <v>0</v>
       </c>
       <c r="J60" t="s">
@@ -4325,14 +4358,14 @@
       <c r="E61" t="s">
         <v>302</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61">
         <v>1</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="H61">
-        <f>E61*VALUE(LEFT(G61, FIND(":", G61)-1))</f>
+      <c r="H61" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I61">
+        <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
         <v>0</v>
       </c>
       <c r="J61" t="s">
@@ -4354,14 +4387,14 @@
       <c r="E62" t="s">
         <v>301</v>
       </c>
-      <c r="F62" s="1">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H62">
-        <f>E62*VALUE(LEFT(G62, FIND(":", G62)-1))</f>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I62">
+        <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
         <v>0</v>
       </c>
       <c r="J62" t="s">
@@ -4383,14 +4416,14 @@
       <c r="E63" t="s">
         <v>301</v>
       </c>
-      <c r="F63" s="1">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H63">
-        <f>E63*VALUE(LEFT(G63, FIND(":", G63)-1))</f>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I63">
+        <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
         <v>0</v>
       </c>
       <c r="J63" t="s">
@@ -4412,14 +4445,14 @@
       <c r="E64" t="s">
         <v>301</v>
       </c>
-      <c r="F64" s="1">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H64">
-        <f>E64*VALUE(LEFT(G64, FIND(":", G64)-1))</f>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I64">
+        <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
         <v>0</v>
       </c>
       <c r="J64" t="s">
@@ -4443,14 +4476,17 @@
       <c r="E65" t="s">
         <v>302</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65">
         <v>1</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H65">
-        <f>E65*VALUE(LEFT(G65, FIND(":", G65)-1))</f>
+        <v>315</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I65">
+        <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
         <v>0</v>
       </c>
       <c r="J65" t="s">
@@ -4472,14 +4508,17 @@
       <c r="E66" t="s">
         <v>302</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="H66">
-        <f>E66*VALUE(LEFT(G66, FIND(":", G66)-1))</f>
+        <v>316</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I66">
+        <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
         <v>0</v>
       </c>
       <c r="J66" t="s">
@@ -4501,14 +4540,17 @@
       <c r="E67" t="s">
         <v>302</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67">
         <v>1</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H67">
-        <f>E67*VALUE(LEFT(G67, FIND(":", G67)-1))</f>
+        <v>317</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I67">
+        <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
         <v>0</v>
       </c>
       <c r="J67" t="s">
@@ -4530,14 +4572,17 @@
       <c r="E68" t="s">
         <v>302</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="H68">
-        <f>E68*VALUE(LEFT(G68, FIND(":", G68)-1))</f>
+        <v>318</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I68">
+        <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
         <v>0</v>
       </c>
       <c r="J68" t="s">
@@ -4559,14 +4604,17 @@
       <c r="E69" t="s">
         <v>302</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="H69">
-        <f>E69*VALUE(LEFT(G69, FIND(":", G69)-1))</f>
+        <v>319</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I69">
+        <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
         <v>0</v>
       </c>
       <c r="J69" t="s">
@@ -4588,14 +4636,17 @@
       <c r="E70" t="s">
         <v>302</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H70">
-        <f>E70*VALUE(LEFT(G70, FIND(":", G70)-1))</f>
+        <v>320</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I70">
+        <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
         <v>0</v>
       </c>
       <c r="J70" t="s">
@@ -4617,14 +4668,14 @@
       <c r="E71" t="s">
         <v>301</v>
       </c>
-      <c r="F71" s="1">
-        <v>0</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H71">
-        <f>E71*VALUE(LEFT(G71, FIND(":", G71)-1))</f>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I71">
+        <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
         <v>0</v>
       </c>
       <c r="J71" t="s">
@@ -4648,14 +4699,17 @@
       <c r="E72" t="s">
         <v>302</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H72">
-        <f>E72*VALUE(LEFT(G72, FIND(":", G72)-1))</f>
+        <v>321</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I72">
+        <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
         <v>0</v>
       </c>
       <c r="J72" t="s">
@@ -4677,14 +4731,17 @@
       <c r="E73" t="s">
         <v>302</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H73">
-        <f>E73*VALUE(LEFT(G73, FIND(":", G73)-1))</f>
+        <v>322</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I73">
+        <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
         <v>0</v>
       </c>
       <c r="J73" t="s">
@@ -4706,14 +4763,14 @@
       <c r="E74" t="s">
         <v>302</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74">
         <v>1</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="H74">
-        <f>E74*VALUE(LEFT(G74, FIND(":", G74)-1))</f>
+      <c r="H74" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="I74">
+        <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
         <v>0</v>
       </c>
       <c r="J74" t="s">
@@ -4735,14 +4792,14 @@
       <c r="E75" t="s">
         <v>301</v>
       </c>
-      <c r="F75" s="1">
-        <v>0</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H75">
-        <f>E75*VALUE(LEFT(G75, FIND(":", G75)-1))</f>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I75">
+        <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
         <v>0</v>
       </c>
       <c r="J75" t="s">
@@ -4764,14 +4821,14 @@
       <c r="E76" t="s">
         <v>301</v>
       </c>
-      <c r="F76" s="1">
-        <v>0</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H76">
-        <f>E76*VALUE(LEFT(G76, FIND(":", G76)-1))</f>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I76">
+        <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
         <v>0</v>
       </c>
       <c r="J76" t="s">
@@ -4793,14 +4850,17 @@
       <c r="E77" t="s">
         <v>302</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H77">
-        <f>E77*VALUE(LEFT(G77, FIND(":", G77)-1))</f>
+        <v>323</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I77">
+        <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
         <v>0</v>
       </c>
       <c r="J77" t="s">
@@ -4822,14 +4882,14 @@
       <c r="E78" t="s">
         <v>301</v>
       </c>
-      <c r="F78" s="1">
-        <v>0</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H78">
-        <f>E78*VALUE(LEFT(G78, FIND(":", G78)-1))</f>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I78">
+        <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
         <v>0</v>
       </c>
       <c r="J78" t="s">
@@ -4851,16 +4911,16 @@
         <v>248</v>
       </c>
       <c r="E79" t="s">
-        <v>301</v>
-      </c>
-      <c r="F79" s="1">
-        <v>0</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H79">
-        <f>E79*VALUE(LEFT(G79, FIND(":", G79)-1))</f>
+        <v>303</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I79">
+        <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
         <v>0</v>
       </c>
       <c r="J79" t="s">
@@ -4882,14 +4942,14 @@
       <c r="E80" t="s">
         <v>301</v>
       </c>
-      <c r="F80" s="1">
-        <v>0</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H80">
-        <f>E80*VALUE(LEFT(G80, FIND(":", G80)-1))</f>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I80">
+        <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
         <v>0</v>
       </c>
       <c r="J80" t="s">
@@ -4911,14 +4971,14 @@
       <c r="E81" t="s">
         <v>301</v>
       </c>
-      <c r="F81" s="1">
-        <v>0</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H81">
-        <f>E81*VALUE(LEFT(G81, FIND(":", G81)-1))</f>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I81">
+        <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
         <v>0</v>
       </c>
       <c r="J81" t="s">
@@ -4940,14 +5000,14 @@
       <c r="E82" t="s">
         <v>302</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82">
         <v>1</v>
       </c>
-      <c r="G82" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H82">
-        <f>E82*VALUE(LEFT(G82, FIND(":", G82)-1))</f>
+      <c r="H82" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="I82">
+        <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
         <v>0</v>
       </c>
       <c r="J82" t="s">
@@ -4969,14 +5029,14 @@
       <c r="E83" t="s">
         <v>301</v>
       </c>
-      <c r="F83" s="1">
-        <v>0</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H83">
-        <f>E83*VALUE(LEFT(G83, FIND(":", G83)-1))</f>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I83">
+        <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
         <v>0</v>
       </c>
       <c r="J83" t="s">
@@ -4998,14 +5058,17 @@
       <c r="E84" t="s">
         <v>302</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84">
         <v>1</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H84">
-        <f>E84*VALUE(LEFT(G84, FIND(":", G84)-1))</f>
+        <v>324</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I84">
+        <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
         <v>0</v>
       </c>
       <c r="J84" t="s">
@@ -5027,14 +5090,17 @@
       <c r="E85" t="s">
         <v>302</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85">
         <v>1</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H85">
-        <f>E85*VALUE(LEFT(G85, FIND(":", G85)-1))</f>
+        <v>325</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I85">
+        <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
         <v>0</v>
       </c>
       <c r="J85" t="s">
@@ -5056,14 +5122,14 @@
       <c r="E86" t="s">
         <v>301</v>
       </c>
-      <c r="F86" s="1">
-        <v>0</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H86">
-        <f>E86*VALUE(LEFT(G86, FIND(":", G86)-1))</f>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I86">
+        <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
         <v>0</v>
       </c>
       <c r="J86" t="s">
@@ -5083,16 +5149,16 @@
         <v>256</v>
       </c>
       <c r="E87" t="s">
-        <v>303</v>
-      </c>
-      <c r="F87" s="1">
+        <v>304</v>
+      </c>
+      <c r="F87">
         <v>1</v>
       </c>
-      <c r="G87" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H87">
-        <f>E87*VALUE(LEFT(G87, FIND(":", G87)-1))</f>
+      <c r="H87" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="I87">
+        <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
         <v>0</v>
       </c>
       <c r="J87" t="s">
@@ -5116,14 +5182,14 @@
       <c r="E88" t="s">
         <v>301</v>
       </c>
-      <c r="F88" s="1">
-        <v>0</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H88">
-        <f>E88*VALUE(LEFT(G88, FIND(":", G88)-1))</f>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I88">
+        <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
         <v>0</v>
       </c>
       <c r="J88" t="s">
@@ -5145,14 +5211,17 @@
       <c r="E89" t="s">
         <v>302</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H89">
-        <f>E89*VALUE(LEFT(G89, FIND(":", G89)-1))</f>
+        <v>326</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I89">
+        <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
         <v>0</v>
       </c>
       <c r="J89" t="s">
@@ -5174,14 +5243,17 @@
       <c r="E90" t="s">
         <v>302</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H90">
-        <f>E90*VALUE(LEFT(G90, FIND(":", G90)-1))</f>
+        <v>327</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I90">
+        <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
         <v>0</v>
       </c>
       <c r="J90" t="s">
@@ -5203,14 +5275,14 @@
       <c r="E91" t="s">
         <v>301</v>
       </c>
-      <c r="F91" s="1">
-        <v>0</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H91">
-        <f>E91*VALUE(LEFT(G91, FIND(":", G91)-1))</f>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I91">
+        <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
         <v>0</v>
       </c>
       <c r="J91" t="s">
@@ -5232,14 +5304,14 @@
       <c r="E92" t="s">
         <v>302</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92">
         <v>1</v>
       </c>
-      <c r="G92" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="H92">
-        <f>E92*VALUE(LEFT(G92, FIND(":", G92)-1))</f>
+      <c r="H92" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="I92">
+        <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
         <v>0</v>
       </c>
       <c r="J92" t="s">
@@ -5261,14 +5333,14 @@
       <c r="E93" t="s">
         <v>301</v>
       </c>
-      <c r="F93" s="1">
-        <v>0</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H93">
-        <f>E93*VALUE(LEFT(G93, FIND(":", G93)-1))</f>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I93">
+        <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
         <v>0</v>
       </c>
       <c r="J93" t="s">
@@ -5290,14 +5362,14 @@
       <c r="E94" t="s">
         <v>301</v>
       </c>
-      <c r="F94" s="1">
-        <v>0</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H94">
-        <f>E94*VALUE(LEFT(G94, FIND(":", G94)-1))</f>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I94">
+        <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
         <v>0</v>
       </c>
       <c r="J94" t="s">
@@ -5323,14 +5395,14 @@
       <c r="E95" t="s">
         <v>301</v>
       </c>
-      <c r="F95" s="1">
-        <v>0</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H95">
-        <f>E95*VALUE(LEFT(G95, FIND(":", G95)-1))</f>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I95">
+        <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
         <v>0</v>
       </c>
       <c r="J95" t="s">
@@ -5352,14 +5424,14 @@
       <c r="E96" t="s">
         <v>301</v>
       </c>
-      <c r="F96" s="1">
-        <v>0</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H96">
-        <f>E96*VALUE(LEFT(G96, FIND(":", G96)-1))</f>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I96">
+        <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
         <v>0</v>
       </c>
       <c r="J96" t="s">
@@ -5381,14 +5453,14 @@
       <c r="E97" t="s">
         <v>301</v>
       </c>
-      <c r="F97" s="1">
-        <v>0</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H97">
-        <f>E97*VALUE(LEFT(G97, FIND(":", G97)-1))</f>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I97">
+        <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
         <v>0</v>
       </c>
       <c r="J97" t="s">
@@ -5410,14 +5482,14 @@
       <c r="E98" t="s">
         <v>301</v>
       </c>
-      <c r="F98" s="1">
-        <v>0</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H98">
-        <f>E98*VALUE(LEFT(G98, FIND(":", G98)-1))</f>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I98">
+        <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
         <v>0</v>
       </c>
       <c r="J98" t="s">
@@ -5439,14 +5511,14 @@
       <c r="E99" t="s">
         <v>302</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99">
         <v>1</v>
       </c>
-      <c r="G99" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="H99">
-        <f>E99*VALUE(LEFT(G99, FIND(":", G99)-1))</f>
+      <c r="H99" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I99">
+        <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
         <v>0</v>
       </c>
       <c r="J99" t="s">
@@ -5468,14 +5540,14 @@
       <c r="E100" t="s">
         <v>301</v>
       </c>
-      <c r="F100" s="1">
-        <v>0</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H100">
-        <f>E100*VALUE(LEFT(G100, FIND(":", G100)-1))</f>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I100">
+        <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
         <v>0</v>
       </c>
       <c r="J100" t="s">
@@ -5499,14 +5571,14 @@
       <c r="E101" t="s">
         <v>302</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101">
         <v>1</v>
       </c>
-      <c r="G101" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="H101">
-        <f>E101*VALUE(LEFT(G101, FIND(":", G101)-1))</f>
+      <c r="H101" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="I101">
+        <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
         <v>0</v>
       </c>
       <c r="J101" t="s">
@@ -5528,14 +5600,14 @@
       <c r="E102" t="s">
         <v>302</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102">
         <v>1</v>
       </c>
-      <c r="G102" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="H102">
-        <f>E102*VALUE(LEFT(G102, FIND(":", G102)-1))</f>
+      <c r="H102" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="I102">
+        <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
         <v>0</v>
       </c>
       <c r="J102" t="s">
@@ -5557,14 +5629,14 @@
       <c r="E103" t="s">
         <v>301</v>
       </c>
-      <c r="F103" s="1">
-        <v>0</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H103">
-        <f>E103*VALUE(LEFT(G103, FIND(":", G103)-1))</f>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I103">
+        <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
         <v>0</v>
       </c>
       <c r="J103" t="s">
@@ -5586,14 +5658,14 @@
       <c r="E104" t="s">
         <v>301</v>
       </c>
-      <c r="F104" s="1">
-        <v>0</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H104">
-        <f>E104*VALUE(LEFT(G104, FIND(":", G104)-1))</f>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I104">
+        <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
         <v>0</v>
       </c>
       <c r="J104" t="s">
@@ -5615,14 +5687,14 @@
       <c r="E105" t="s">
         <v>301</v>
       </c>
-      <c r="F105" s="1">
-        <v>0</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H105">
-        <f>E105*VALUE(LEFT(G105, FIND(":", G105)-1))</f>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I105">
+        <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
         <v>0</v>
       </c>
       <c r="J105" t="s">
@@ -5644,14 +5716,14 @@
       <c r="E106" t="s">
         <v>301</v>
       </c>
-      <c r="F106" s="1">
-        <v>0</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H106">
-        <f>E106*VALUE(LEFT(G106, FIND(":", G106)-1))</f>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I106">
+        <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
         <v>0</v>
       </c>
       <c r="J106" t="s">
@@ -5675,14 +5747,14 @@
       <c r="E107" t="s">
         <v>301</v>
       </c>
-      <c r="F107" s="1">
-        <v>0</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H107">
-        <f>E107*VALUE(LEFT(G107, FIND(":", G107)-1))</f>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I107">
+        <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
         <v>0</v>
       </c>
       <c r="J107" t="s">
@@ -5704,14 +5776,17 @@
       <c r="E108" t="s">
         <v>302</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108">
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H108">
-        <f>E108*VALUE(LEFT(G108, FIND(":", G108)-1))</f>
+        <v>328</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I108">
+        <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
         <v>0</v>
       </c>
       <c r="J108" t="s">
@@ -5733,14 +5808,14 @@
       <c r="E109" t="s">
         <v>302</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109">
         <v>1</v>
       </c>
-      <c r="G109" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H109">
-        <f>E109*VALUE(LEFT(G109, FIND(":", G109)-1))</f>
+      <c r="H109" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I109">
+        <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
         <v>0</v>
       </c>
       <c r="J109" t="s">
@@ -5762,14 +5837,17 @@
       <c r="E110" t="s">
         <v>302</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110">
         <v>1</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="H110">
-        <f>E110*VALUE(LEFT(G110, FIND(":", G110)-1))</f>
+        <v>329</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I110">
+        <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
         <v>0</v>
       </c>
       <c r="J110" t="s">
@@ -5791,14 +5869,14 @@
       <c r="E111" t="s">
         <v>302</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111">
         <v>1</v>
       </c>
-      <c r="G111" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="H111">
-        <f>E111*VALUE(LEFT(G111, FIND(":", G111)-1))</f>
+      <c r="H111" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="I111">
+        <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
         <v>0</v>
       </c>
       <c r="J111" t="s">
@@ -5820,14 +5898,17 @@
       <c r="E112" t="s">
         <v>302</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H112">
-        <f>E112*VALUE(LEFT(G112, FIND(":", G112)-1))</f>
+        <v>330</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I112">
+        <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
         <v>0</v>
       </c>
       <c r="J112" t="s">
@@ -5851,14 +5932,17 @@
       <c r="E113" t="s">
         <v>300</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113">
         <v>1</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H113">
-        <f>E113*VALUE(LEFT(G113, FIND(":", G113)-1))</f>
+        <v>331</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I113">
+        <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
         <v>0</v>
       </c>
       <c r="J113" t="s">
@@ -5880,14 +5964,17 @@
       <c r="E114" t="s">
         <v>300</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H114">
-        <f>E114*VALUE(LEFT(G114, FIND(":", G114)-1))</f>
+        <v>332</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I114">
+        <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
         <v>0</v>
       </c>
       <c r="J114" t="s">
@@ -5909,14 +5996,17 @@
       <c r="E115" t="s">
         <v>300</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115">
         <v>1</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H115">
-        <f>E115*VALUE(LEFT(G115, FIND(":", G115)-1))</f>
+        <v>333</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I115">
+        <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
         <v>0</v>
       </c>
       <c r="J115" t="s">
@@ -5938,14 +6028,17 @@
       <c r="E116" t="s">
         <v>300</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116">
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H116">
-        <f>E116*VALUE(LEFT(G116, FIND(":", G116)-1))</f>
+        <v>334</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I116">
+        <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
         <v>0</v>
       </c>
       <c r="J116" t="s">
@@ -5967,14 +6060,17 @@
       <c r="E117" t="s">
         <v>302</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117">
         <v>1</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H117">
-        <f>E117*VALUE(LEFT(G117, FIND(":", G117)-1))</f>
+        <v>335</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I117">
+        <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
         <v>0</v>
       </c>
       <c r="J117" t="s">
@@ -5996,14 +6092,14 @@
       <c r="E118" t="s">
         <v>302</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118">
         <v>1</v>
       </c>
-      <c r="G118" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="H118">
-        <f>E118*VALUE(LEFT(G118, FIND(":", G118)-1))</f>
+      <c r="H118" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I118">
+        <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
         <v>0</v>
       </c>
       <c r="J118" t="s">
@@ -6025,14 +6121,17 @@
       <c r="E119" t="s">
         <v>300</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119">
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H119">
-        <f>E119*VALUE(LEFT(G119, FIND(":", G119)-1))</f>
+        <v>336</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I119">
+        <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
         <v>0</v>
       </c>
       <c r="J119" t="s">
@@ -6056,14 +6155,17 @@
       <c r="E120" t="s">
         <v>302</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120">
         <v>1</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H120">
-        <f>E120*VALUE(LEFT(G120, FIND(":", G120)-1))</f>
+        <v>337</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I120">
+        <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
         <v>0</v>
       </c>
       <c r="J120" t="s">
@@ -6085,14 +6187,14 @@
       <c r="E121" t="s">
         <v>301</v>
       </c>
-      <c r="F121" s="1">
-        <v>0</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H121">
-        <f>E121*VALUE(LEFT(G121, FIND(":", G121)-1))</f>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I121">
+        <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
         <v>0</v>
       </c>
       <c r="J121" t="s">
@@ -6114,14 +6216,14 @@
       <c r="E122" t="s">
         <v>301</v>
       </c>
-      <c r="F122" s="1">
-        <v>0</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H122">
-        <f>E122*VALUE(LEFT(G122, FIND(":", G122)-1))</f>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I122">
+        <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
         <v>0</v>
       </c>
       <c r="J122" t="s">
@@ -6143,14 +6245,14 @@
       <c r="E123" t="s">
         <v>301</v>
       </c>
-      <c r="F123" s="1">
-        <v>0</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H123">
-        <f>E123*VALUE(LEFT(G123, FIND(":", G123)-1))</f>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I123">
+        <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
         <v>0</v>
       </c>
       <c r="J123" t="s">
@@ -6172,14 +6274,14 @@
       <c r="E124" t="s">
         <v>301</v>
       </c>
-      <c r="F124" s="1">
-        <v>0</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H124">
-        <f>E124*VALUE(LEFT(G124, FIND(":", G124)-1))</f>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I124">
+        <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
         <v>0</v>
       </c>
       <c r="J124" t="s">
@@ -6201,14 +6303,14 @@
       <c r="E125" t="s">
         <v>302</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F125">
         <v>1</v>
       </c>
-      <c r="G125" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H125">
-        <f>E125*VALUE(LEFT(G125, FIND(":", G125)-1))</f>
+      <c r="H125" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I125">
+        <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
         <v>0</v>
       </c>
       <c r="J125" t="s">
@@ -6234,14 +6336,14 @@
       <c r="E126" t="s">
         <v>301</v>
       </c>
-      <c r="F126" s="1">
-        <v>0</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H126">
-        <f>E126*VALUE(LEFT(G126, FIND(":", G126)-1))</f>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I126">
+        <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
         <v>0</v>
       </c>
       <c r="J126" t="s">
@@ -6263,14 +6365,14 @@
       <c r="E127" t="s">
         <v>301</v>
       </c>
-      <c r="F127" s="1">
-        <v>0</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H127">
-        <f>E127*VALUE(LEFT(G127, FIND(":", G127)-1))</f>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I127">
+        <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
         <v>0</v>
       </c>
       <c r="J127" t="s">
@@ -6292,14 +6394,14 @@
       <c r="E128" t="s">
         <v>301</v>
       </c>
-      <c r="F128" s="1">
-        <v>0</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H128">
-        <f>E128*VALUE(LEFT(G128, FIND(":", G128)-1))</f>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I128">
+        <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
         <v>0</v>
       </c>
       <c r="J128" t="s">
@@ -6321,14 +6423,14 @@
       <c r="E129" t="s">
         <v>302</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F129">
         <v>1</v>
       </c>
-      <c r="G129" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H129">
-        <f>E129*VALUE(LEFT(G129, FIND(":", G129)-1))</f>
+      <c r="H129" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I129">
+        <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
         <v>0</v>
       </c>
       <c r="J129" t="s">
@@ -6350,14 +6452,14 @@
       <c r="E130" t="s">
         <v>301</v>
       </c>
-      <c r="F130" s="1">
-        <v>0</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H130">
-        <f>E130*VALUE(LEFT(G130, FIND(":", G130)-1))</f>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I130">
+        <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
         <v>0</v>
       </c>
       <c r="J130" t="s">
@@ -6395,391 +6497,391 @@
     <mergeCell ref="B126:B130"/>
   </mergeCells>
   <dataValidations count="129">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"0: 0 items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5">
-      <formula1>"0: No items completed,3: item 1 completed,5: items 1, and 2 completed,8: items 1, 2, and 3 completed,10: items 1, 2, 3, and 4 completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5">
+      <formula1>"0: No items completed,3: item 1 completed,5: items 1. and 2 completed,8: items 1. 2. and 3 completed,10: items 1. 2. 3. and 4 completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G9">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G13">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G14">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G15">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G16">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G17">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G18">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
       <formula1>"0: No rules established,10: Published policy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G20">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G22">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G23">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G24">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G25">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G26">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G27">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G28">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G29">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G30">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G31">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
       <formula1>"0: Not done,10: Done and clearly defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G32">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G33">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G34">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G35">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G36">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
       <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G38">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G39">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G40">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G41">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G42">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G43">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G44">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G45">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G46">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G47">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G48">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G49">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G50">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G51">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G52">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G53">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G54">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G55">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G56">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G57">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G58">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G59">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G60">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
       <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G61">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G62">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G63">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G64">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G66">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G67">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
       <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G69">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G70">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G71">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G72">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G73">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G74">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
       <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G75">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G76">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
       <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G78">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G79">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G80">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G81">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G82">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H78">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G83">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G84">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H83">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H84">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G85">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G86">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G87">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G88">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G89">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G90">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G91">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G92">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
       <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G93">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G94">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G95">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G96">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G97">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G98">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G99">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
       <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G100">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G102">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G103">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G104">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G105">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G106">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G107">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G108">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H105">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H106">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G109">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
       <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G110">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H110">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G111">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H111">
       <formula1>"0: No alerting,10: Alerting exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G112">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H112">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G113">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H113">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G114">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H114">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G115">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H115">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G116">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H116">
       <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G117">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H117">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G118">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H118">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G119">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H119">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G120">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H120">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G121">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G122">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G123">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G124">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G125">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H121">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H122">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H123">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H124">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H125">
       <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G126">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G127">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G128">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H126">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H127">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H128">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H129">
       <formula1>"0: Not monitored,2: Reported,5: Manual remediation,10: Automated remediation"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G130">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H130">
       <formula1>"0: None"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="410">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -70,6 +70,9 @@
     <t>Data Ingestion</t>
   </si>
   <si>
+    <t>Executive Strategy Alignment</t>
+  </si>
+  <si>
     <t>FinOps Assessment</t>
   </si>
   <si>
@@ -217,7 +220,7 @@
     <t>Share Reporting &amp; Definitions</t>
   </si>
   <si>
-    <t>Provide Cloud Metrics to Teams</t>
+    <t>Provide Technology Metrics to Teams</t>
   </si>
   <si>
     <t>Coordinate Policy Changes Broadly</t>
@@ -244,6 +247,18 @@
     <t>Resolve Variances &amp; Increase Coverage</t>
   </si>
   <si>
+    <t>Establish Executive Sponsorship</t>
+  </si>
+  <si>
+    <t>Define Decision Rights &amp; Guardrails</t>
+  </si>
+  <si>
+    <t>Build Multi-Year Investment Forecast</t>
+  </si>
+  <si>
+    <t>Establish Decision Support Cadence</t>
+  </si>
+  <si>
     <t>Establish Architecture Review Process</t>
   </si>
   <si>
@@ -631,6 +646,18 @@
     <t>112</t>
   </si>
   <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
     <t>061</t>
   </si>
   <si>
@@ -922,13 +949,22 @@
     <t>0.8.0</t>
   </si>
   <si>
+    <t>0.7.1</t>
+  </si>
+  <si>
     <t>0.7.0</t>
   </si>
   <si>
     <t>1.7.0</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.9.0</t>
+  </si>
+  <si>
+    <t>0.8.1</t>
+  </si>
+  <si>
+    <t>0.0.1</t>
   </si>
   <si>
     <t>1.5.0</t>
@@ -977,6 +1013,64 @@
 * CI/CD governance
 * Proactive recommendations at deployment
 10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>1. Identify key stakeholder teams and key contacts for each (ITAM, SRE, etc.)
+2. Document initial thoughts on how this other team may help FinOps goals
+3. Document initial thoughts on how the FinOps team may help the other team's goals
+4. Reach out to the other team with the initial summary of goals
+5. Meet with the other team to better understand how they work</t>
+  </si>
+  <si>
+    <t>* Align on new shared goals that will enhance both teams achievements
+* Determine what data is shared across teams to establish a single source of truth
+* Identify and agree on tasks that will lead to accomplishing shared goals
+* Determine which teams have capacity to work on goal tasks periodically
+* Incorporate tasks into team capacity planning and dependency workflows
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Agree on definitions of shared concepts across teams to reduce confusion
+* Adjust reporting so shared metrics are consistent and from the same source, even if multiple dashboards exist
+* Regularly align on interpretation of shared metrics to plan next steps and report those to leadership
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Share relevant data already maintained and tracked by FinOps
+* Share metric reporting and the calculations behind FinOps created metrics
+* Create new metrics from FinOps and other data based on needs of allied teams
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>1. Document new policies as a result of cross-functional collaboration goals
+2. Broad policy changes are accepted by governing and stakeholder teams
+3. Communication is distributed by all governing teams using shared language
+4. Change management procedures are followed for updated policy implementation
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>* Come up with shared responses as allied teams to external conflicts
+* Resolve internal conflicts before deciding on the next steps needed to reach shared goals
+* Communication to external teams or leaders includes the full story of how allied teams achieve goals together
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Document decision rights and approval authority for technology spend
+* Define and publish spend guardrails with named owners
+* Establish escalation path for spend exceptions
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Inventory vendor commitments across technology categories (cloud, SaaS, data center, AI)
+* Create a multi-year forecast incorporating renewal timelines and growth projections
+* Incorporate transition and modernization costs into the investment plan
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Define a regular review cadence for technology investment decisions
+* Deliver cost and outcome comparisons for competing initiatives at reviews
+* Track and report action follow-through from investment decisions
+10*Ceil(x/3)</t>
   </si>
   <si>
     <t>* Define process to address notifications from CSPs
@@ -1163,6 +1257,40 @@
 10*Ceil(x/4)</t>
   </si>
   <si>
+    <t>* Identify key business performance data to select from various operational areas
+* Agree on source of truth for business data with common terminology
+* Clearly define what a unit of value is for each business metric to be tracked
+* Agree on which costs to use in calculations (list, discounted, amortized, etc.)
+* Define formulas to allocate cost per unit of business value over the same time period to create a KPI
+* Changes to data ingestion, metric definitions, or cost allocations are documented and communicated
+10*Ceil(x/6)</t>
+  </si>
+  <si>
+    <t>* Continuously collect data over time for all inputs to unit economic equations
+* Automate unit economic calculations for each corresponding point in time for cost and business data
+* Create plots of unit economic metrics over time to easily report on and track trends
+* Show disaggregated data to compare unit metrics with standalone usage or rate changes
+* Include filters to show data by each relevant operational area of the business (product/segment/region/etc.)
+* Plots and dashboards are easily accessible by key stakeholders across the business
+10*Ceil(x/6)</t>
+  </si>
+  <si>
+    <t>* Collaborate with stakeholders on desired acceptable thresholds or goals for each unit economic value
+* Review data with stakeholders when metrics exceed acceptable thresholds in either direction
+* Incorporate metric reviews into the decision making processes of stakeholder departments
+* The FinOps team should periodically publish an analysis of major changes in the metrics dashboards
+as well as facilitate reviews of metrics, adoption data, modifications, and KPI refreshes
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>* Scenario plan for which metric values will drive the next decisions, behaviors, or outcomes needed
+* Investigate root causes for changes in metric values to determine next steps
+* Add to the backlog which actions are required to get unit metrics to a desired level
+* Unit economics influence the decisions in build vs buy, architecture design,
+ workload placement, migration, sourcing, pricing, etc.
+10*Ceil(x/4)</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': '0 items completed'}, {'Score': 3, 'Condition': '1 item completed'}, {'Score': 5, 'Condition': '2 items completed'}, {'Score': 8, 'Condition': '3 items completed'}, {'Score': 10, 'Condition': '4 items completed'}]</t>
   </si>
   <si>
@@ -1172,7 +1300,7 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 4, 'Condition': '1 item completed'}, {'Score': 7, 'Condition': '2 items completed'}, {'Score': 10, 'Condition': '3 items completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1, and 2 completed'}, {'Score': 8, 'Condition': 'items 1, 2, and 3 completed'}, {'Score': 10, 'Condition': 'items 1, 2, 3, and 4 completed'}]</t>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1-2 completed'}, {'Score': 8, 'Condition': 'items 1-3 completed'}, {'Score': 10, 'Condition': 'items 1-4 completed'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': None}]</t>
@@ -1190,9 +1318,15 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 6, 'Condition': '3 items completed'}, {'Score': 8, 'Condition': '4 items completed'}, {'Score': 10, 'Condition': '5 items completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': 'item 1 completed'}, {'Score': 4, 'Condition': 'items 1-2 completed'}, {'Score': 6, 'Condition': 'items 1-3 completed'}, {'Score': 8, 'Condition': 'items 1-4 completed'}, {'Score': 10, 'Condition': 'items 1-5 completed'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Done and clearly defined'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No executive sponsor identified'}, {'Score': 10, 'Condition': 'Executive sponsor formally identified and actively engaged'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Does not exist'}, {'Score': 10, 'Condition': 'Exists'}]</t>
   </si>
   <si>
@@ -1263,6 +1397,9 @@
   </si>
   <si>
     <t>0: No rules established</t>
+  </si>
+  <si>
+    <t>0: No executive sponsor identified</t>
   </si>
   <si>
     <t>0: Does not exist</t>
@@ -1566,9 +1703,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Overview!$A$12:$A$31</c:f>
+              <c:f>Overview!$A$12:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>Allocation</c:v>
                 </c:pt>
@@ -1588,45 +1725,48 @@
                   <c:v>Data Ingestion</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>Executive Strategy Alignment</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>FinOps Assessment</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>FinOps Education &amp; Enablement</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>FinOps Practice Operations</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>Forecasting</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>Intersecting Disciplines</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>Invoicing &amp; Chargeback</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>KPIs &amp; Benchmarking</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>Licensing &amp; SaaS</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>Planning &amp; Estimating</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>Policy</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>Rate Optimization</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>Reporting &amp; Analytics</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>Unit Economics</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>Usage Optimization</c:v>
                 </c:pt>
               </c:strCache>
@@ -1634,10 +1774,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Overview!$U$12:$U$31</c:f>
+              <c:f>Overview!$U$12:$U$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1696,6 +1836,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1867,7 +2010,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A11:B31" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A11:B32" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Capability"/>
     <tableColumn id="2" name="Action Count"/>
@@ -2161,7 +2304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
@@ -2186,14 +2329,14 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2">
-        <f>SUM(Scoring!F2:F130)</f>
+        <f>SUM(Scoring!F2:F134)</f>
         <v>0</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2">
-        <f>SUM(Scoring!I2:I130)/A2</f>
+        <f>SUM(Scoring!I2:I134)/A2</f>
         <v>0</v>
       </c>
       <c r="D2">
@@ -2217,7 +2360,7 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <f>SUMIF(Scoring!J2:J130,A5,Scoring!I2:I130)/SUMIF(Scoring!J2:J130,A5,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!J2:J134,A5,Scoring!I2:I134)/SUMIF(Scoring!J2:J134,A5,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2226,10 +2369,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="U6">
-        <f>SUMIF(Scoring!J2:J130,A6,Scoring!I2:I130)/SUMIF(Scoring!J2:J130,A6,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!J2:J134,A6,Scoring!I2:I134)/SUMIF(Scoring!J2:J134,A6,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2241,7 +2384,7 @@
         <v>31</v>
       </c>
       <c r="U7">
-        <f>SUMIF(Scoring!J2:J130,A7,Scoring!I2:I130)/SUMIF(Scoring!J2:J130,A7,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!J2:J134,A7,Scoring!I2:I134)/SUMIF(Scoring!J2:J134,A7,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2253,7 +2396,7 @@
         <v>60</v>
       </c>
       <c r="U8">
-        <f>SUMIF(Scoring!J2:J130,A8,Scoring!I2:I130)/SUMIF(Scoring!J2:J130,A8,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!J2:J134,A8,Scoring!I2:I134)/SUMIF(Scoring!J2:J134,A8,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2279,7 +2422,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <f>SUMIF(Scoring!K2:K130,A12,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A12,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A12,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A12,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2291,7 +2434,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <f>SUMIF(Scoring!K2:K130,A13,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A13,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A13,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A13,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2303,7 +2446,7 @@
         <v>12</v>
       </c>
       <c r="U14">
-        <f>SUMIF(Scoring!K2:K130,A14,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A14,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A14,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A14,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2315,7 +2458,7 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <f>SUMIF(Scoring!K2:K130,A15,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A15,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A15,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A15,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2327,7 +2470,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <f>SUMIF(Scoring!K2:K130,A16,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A16,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A16,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A16,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2339,7 +2482,7 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <f>SUMIF(Scoring!K2:K130,A17,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A17,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A17,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A17,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2348,10 +2491,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <f>SUMIF(Scoring!K2:K130,A18,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A18,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A18,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A18,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2363,7 +2506,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <f>SUMIF(Scoring!K2:K130,A19,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A19,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A19,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A19,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2372,10 +2515,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <f>SUMIF(Scoring!K2:K130,A20,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A20,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A20,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A20,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2387,7 +2530,7 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <f>SUMIF(Scoring!K2:K130,A21,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A21,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A21,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A21,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2399,7 +2542,7 @@
         <v>6</v>
       </c>
       <c r="U22">
-        <f>SUMIF(Scoring!K2:K130,A22,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A22,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A22,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A22,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2411,7 +2554,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <f>SUMIF(Scoring!K2:K130,A23,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A23,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A23,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A23,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2423,7 +2566,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <f>SUMIF(Scoring!K2:K130,A24,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A24,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A24,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A24,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2435,7 +2578,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <f>SUMIF(Scoring!K2:K130,A25,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A25,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A25,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A25,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2444,10 +2587,10 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <f>SUMIF(Scoring!K2:K130,A26,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A26,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A26,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A26,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2456,10 +2599,10 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <f>SUMIF(Scoring!K2:K130,A27,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A27,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A27,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A27,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2468,10 +2611,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U28">
-        <f>SUMIF(Scoring!K2:K130,A28,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A28,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A28,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A28,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2480,10 +2623,10 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <f>SUMIF(Scoring!K2:K130,A29,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A29,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A29,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A29,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2492,10 +2635,10 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <f>SUMIF(Scoring!K2:K130,A30,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A30,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A30,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A30,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2507,13 +2650,25 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <f>SUMIF(Scoring!K2:K130,A31,Scoring!I2:I130)/SUMIF(Scoring!K2:K130,A31,Scoring!F2:F130)</f>
+        <f>SUMIF(Scoring!K2:K134,A31,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A31,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:21">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
       <c r="B32">
-        <f>SUM(Overview!$B$12:$B$31)</f>
+        <v>6</v>
+      </c>
+      <c r="U32">
+        <f>SUMIF(Scoring!K2:K134,A32,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A32,Scoring!F2:F134)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33">
+        <f>SUM(Overview!$B$12:$B$32)</f>
         <v>0</v>
       </c>
     </row>
@@ -2530,7 +2685,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K130"/>
+  <dimension ref="A1:K134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -2548,37 +2703,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2586,25 +2741,25 @@
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2614,29 +2769,29 @@
         <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E3" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2646,29 +2801,29 @@
         <v>7</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E4" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2678,29 +2833,29 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2710,29 +2865,29 @@
         <v>7</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E6" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2742,28 +2897,28 @@
         <v>7</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E7" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -2773,26 +2928,26 @@
         <v>7</v>
       </c>
       <c r="K7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E8" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -2802,26 +2957,26 @@
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E9" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -2831,29 +2986,29 @@
         <v>7</v>
       </c>
       <c r="K9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E10" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -2863,26 +3018,26 @@
         <v>7</v>
       </c>
       <c r="K10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E11" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -2892,28 +3047,28 @@
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E12" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -2923,26 +3078,26 @@
         <v>7</v>
       </c>
       <c r="K12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E13" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -2952,26 +3107,26 @@
         <v>7</v>
       </c>
       <c r="K13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E14" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -2981,26 +3136,26 @@
         <v>7</v>
       </c>
       <c r="K14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E15" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3010,26 +3165,26 @@
         <v>7</v>
       </c>
       <c r="K15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E16" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3039,26 +3194,26 @@
         <v>7</v>
       </c>
       <c r="K16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E17" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3068,7 +3223,7 @@
         <v>7</v>
       </c>
       <c r="K17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3077,19 +3232,19 @@
         <v>14</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E18" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3106,19 +3261,19 @@
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E19" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3135,19 +3290,19 @@
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E20" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3164,22 +3319,22 @@
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E21" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3196,19 +3351,19 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E22" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3224,22 +3379,25 @@
     <row r="23" spans="1:11">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E23" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3249,26 +3407,29 @@
         <v>7</v>
       </c>
       <c r="K23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E24" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3278,26 +3439,29 @@
         <v>7</v>
       </c>
       <c r="K24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E25" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3307,26 +3471,29 @@
         <v>7</v>
       </c>
       <c r="K25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E26" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3336,26 +3503,29 @@
         <v>7</v>
       </c>
       <c r="K26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E27" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3365,26 +3535,29 @@
         <v>7</v>
       </c>
       <c r="K27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E28" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3394,28 +3567,28 @@
         <v>7</v>
       </c>
       <c r="K28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E29" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3425,26 +3598,26 @@
         <v>7</v>
       </c>
       <c r="K29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E30" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3454,26 +3627,26 @@
         <v>7</v>
       </c>
       <c r="K30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E31" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3483,26 +3656,26 @@
         <v>7</v>
       </c>
       <c r="K31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E32" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3512,26 +3685,26 @@
         <v>7</v>
       </c>
       <c r="K32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E33" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3541,26 +3714,26 @@
         <v>7</v>
       </c>
       <c r="K33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E34" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -3570,149 +3743,157 @@
         <v>7</v>
       </c>
       <c r="K34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E35" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E36" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E37" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E38" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
+      <c r="G38" s="1" t="s">
+        <v>332</v>
+      </c>
       <c r="H38" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
         <v>0</v>
       </c>
       <c r="J38" t="s">
+        <v>7</v>
+      </c>
+      <c r="K38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K38" t="s">
+      <c r="B39" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E39" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -3729,19 +3910,22 @@
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E40" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -3758,19 +3942,19 @@
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E41" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -3787,19 +3971,19 @@
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E42" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -3816,22 +4000,19 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E43" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -3848,19 +4029,19 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E44" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -3877,19 +4058,19 @@
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E45" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -3906,19 +4087,19 @@
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E46" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -3933,23 +4114,24 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="2"/>
-      <c r="B47" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B47" s="2"/>
       <c r="C47" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E47" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
+      <c r="G47" s="1" t="s">
+        <v>334</v>
+      </c>
       <c r="H47" s="1" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -3959,26 +4141,26 @@
         <v>9</v>
       </c>
       <c r="K47" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E48" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -3988,26 +4170,26 @@
         <v>9</v>
       </c>
       <c r="K48" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E49" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4017,26 +4199,26 @@
         <v>9</v>
       </c>
       <c r="K49" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E50" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4046,26 +4228,28 @@
         <v>9</v>
       </c>
       <c r="K50" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
+      <c r="B51" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="C51" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E51" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4075,26 +4259,26 @@
         <v>9</v>
       </c>
       <c r="K51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E52" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4104,28 +4288,26 @@
         <v>9</v>
       </c>
       <c r="K52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="2"/>
-      <c r="B53" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="B53" s="2"/>
       <c r="C53" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E53" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4135,26 +4317,26 @@
         <v>9</v>
       </c>
       <c r="K53" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E54" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4164,26 +4346,26 @@
         <v>9</v>
       </c>
       <c r="K54" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E55" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4193,26 +4375,26 @@
         <v>9</v>
       </c>
       <c r="K55" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E56" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4222,26 +4404,28 @@
         <v>9</v>
       </c>
       <c r="K56" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
+      <c r="B57" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C57" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E57" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4251,29 +4435,26 @@
         <v>9</v>
       </c>
       <c r="K57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E58" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="H58" s="1" t="s">
-        <v>368</v>
+        <v>397</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4283,28 +4464,26 @@
         <v>9</v>
       </c>
       <c r="K58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="2"/>
-      <c r="B59" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="B59" s="2"/>
       <c r="C59" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E59" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4314,26 +4493,26 @@
         <v>9</v>
       </c>
       <c r="K59" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E60" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4343,26 +4522,26 @@
         <v>9</v>
       </c>
       <c r="K60" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E61" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4372,26 +4551,29 @@
         <v>9</v>
       </c>
       <c r="K61" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E62" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4401,26 +4583,28 @@
         <v>9</v>
       </c>
       <c r="K62" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
+      <c r="B63" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C63" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E63" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4430,26 +4614,26 @@
         <v>9</v>
       </c>
       <c r="K63" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E64" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4459,31 +4643,26 @@
         <v>9</v>
       </c>
       <c r="K64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="2"/>
-      <c r="B65" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B65" s="2"/>
       <c r="C65" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E65" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="H65" s="1" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4493,29 +4672,26 @@
         <v>9</v>
       </c>
       <c r="K65" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E66" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F66">
-        <v>1</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4525,29 +4701,26 @@
         <v>9</v>
       </c>
       <c r="K66" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E67" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F67">
-        <v>1</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>317</v>
+        <v>0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -4557,29 +4730,26 @@
         <v>9</v>
       </c>
       <c r="K67" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E68" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F68">
-        <v>1</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -4589,29 +4759,31 @@
         <v>9</v>
       </c>
       <c r="K68" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
+      <c r="B69" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C69" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -4628,22 +4800,22 @@
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E70" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -4660,19 +4832,22 @@
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E71" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -4687,26 +4862,24 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="2"/>
-      <c r="B72" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B72" s="2"/>
       <c r="C72" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E72" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -4716,29 +4889,29 @@
         <v>9</v>
       </c>
       <c r="K72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E73" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -4748,26 +4921,29 @@
         <v>9</v>
       </c>
       <c r="K73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E74" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
+      <c r="G74" s="1" t="s">
+        <v>341</v>
+      </c>
       <c r="H74" s="1" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -4777,26 +4953,26 @@
         <v>9</v>
       </c>
       <c r="K74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E75" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -4806,26 +4982,31 @@
         <v>9</v>
       </c>
       <c r="K75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
+      <c r="B76" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C76" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E76" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -4842,22 +5023,22 @@
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E77" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -4874,19 +5055,19 @@
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E78" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>369</v>
+        <v>404</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -4901,23 +5082,21 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="2"/>
-      <c r="B79" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B79" s="2"/>
       <c r="C79" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E79" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="F79">
         <v>0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -4927,26 +5106,26 @@
         <v>9</v>
       </c>
       <c r="K79" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E80" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F80">
         <v>0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -4956,26 +5135,29 @@
         <v>9</v>
       </c>
       <c r="K80" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E81" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>344</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -4985,26 +5167,26 @@
         <v>9</v>
       </c>
       <c r="K81" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E82" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5014,26 +5196,28 @@
         <v>9</v>
       </c>
       <c r="K82" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
+      <c r="B83" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C83" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E83" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="F83">
         <v>0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5050,22 +5234,19 @@
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E84" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F84">
-        <v>1</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5082,22 +5263,19 @@
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E85" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F85">
-        <v>1</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5114,19 +5292,19 @@
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E86" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5143,19 +5321,19 @@
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E87" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5170,23 +5348,24 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="2"/>
-      <c r="B88" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B88" s="2"/>
       <c r="C88" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E88" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5196,29 +5375,29 @@
         <v>9</v>
       </c>
       <c r="K88" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E89" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5228,29 +5407,26 @@
         <v>9</v>
       </c>
       <c r="K89" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E90" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F90">
-        <v>1</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5260,26 +5436,26 @@
         <v>9</v>
       </c>
       <c r="K90" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E91" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5289,26 +5465,28 @@
         <v>9</v>
       </c>
       <c r="K91" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
+      <c r="B92" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="C92" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E92" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5318,26 +5496,29 @@
         <v>9</v>
       </c>
       <c r="K92" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E93" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5347,26 +5528,29 @@
         <v>9</v>
       </c>
       <c r="K93" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E94" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5376,146 +5560,146 @@
         <v>9</v>
       </c>
       <c r="K94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:11">
-      <c r="A95" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
       <c r="C95" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E95" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F95">
         <v>0</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K95" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E96" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
         <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K96" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E97" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F97">
         <v>0</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K97" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E98" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F98">
         <v>0</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
         <v>0</v>
       </c>
       <c r="J98" t="s">
+        <v>9</v>
+      </c>
+      <c r="K98" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K98" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
+      <c r="B99" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C99" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E99" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -5525,26 +5709,26 @@
         <v>8</v>
       </c>
       <c r="K99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E100" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F100">
         <v>0</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -5554,28 +5738,26 @@
         <v>8</v>
       </c>
       <c r="K100" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="2"/>
-      <c r="B101" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B101" s="2"/>
       <c r="C101" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E101" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -5585,26 +5767,26 @@
         <v>8</v>
       </c>
       <c r="K101" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E102" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -5614,26 +5796,26 @@
         <v>8</v>
       </c>
       <c r="K102" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E103" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -5643,26 +5825,26 @@
         <v>8</v>
       </c>
       <c r="K103" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E104" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -5672,26 +5854,28 @@
         <v>8</v>
       </c>
       <c r="K104" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
+      <c r="B105" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C105" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E105" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -5708,19 +5892,19 @@
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E106" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -5735,23 +5919,21 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="2"/>
-      <c r="B107" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="B107" s="2"/>
       <c r="C107" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E107" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F107">
         <v>0</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -5761,29 +5943,26 @@
         <v>8</v>
       </c>
       <c r="K107" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E108" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F108">
-        <v>1</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -5793,26 +5972,26 @@
         <v>8</v>
       </c>
       <c r="K108" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E109" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -5822,29 +6001,26 @@
         <v>8</v>
       </c>
       <c r="K109" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="E110" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F110">
-        <v>1</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
@@ -5854,26 +6030,28 @@
         <v>8</v>
       </c>
       <c r="K110" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="2"/>
-      <c r="B111" s="2"/>
+      <c r="B111" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="C111" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E111" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -5883,29 +6061,29 @@
         <v>8</v>
       </c>
       <c r="K111" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E112" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -5915,31 +6093,26 @@
         <v>8</v>
       </c>
       <c r="K112" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="2"/>
-      <c r="B113" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="B113" s="2"/>
       <c r="C113" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E113" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
-      <c r="G113" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="H113" s="1" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -5949,29 +6122,29 @@
         <v>8</v>
       </c>
       <c r="K113" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E114" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -5981,29 +6154,26 @@
         <v>8</v>
       </c>
       <c r="K114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E115" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
-      <c r="G115" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="H115" s="1" t="s">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6013,29 +6183,29 @@
         <v>8</v>
       </c>
       <c r="K115" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E116" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="F116">
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6045,29 +6215,31 @@
         <v>8</v>
       </c>
       <c r="K116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="2"/>
-      <c r="B117" s="2"/>
+      <c r="B117" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C117" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E117" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F117">
         <v>1</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6077,26 +6249,29 @@
         <v>8</v>
       </c>
       <c r="K117" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E118" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F118">
         <v>1</v>
       </c>
+      <c r="G118" s="1" t="s">
+        <v>353</v>
+      </c>
       <c r="H118" s="1" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6106,29 +6281,29 @@
         <v>8</v>
       </c>
       <c r="K118" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E119" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="F119">
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -6138,31 +6313,29 @@
         <v>8</v>
       </c>
       <c r="K119" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="2"/>
-      <c r="B120" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B120" s="2"/>
       <c r="C120" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F120">
         <v>1</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -6172,26 +6345,29 @@
         <v>8</v>
       </c>
       <c r="K120" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E121" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -6201,26 +6377,26 @@
         <v>8</v>
       </c>
       <c r="K121" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E122" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -6230,26 +6406,29 @@
         <v>8</v>
       </c>
       <c r="K122" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E123" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -6259,26 +6438,31 @@
         <v>8</v>
       </c>
       <c r="K123" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="2"/>
-      <c r="B124" s="2"/>
+      <c r="B124" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="C124" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E124" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -6288,26 +6472,29 @@
         <v>8</v>
       </c>
       <c r="K124" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E125" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F125">
         <v>1</v>
       </c>
+      <c r="G125" s="1" t="s">
+        <v>359</v>
+      </c>
       <c r="H125" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -6317,146 +6504,155 @@
         <v>8</v>
       </c>
       <c r="K125" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126" spans="1:11">
-      <c r="A126" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
       <c r="C126" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="E126" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
         <v>0</v>
       </c>
       <c r="J126" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K126" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E127" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>361</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
         <v>0</v>
       </c>
       <c r="J127" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K127" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E128" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
         <v>0</v>
       </c>
       <c r="J128" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K128" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E129" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F129">
         <v>1</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
         <v>0</v>
       </c>
       <c r="J129" t="s">
+        <v>8</v>
+      </c>
+      <c r="K129" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K129" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11">
-      <c r="A130" s="2"/>
-      <c r="B130" s="2"/>
+      <c r="B130" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C130" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E130" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F130">
         <v>0</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -6466,37 +6662,154 @@
         <v>6</v>
       </c>
       <c r="K130" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="2"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E131" t="s">
+        <v>311</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="I131">
+        <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J131" t="s">
+        <v>6</v>
+      </c>
+      <c r="K131" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" s="2"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E132" t="s">
+        <v>311</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="I132">
+        <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J132" t="s">
+        <v>6</v>
+      </c>
+      <c r="K132" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133" s="2"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E133" t="s">
+        <v>312</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I133">
+        <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J133" t="s">
+        <v>6</v>
+      </c>
+      <c r="K133" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E134" t="s">
+        <v>311</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="I134">
+        <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J134" t="s">
+        <v>6</v>
+      </c>
+      <c r="K134" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A2:A34"/>
-    <mergeCell ref="A35:A94"/>
-    <mergeCell ref="A95:A125"/>
-    <mergeCell ref="A126:A130"/>
+  <mergeCells count="25">
+    <mergeCell ref="A2:A38"/>
+    <mergeCell ref="A39:A98"/>
+    <mergeCell ref="A99:A129"/>
+    <mergeCell ref="A130:A134"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="B7:B11"/>
     <mergeCell ref="B12:B17"/>
     <mergeCell ref="B18:B22"/>
     <mergeCell ref="B23:B28"/>
     <mergeCell ref="B29:B34"/>
-    <mergeCell ref="B35:B46"/>
-    <mergeCell ref="B47:B52"/>
-    <mergeCell ref="B53:B58"/>
-    <mergeCell ref="B59:B64"/>
-    <mergeCell ref="B65:B71"/>
-    <mergeCell ref="B72:B78"/>
-    <mergeCell ref="B79:B87"/>
-    <mergeCell ref="B88:B94"/>
-    <mergeCell ref="B95:B100"/>
-    <mergeCell ref="B101:B106"/>
-    <mergeCell ref="B107:B112"/>
-    <mergeCell ref="B113:B119"/>
-    <mergeCell ref="B120:B125"/>
-    <mergeCell ref="B126:B130"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B39:B50"/>
+    <mergeCell ref="B51:B56"/>
+    <mergeCell ref="B57:B62"/>
+    <mergeCell ref="B63:B68"/>
+    <mergeCell ref="B69:B75"/>
+    <mergeCell ref="B76:B82"/>
+    <mergeCell ref="B83:B91"/>
+    <mergeCell ref="B92:B98"/>
+    <mergeCell ref="B99:B104"/>
+    <mergeCell ref="B105:B110"/>
+    <mergeCell ref="B111:B116"/>
+    <mergeCell ref="B117:B123"/>
+    <mergeCell ref="B124:B129"/>
+    <mergeCell ref="B130:B134"/>
   </mergeCells>
-  <dataValidations count="129">
+  <dataValidations count="133">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"0: 0 items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
@@ -6507,7 +6820,7 @@
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5">
-      <formula1>"0: No items completed,3: item 1 completed,5: items 1. and 2 completed,8: items 1. 2. and 3 completed,10: items 1. 2. 3. and 4 completed"</formula1>
+      <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
@@ -6561,22 +6874,22 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: item 1 completed,4: items 1-2 completed,6: items 1-3 completed,8: items 1-4 completed,10: items 1-5 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
       <formula1>"0: None"</formula1>
@@ -6597,31 +6910,31 @@
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
+      <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
       <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
-      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
       <formula1>"0: None"</formula1>
@@ -6633,7 +6946,7 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
       <formula1>"0: None"</formula1>
@@ -6642,16 +6955,16 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
@@ -6663,70 +6976,70 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
-      <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
+      <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
       <formula1>"0: None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
       <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
-      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
-      <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H78">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
       <formula1>"0: None"</formula1>
@@ -6735,52 +7048,52 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
+      <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
       <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
-      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H83">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H84">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
+      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
+      <formula1>"0: None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
       <formula1>"0: None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
       <formula1>"0: None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
-      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
-      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
       <formula1>"0: None"</formula1>
@@ -6789,99 +7102,111 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
-      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H105">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H106">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
-      <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H110">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H111">
-      <formula1>"0: No alerting,10: Alerting exists"</formula1>
+      <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H112">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H113">
+      <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H114">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H115">
+      <formula1>"0: No alerting,10: Alerting exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H116">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H117">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H114">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H118">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H115">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H119">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H116">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H120">
       <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H117">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H121">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H118">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H122">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H119">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H123">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H120">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H124">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H121">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H125">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H126">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H127">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H128">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H129">
+      <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H130">
       <formula1>"0: None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H122">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H131">
       <formula1>"0: None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H123">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H132">
       <formula1>"0: None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H124">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H125">
-      <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H126">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H127">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H128">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H133">
       <formula1>"0: Not monitored,2: Reported,5: Manual remediation,10: Automated remediation"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H130">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H134">
       <formula1>"0: None"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7015,6 +7340,10 @@
     <hyperlink ref="D128" r:id="rId127"/>
     <hyperlink ref="D129" r:id="rId128"/>
     <hyperlink ref="D130" r:id="rId129"/>
+    <hyperlink ref="D131" r:id="rId130"/>
+    <hyperlink ref="D132" r:id="rId131"/>
+    <hyperlink ref="D133" r:id="rId132"/>
+    <hyperlink ref="D134" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="415">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -946,25 +946,25 @@
     <t>106</t>
   </si>
   <si>
+    <t>1.0.0</t>
+  </si>
+  <si>
+    <t>0.7.0</t>
+  </si>
+  <si>
     <t>0.8.0</t>
   </si>
   <si>
+    <t>1.7.0</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>0.0.1</t>
+  </si>
+  <si>
     <t>0.7.1</t>
-  </si>
-  <si>
-    <t>0.7.0</t>
-  </si>
-  <si>
-    <t>1.7.0</t>
-  </si>
-  <si>
-    <t>0.9.0</t>
-  </si>
-  <si>
-    <t>0.8.1</t>
-  </si>
-  <si>
-    <t>0.0.1</t>
   </si>
   <si>
     <t>1.5.0</t>
@@ -1005,6 +1005,40 @@
     <t>* Define process for reviewing asking for credits from CSPs
 * Define frequency of review, etc.
 10*Ceil(x/2)</t>
+  </si>
+  <si>
+    <t>* Weighted sum
+	TCO (score ×3),
+	Vendor scoring (score ×3),
+	Decision document (score ×3),
+	Rules established (score ×1).
+  Max Raw Score (29)
+* TCO_Analysis - Total Cost of Ownership analysis performed
+  (0=None, 1=High-level, 2=Detailed, 3=Validated with Finance)
+* Vendor_Scored - Vendor options scored against criteria
+  (0=None, 1=Informal, 2=Structured scorecard, 3=Multi-stakeholder RFP)
+* Decision_Doc - Build vs Buy decision formally documented and approved
+  (0=No, 1=Informal note, 2=Formal doc, 3=Exec-approved+reviewed)
+* Rules_Est - Guiding rules / policy established for future decsions
+  (0=No rules, 1=Draft, 2=Published+Enforced)
+* Output Range (0 - Max Raw)</t>
+  </si>
+  <si>
+    <t>* Weighted sum
+  Env coverage (score x4),
+  Data Integration (score x4),
+  Tag Config (score x2),
+  Config Doc (score x2).
+  Max raw (52)
+* Env_Coverage - % of cloud environments covered by deployed tools
+  (0=0%, 1&lt;50%, 2=50-79%, 3=80-94%, 4=95-99%, 5=100%)
+* Data_Integration - Data sources integrated (billing, usage, tags, business context)
+  (0=None, 1=Billing Only, 2=+Usage, 3=+Tags, 4=+Business context, 5=All+Automated)
+* Tag_Config - Tag/allocation rules configured and enforced tool
+  (0=No, 1=Partial manual, 2=Full manual, 3=Automated enforcement)
+* Config_Doc - Tool configuration documented and version-controlled
+  (0=No rules, 1=Informal, 2=Documented, 3=Version-controlled+Reviewed)
+* Output Range (0-52)</t>
   </si>
   <si>
     <t>* Define communication pathways between FinOps and the business
@@ -1279,15 +1313,15 @@
 * Review data with stakeholders when metrics exceed acceptable thresholds in either direction
 * Incorporate metric reviews into the decision making processes of stakeholder departments
 * The FinOps team should periodically publish an analysis of major changes in the metrics dashboards
-as well as facilitate reviews of metrics, adoption data, modifications, and KPI refreshes
+  as well as facilitate reviews of metrics, adoption data, modifications, and KPI refreshes
 10*Ceil(x/4)</t>
   </si>
   <si>
     <t>* Scenario plan for which metric values will drive the next decisions, behaviors, or outcomes needed
 * Investigate root causes for changes in metric values to determine next steps
 * Add to the backlog which actions are required to get unit metrics to a desired level
-* Unit economics influence the decisions in build vs buy, architecture design,
- workload placement, migration, sourcing, pricing, etc.
+* Unit economics influence the decisions in build vs buy, architecture design, workload placement,
+  migration, sourcing, pricing, etc.
 10*Ceil(x/4)</t>
   </si>
   <si>
@@ -1303,16 +1337,22 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1-2 completed'}, {'Score': 8, 'Condition': 'items 1-3 completed'}, {'Score': 10, 'Condition': 'items 1-4 completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Defined'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': None}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Defined'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No rules established'}, {'Score': 10, 'Condition': 'Published policy'}]</t>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-8)'}, {'Score': 4, 'Condition': 'Developing, Score Range (9-17)'}, {'Score': 7, 'Condition': 'Established, Score Range (18-24)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (25-29)'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-15)'}, {'Score': 4, 'Condition': 'Developing, Score Range (16-31)'}, {'Score': 7, 'Condition': 'Established, Score Range (32-44)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (45-52)'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 6, 'Condition': '3 items completed'}, {'Score': 8, 'Condition': '4 items completed'}, {'Score': 10, 'Condition': '5 items completed'}]</t>
@@ -1390,13 +1430,16 @@
     <t>0: No items completed</t>
   </si>
   <si>
+    <t>0: Not done</t>
+  </si>
+  <si>
     <t>0: None</t>
   </si>
   <si>
-    <t>0: Not done</t>
-  </si>
-  <si>
-    <t>0: No rules established</t>
+    <t>0: Low Maturity. Score Range (0-8)</t>
+  </si>
+  <si>
+    <t>0: Low Maturity. Score Range (0-15)</t>
   </si>
   <si>
     <t>0: No executive sponsor identified</t>
@@ -2759,7 +2802,7 @@
         <v>317</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2791,7 +2834,7 @@
         <v>318</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2823,7 +2866,7 @@
         <v>319</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2846,7 +2889,7 @@
         <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -2855,7 +2898,7 @@
         <v>320</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2878,7 +2921,7 @@
         <v>180</v>
       </c>
       <c r="E6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2887,7 +2930,7 @@
         <v>321</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2915,10 +2958,10 @@
         <v>311</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -2944,10 +2987,10 @@
         <v>311</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -2973,10 +3016,10 @@
         <v>311</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -3008,7 +3051,7 @@
         <v>322</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -3034,10 +3077,10 @@
         <v>311</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -3068,7 +3111,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -3094,10 +3137,10 @@
         <v>311</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3123,10 +3166,10 @@
         <v>311</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3152,10 +3195,10 @@
         <v>311</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3181,10 +3224,10 @@
         <v>311</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3210,10 +3253,10 @@
         <v>311</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3238,13 +3281,13 @@
         <v>192</v>
       </c>
       <c r="E18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3267,13 +3310,16 @@
         <v>193</v>
       </c>
       <c r="E19" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
+      <c r="G19" s="1" t="s">
+        <v>323</v>
+      </c>
       <c r="H19" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3296,13 +3342,16 @@
         <v>194</v>
       </c>
       <c r="E20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3331,10 +3380,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3357,13 +3406,13 @@
         <v>196</v>
       </c>
       <c r="E22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3394,10 +3443,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3426,10 +3475,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3458,10 +3507,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3484,16 +3533,16 @@
         <v>200</v>
       </c>
       <c r="E26" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3522,10 +3571,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3548,16 +3597,16 @@
         <v>202</v>
       </c>
       <c r="E28" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3585,10 +3634,10 @@
         <v>311</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3614,10 +3663,10 @@
         <v>311</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3646,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3672,10 +3721,10 @@
         <v>311</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3701,10 +3750,10 @@
         <v>311</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3733,7 +3782,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -3758,13 +3807,13 @@
         <v>209</v>
       </c>
       <c r="E35" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -3787,16 +3836,16 @@
         <v>210</v>
       </c>
       <c r="E36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -3819,16 +3868,16 @@
         <v>211</v>
       </c>
       <c r="E37" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F37">
         <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -3851,16 +3900,16 @@
         <v>212</v>
       </c>
       <c r="E38" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -3893,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -3922,10 +3971,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -3954,7 +4003,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -3977,13 +4026,13 @@
         <v>216</v>
       </c>
       <c r="E42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -4006,13 +4055,13 @@
         <v>217</v>
       </c>
       <c r="E43" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -4035,13 +4084,13 @@
         <v>218</v>
       </c>
       <c r="E44" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -4067,10 +4116,10 @@
         <v>311</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -4096,10 +4145,10 @@
         <v>311</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4128,10 +4177,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4157,10 +4206,10 @@
         <v>311</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4186,10 +4235,10 @@
         <v>311</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4215,10 +4264,10 @@
         <v>311</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4249,7 +4298,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4275,10 +4324,10 @@
         <v>311</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4304,10 +4353,10 @@
         <v>311</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4336,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4362,10 +4411,10 @@
         <v>311</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4391,10 +4440,10 @@
         <v>311</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4425,7 +4474,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4454,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4477,13 +4526,13 @@
         <v>233</v>
       </c>
       <c r="E59" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4506,13 +4555,13 @@
         <v>234</v>
       </c>
       <c r="E60" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4535,13 +4584,13 @@
         <v>235</v>
       </c>
       <c r="E61" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4570,10 +4619,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4601,10 +4650,10 @@
         <v>311</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4633,7 +4682,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4662,7 +4711,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4688,10 +4737,10 @@
         <v>311</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4717,10 +4766,10 @@
         <v>311</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -4746,10 +4795,10 @@
         <v>311</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -4780,10 +4829,10 @@
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -4812,10 +4861,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -4844,10 +4893,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -4876,10 +4925,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -4908,10 +4957,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -4940,10 +4989,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -4966,13 +5015,13 @@
         <v>249</v>
       </c>
       <c r="E75" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -5003,10 +5052,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -5035,10 +5084,10 @@
         <v>1</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -5067,7 +5116,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -5090,13 +5139,13 @@
         <v>253</v>
       </c>
       <c r="E79" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F79">
         <v>0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -5119,13 +5168,13 @@
         <v>254</v>
       </c>
       <c r="E80" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F80">
         <v>0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5154,10 +5203,10 @@
         <v>1</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5180,13 +5229,13 @@
         <v>256</v>
       </c>
       <c r="E82" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F82">
         <v>0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5211,13 +5260,13 @@
         <v>257</v>
       </c>
       <c r="E83" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F83">
         <v>0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5240,13 +5289,13 @@
         <v>258</v>
       </c>
       <c r="E84" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F84">
         <v>0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5269,13 +5318,13 @@
         <v>259</v>
       </c>
       <c r="E85" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F85">
         <v>0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5304,7 +5353,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5327,13 +5376,13 @@
         <v>261</v>
       </c>
       <c r="E87" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F87">
         <v>0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5362,10 +5411,10 @@
         <v>1</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5394,10 +5443,10 @@
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5420,13 +5469,13 @@
         <v>264</v>
       </c>
       <c r="E90" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F90">
         <v>0</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5455,7 +5504,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5483,10 +5532,10 @@
         <v>311</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5515,10 +5564,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5547,10 +5596,10 @@
         <v>1</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5576,10 +5625,10 @@
         <v>311</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -5608,7 +5657,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -5634,10 +5683,10 @@
         <v>311</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -5663,10 +5712,10 @@
         <v>311</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -5693,13 +5742,13 @@
         <v>273</v>
       </c>
       <c r="E99" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F99">
         <v>0</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -5722,13 +5771,13 @@
         <v>274</v>
       </c>
       <c r="E100" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F100">
         <v>0</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -5751,13 +5800,13 @@
         <v>275</v>
       </c>
       <c r="E101" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F101">
         <v>0</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -5780,13 +5829,13 @@
         <v>276</v>
       </c>
       <c r="E102" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F102">
         <v>0</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -5815,7 +5864,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -5838,13 +5887,13 @@
         <v>278</v>
       </c>
       <c r="E104" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -5875,7 +5924,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -5904,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -5930,10 +5979,10 @@
         <v>311</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -5959,10 +6008,10 @@
         <v>311</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -5988,10 +6037,10 @@
         <v>311</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -6017,10 +6066,10 @@
         <v>311</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
@@ -6045,13 +6094,13 @@
         <v>285</v>
       </c>
       <c r="E111" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F111">
         <v>0</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -6080,10 +6129,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -6112,7 +6161,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -6141,10 +6190,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -6173,7 +6222,7 @@
         <v>1</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6202,10 +6251,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6236,10 +6285,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6268,10 +6317,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6300,10 +6349,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -6332,10 +6381,10 @@
         <v>1</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -6364,10 +6413,10 @@
         <v>1</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -6396,7 +6445,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -6425,10 +6474,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -6459,10 +6508,10 @@
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -6491,10 +6540,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -6523,10 +6572,10 @@
         <v>1</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
@@ -6555,10 +6604,10 @@
         <v>1</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
@@ -6587,10 +6636,10 @@
         <v>1</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
@@ -6619,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
@@ -6646,13 +6695,13 @@
         <v>304</v>
       </c>
       <c r="E130" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F130">
         <v>0</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -6675,13 +6724,13 @@
         <v>305</v>
       </c>
       <c r="E131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F131">
         <v>0</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I131">
         <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
@@ -6704,13 +6753,13 @@
         <v>306</v>
       </c>
       <c r="E132" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F132">
         <v>0</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I132">
         <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
@@ -6739,7 +6788,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="I133">
         <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
@@ -6762,13 +6811,13 @@
         <v>308</v>
       </c>
       <c r="E134" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F134">
         <v>0</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I134">
         <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
@@ -6826,46 +6875,46 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
-      <formula1>"0: No rules established,10: Published policy"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-8),4: Developing. Score Range (9-17),7: Established. Score Range (18-24),10: Optimizing. Score Range (25-29)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-15),4: Developing. Score Range (16-31),7: Established. Score Range (32-44),10: Optimizing. Score Range (45-52)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
@@ -6892,19 +6941,19 @@
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
       <formula1>"0: Not done,10: Done and clearly defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
       <formula1>"0: Not done,10: Defined"</formula1>
@@ -6940,40 +6989,40 @@
       <formula1>"0: None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
@@ -6994,7 +7043,7 @@
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
       <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
@@ -7003,13 +7052,13 @@
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
@@ -7081,7 +7130,7 @@
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
@@ -7090,16 +7139,16 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
       <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
       <formula1>"0: None"</formula1>
@@ -7126,16 +7175,16 @@
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H110">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H111">
       <formula1>"0: None"</formula1>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="275">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -160,45 +160,12 @@
     <t>Prioritize Actions &amp; Publish Roadmap</t>
   </si>
   <si>
-    <t>Reassess Progress &amp; Update Priorities</t>
-  </si>
-  <si>
-    <t>Assess Skills &amp; Training Needs</t>
-  </si>
-  <si>
-    <t>Develop Role-Based Learning Content</t>
-  </si>
-  <si>
-    <t>Offer Certifications &amp; Informal Learning</t>
-  </si>
-  <si>
     <t>Leverage Vendor Training Resources</t>
   </si>
   <si>
-    <t>Track Training Impact &amp; Refresh Content</t>
-  </si>
-  <si>
     <t>Define Org Model &amp; Budget</t>
   </si>
   <si>
-    <t>Create Implementation Roadmap</t>
-  </si>
-  <si>
-    <t>Integrate Cost Data in Workflows</t>
-  </si>
-  <si>
-    <t>Publish FinOps KPIs</t>
-  </si>
-  <si>
-    <t>Drive Stakeholder Engagement</t>
-  </si>
-  <si>
-    <t>Automate Tasks &amp; Review Maturity</t>
-  </si>
-  <si>
-    <t>Assess Tooling Needs &amp; Criteria</t>
-  </si>
-  <si>
     <t>Evaluate Build vs Buy Options</t>
   </si>
   <si>
@@ -208,9 +175,6 @@
     <t>Train Users &amp; Integrate Data</t>
   </si>
   <si>
-    <t>Monitor Adoption &amp; Iterate Tools</t>
-  </si>
-  <si>
     <t>Establish Cross-Team Collab</t>
   </si>
   <si>
@@ -229,36 +193,15 @@
     <t>Drive Adoption &amp; Resolve Conflicts</t>
   </si>
   <si>
-    <t>Map Invoices to Allocation Model</t>
-  </si>
-  <si>
-    <t>Reconcile Rates &amp; Track Completion</t>
-  </si>
-  <si>
     <t>Design Chargeback with Finance</t>
   </si>
   <si>
-    <t>Automate Chargeback Data Flows</t>
-  </si>
-  <si>
-    <t>Distribute Reports &amp; Track Accuracy</t>
-  </si>
-  <si>
     <t>Resolve Variances &amp; Increase Coverage</t>
   </si>
   <si>
     <t>Establish Executive Sponsorship</t>
   </si>
   <si>
-    <t>Define Decision Rights &amp; Guardrails</t>
-  </si>
-  <si>
-    <t>Build Multi-Year Investment Forecast</t>
-  </si>
-  <si>
-    <t>Establish Decision Support Cadence</t>
-  </si>
-  <si>
     <t>Establish Architecture Review Process</t>
   </si>
   <si>
@@ -268,87 +211,30 @@
     <t>Estimate Trade-Offs &amp; Document Cases</t>
   </si>
   <si>
-    <t>Implement Iteratively &amp; Measure Results</t>
-  </si>
-  <si>
-    <t>Publish Benefits &amp; Update References</t>
-  </si>
-  <si>
-    <t>Strengthen Architecture Collaboration</t>
-  </si>
-  <si>
-    <t>Create Workload Selection Criteria</t>
-  </si>
-  <si>
-    <t>Define Success Criteria &amp; Scope</t>
-  </si>
-  <si>
     <t>Enforce Tagging at Onboarding</t>
   </si>
   <si>
-    <t>Align Timelines with Budgets</t>
-  </si>
-  <si>
-    <t>Start with Lower Environments</t>
-  </si>
-  <si>
-    <t>Review Outcomes &amp; Adjust Patterns</t>
-  </si>
-  <si>
     <t>Inventory Licenses &amp; Map Resources</t>
   </si>
   <si>
-    <t>Document Licensing Models</t>
-  </si>
-  <si>
-    <t>Integrate Billing with Procurement</t>
-  </si>
-  <si>
     <t>Validate Utilization &amp; Remediate</t>
   </si>
   <si>
-    <t>Influence Workload Design Choices</t>
-  </si>
-  <si>
-    <t>Publish License Spend &amp; Utilization</t>
-  </si>
-  <si>
     <t>Document Commitment Strategy</t>
   </si>
   <si>
     <t>Build Commitment Analysis Process</t>
   </si>
   <si>
-    <t>Purchase Commitments Regularly</t>
-  </si>
-  <si>
-    <t>Track ROI &amp; Notify Owners</t>
-  </si>
-  <si>
-    <t>Allocate Upfront Costs Transparently</t>
-  </si>
-  <si>
     <t>Leverage Spot &amp; Negotiated Discounts</t>
   </si>
   <si>
-    <t>Define Optimization Strategy</t>
-  </si>
-  <si>
     <t>Inventory &amp; Classify Workloads</t>
   </si>
   <si>
     <t>Collect Metrics &amp; Identify Candidates</t>
   </si>
   <si>
-    <t>Partner on Scheduling Actions</t>
-  </si>
-  <si>
-    <t>Gamify Adoption &amp; Celebrate Wins</t>
-  </si>
-  <si>
-    <t>Track KPIs &amp; Document Playbooks</t>
-  </si>
-  <si>
     <t>Define Metadata &amp; Hierarchy Strategy</t>
   </si>
   <si>
@@ -367,9 +253,6 @@
     <t>Automate Tagging &amp; Enforcement</t>
   </si>
   <si>
-    <t>Iterate Strategies &amp; Communicate</t>
-  </si>
-  <si>
     <t>Configure Cost Spike Detection</t>
   </si>
   <si>
@@ -379,105 +262,39 @@
     <t>Automate Alert Routing</t>
   </si>
   <si>
-    <t>Record Anomaly Context &amp; Timeline</t>
-  </si>
-  <si>
-    <t>Analyze Root Causes &amp; Fix Issues</t>
-  </si>
-  <si>
     <t>Track Metrics &amp; Avoidance Rates</t>
   </si>
   <si>
-    <t>Tune Thresholds to Reduce Noise</t>
-  </si>
-  <si>
-    <t>Inventory All Data Sources</t>
-  </si>
-  <si>
-    <t>Choose Data Landing Tooling</t>
-  </si>
-  <si>
-    <t>Create Landing Zones &amp; Controls</t>
-  </si>
-  <si>
     <t>Define Data Granularity &amp; Frequency</t>
   </si>
   <si>
-    <t>Document Normalization Rules</t>
-  </si>
-  <si>
     <t>Implement Data Quality Checks</t>
   </si>
   <si>
     <t>Build Ingestion Anomaly Dashboards</t>
   </si>
   <si>
-    <t>Optimize Pipelines for Timeliness</t>
-  </si>
-  <si>
     <t>Define ingestion frequency; include mandatory metadata.</t>
   </si>
   <si>
-    <t>Gather Requirements &amp; Define KPIs</t>
-  </si>
-  <si>
     <t>Enrich Billing with Business Logic</t>
   </si>
   <si>
     <t>Build Dashboards for All Views</t>
   </si>
   <si>
-    <t>Publish Documentation &amp; Support</t>
-  </si>
-  <si>
     <t>Embed Reports in Workflows</t>
   </si>
   <si>
-    <t>Track Adoption &amp; Manage Changes</t>
-  </si>
-  <si>
-    <t>Iterate Based on Feedback</t>
-  </si>
-  <si>
-    <t>Select KPIs &amp; Measurement Scope</t>
-  </si>
-  <si>
-    <t>Validate Tagging for Comparability</t>
-  </si>
-  <si>
-    <t>Choose Internal vs External Benchmarks</t>
-  </si>
-  <si>
-    <t>Stand Up Internal Benchmarking</t>
-  </si>
-  <si>
     <t>Track Trends &amp; Compare Over Time</t>
   </si>
   <si>
-    <t>Translate Gaps to Initiatives</t>
-  </si>
-  <si>
     <t>Define Budgeting Strategy</t>
   </si>
   <si>
     <t>Integrate Rolling Forecasts</t>
   </si>
   <si>
-    <t>Increase Shared Cost Coverage</t>
-  </si>
-  <si>
-    <t>Publish Budget vs Actual Reports</t>
-  </si>
-  <si>
-    <t>Automate Budget Threshold Alerts</t>
-  </si>
-  <si>
-    <t>Review &amp; Adapt Budget Strategy</t>
-  </si>
-  <si>
-    <t>Establish Forecasting Approach</t>
-  </si>
-  <si>
     <t>Collect Business Drivers Regularly</t>
   </si>
   <si>
@@ -532,21 +349,9 @@
     <t>Communicate Unit Cost Wins</t>
   </si>
   <si>
-    <t>Draft Cloud Financial Policies</t>
-  </si>
-  <si>
-    <t>Publish Guidelines &amp; Guardrails</t>
-  </si>
-  <si>
-    <t>Educate Stakeholders on Policy</t>
-  </si>
-  <si>
     <t>Monitor Compliance &amp; Report Breaches</t>
   </si>
   <si>
-    <t>Iterate Policies Based on Feedback</t>
-  </si>
-  <si>
     <t>113</t>
   </si>
   <si>
@@ -559,45 +364,12 @@
     <t>116</t>
   </si>
   <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>097</t>
-  </si>
-  <si>
-    <t>098</t>
-  </si>
-  <si>
-    <t>099</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
-    <t>101</t>
-  </si>
-  <si>
     <t>091</t>
   </si>
   <si>
-    <t>092</t>
-  </si>
-  <si>
-    <t>093</t>
-  </si>
-  <si>
-    <t>094</t>
-  </si>
-  <si>
-    <t>095</t>
-  </si>
-  <si>
-    <t>096</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
     <t>125</t>
   </si>
   <si>
@@ -607,9 +379,6 @@
     <t>127</t>
   </si>
   <si>
-    <t>128</t>
-  </si>
-  <si>
     <t>129</t>
   </si>
   <si>
@@ -628,36 +397,15 @@
     <t>134</t>
   </si>
   <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
     <t>109</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>112</t>
   </si>
   <si>
     <t>136</t>
   </si>
   <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
     <t>061</t>
   </si>
   <si>
@@ -667,87 +415,30 @@
     <t>063</t>
   </si>
   <si>
-    <t>064</t>
-  </si>
-  <si>
-    <t>065</t>
-  </si>
-  <si>
-    <t>066</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>073</t>
   </si>
   <si>
-    <t>074</t>
-  </si>
-  <si>
-    <t>075</t>
-  </si>
-  <si>
     <t>076</t>
   </si>
   <si>
-    <t>077</t>
-  </si>
-  <si>
-    <t>078</t>
-  </si>
-  <si>
     <t>079</t>
   </si>
   <si>
     <t>080</t>
   </si>
   <si>
-    <t>081</t>
-  </si>
-  <si>
-    <t>082</t>
-  </si>
-  <si>
-    <t>083</t>
-  </si>
-  <si>
     <t>084</t>
   </si>
   <si>
-    <t>067</t>
-  </si>
-  <si>
     <t>068</t>
   </si>
   <si>
     <t>069</t>
   </si>
   <si>
-    <t>070</t>
-  </si>
-  <si>
-    <t>071</t>
-  </si>
-  <si>
-    <t>072</t>
-  </si>
-  <si>
     <t>009</t>
   </si>
   <si>
@@ -766,9 +457,6 @@
     <t>014</t>
   </si>
   <si>
-    <t>015</t>
-  </si>
-  <si>
     <t>023</t>
   </si>
   <si>
@@ -778,105 +466,39 @@
     <t>025</t>
   </si>
   <si>
-    <t>026</t>
-  </si>
-  <si>
-    <t>027</t>
-  </si>
-  <si>
     <t>028</t>
   </si>
   <si>
-    <t>029</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
     <t>004</t>
   </si>
   <si>
-    <t>005</t>
-  </si>
-  <si>
     <t>006</t>
   </si>
   <si>
     <t>007</t>
   </si>
   <si>
-    <t>008</t>
-  </si>
-  <si>
     <t>135</t>
   </si>
   <si>
-    <t>016</t>
-  </si>
-  <si>
     <t>017</t>
   </si>
   <si>
     <t>018</t>
   </si>
   <si>
-    <t>019</t>
-  </si>
-  <si>
     <t>020</t>
   </si>
   <si>
-    <t>021</t>
-  </si>
-  <si>
-    <t>022</t>
-  </si>
-  <si>
-    <t>049</t>
-  </si>
-  <si>
-    <t>050</t>
-  </si>
-  <si>
-    <t>051</t>
-  </si>
-  <si>
-    <t>052</t>
-  </si>
-  <si>
     <t>053</t>
   </si>
   <si>
-    <t>054</t>
-  </si>
-  <si>
     <t>043</t>
   </si>
   <si>
     <t>044</t>
   </si>
   <si>
-    <t>045</t>
-  </si>
-  <si>
-    <t>046</t>
-  </si>
-  <si>
-    <t>047</t>
-  </si>
-  <si>
-    <t>048</t>
-  </si>
-  <si>
-    <t>037</t>
-  </si>
-  <si>
     <t>038</t>
   </si>
   <si>
@@ -931,40 +553,16 @@
     <t>060</t>
   </si>
   <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
     <t>105</t>
   </si>
   <si>
-    <t>106</t>
-  </si>
-  <si>
     <t>1.0.0</t>
   </si>
   <si>
-    <t>0.7.0</t>
-  </si>
-  <si>
-    <t>0.8.0</t>
-  </si>
-  <si>
     <t>1.7.0</t>
   </si>
   <si>
-    <t>2.0.0</t>
-  </si>
-  <si>
-    <t>0.0.1</t>
-  </si>
-  <si>
-    <t>0.7.1</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>1.5.0</t>
@@ -996,22 +594,16 @@
 4. Work is then scheduled in a roadmap with deadlines that can be tracked at the leadership level</t>
   </si>
   <si>
-    <t>* Schedule a cadence to report progress outcomes to key stakeholders.
-* Create reporting to show progress on key outcomes across all maturity initiatives.
-* After successful outcomes are achieved, move on to the next prioritized item in the roadmap.
-* Periodically reevaluate the gap analysis and priority list based on lessons learned and new business goals.</t>
-  </si>
-  <si>
     <t>* Define process for reviewing asking for credits from CSPs
 * Define frequency of review, etc.
 10*Ceil(x/2)</t>
   </si>
   <si>
-    <t>* Weighted sum
-	TCO (score ×3),
-	Vendor scoring (score ×3),
-	Decision document (score ×3),
-	Rules established (score ×1).
+    <t xml:space="preserve">* Weighted sum
+  TCO (score ×3),
+  Vendor scoring (score ×3),
+  Decision document (score ×3),
+  Rules established (score ×1).
   Max Raw Score (29)
 * TCO_Analysis - Total Cost of Ownership analysis performed
   (0=None, 1=High-level, 2=Detailed, 3=Validated with Finance)
@@ -1021,7 +613,8 @@
   (0=No, 1=Informal note, 2=Formal doc, 3=Exec-approved+reviewed)
 * Rules_Est - Guiding rules / policy established for future decsions
   (0=No rules, 1=Draft, 2=Published+Enforced)
-* Output Range (0 - Max Raw)</t>
+* Output Range (0 - Max Raw)
+</t>
   </si>
   <si>
     <t>* Weighted sum
@@ -1089,24 +682,6 @@
 10*Ceil(x/3)</t>
   </si>
   <si>
-    <t>* Document decision rights and approval authority for technology spend
-* Define and publish spend guardrails with named owners
-* Establish escalation path for spend exceptions
-10*Ceil(x/3)</t>
-  </si>
-  <si>
-    <t>* Inventory vendor commitments across technology categories (cloud, SaaS, data center, AI)
-* Create a multi-year forecast incorporating renewal timelines and growth projections
-* Incorporate transition and modernization costs into the investment plan
-10*Ceil(x/3)</t>
-  </si>
-  <si>
-    <t>* Define a regular review cadence for technology investment decisions
-* Deliver cost and outcome comparisons for competing initiatives at reviews
-* Track and report action follow-through from investment decisions
-10*Ceil(x/3)</t>
-  </si>
-  <si>
     <t>* Define process to address notifications from CSPs
 * Define cadence for review
 * Define exception criteria
@@ -1337,18 +912,12 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1-2 completed'}, {'Score': 8, 'Condition': 'items 1-3 completed'}, {'Score': 10, 'Condition': 'items 1-4 completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Completed'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Defined'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': None}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-8)'}, {'Score': 4, 'Condition': 'Developing, Score Range (9-17)'}, {'Score': 7, 'Condition': 'Established, Score Range (18-24)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (25-29)'}]</t>
   </si>
   <si>
@@ -1433,40 +1002,40 @@
     <t>0: Not done</t>
   </si>
   <si>
+    <t>0: Low Maturity. Score Range (0-8)</t>
+  </si>
+  <si>
+    <t>0: Low Maturity. Score Range (0-15)</t>
+  </si>
+  <si>
+    <t>0: No executive sponsor identified</t>
+  </si>
+  <si>
+    <t>0: Does not exist</t>
+  </si>
+  <si>
+    <t>0: No documented method</t>
+  </si>
+  <si>
+    <t>0: 0%</t>
+  </si>
+  <si>
+    <t>0: No teardown/shutdown policy</t>
+  </si>
+  <si>
+    <t>0: No alerting to any owners</t>
+  </si>
+  <si>
+    <t>0: Never</t>
+  </si>
+  <si>
+    <t>0: No alerting in workflow tools</t>
+  </si>
+  <si>
+    <t>0: No review of trends</t>
+  </si>
+  <si>
     <t>0: None</t>
-  </si>
-  <si>
-    <t>0: Low Maturity. Score Range (0-8)</t>
-  </si>
-  <si>
-    <t>0: Low Maturity. Score Range (0-15)</t>
-  </si>
-  <si>
-    <t>0: No executive sponsor identified</t>
-  </si>
-  <si>
-    <t>0: Does not exist</t>
-  </si>
-  <si>
-    <t>0: No documented method</t>
-  </si>
-  <si>
-    <t>0: 0%</t>
-  </si>
-  <si>
-    <t>0: No teardown/shutdown policy</t>
-  </si>
-  <si>
-    <t>0: No alerting to any owners</t>
-  </si>
-  <si>
-    <t>0: Never</t>
-  </si>
-  <si>
-    <t>0: No alerting in workflow tools</t>
-  </si>
-  <si>
-    <t>0: No review of trends</t>
   </si>
   <si>
     <t>0: No alerting</t>
@@ -2372,14 +1941,14 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2">
-        <f>SUM(Scoring!F2:F134)</f>
+        <f>SUM(Scoring!F2:F69)</f>
         <v>0</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2">
-        <f>SUM(Scoring!I2:I134)/A2</f>
+        <f>SUM(Scoring!I2:I69)/A2</f>
         <v>0</v>
       </c>
       <c r="D2">
@@ -2400,10 +1969,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U5">
-        <f>SUMIF(Scoring!J2:J134,A5,Scoring!I2:I134)/SUMIF(Scoring!J2:J134,A5,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!J2:J69,A5,Scoring!I2:I69)/SUMIF(Scoring!J2:J69,A5,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2412,10 +1981,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="U6">
-        <f>SUMIF(Scoring!J2:J134,A6,Scoring!I2:I134)/SUMIF(Scoring!J2:J134,A6,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!J2:J69,A6,Scoring!I2:I69)/SUMIF(Scoring!J2:J69,A6,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2424,10 +1993,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="U7">
-        <f>SUMIF(Scoring!J2:J134,A7,Scoring!I2:I134)/SUMIF(Scoring!J2:J134,A7,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!J2:J69,A7,Scoring!I2:I69)/SUMIF(Scoring!J2:J69,A7,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2436,10 +2005,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="U8">
-        <f>SUMIF(Scoring!J2:J134,A8,Scoring!I2:I134)/SUMIF(Scoring!J2:J134,A8,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!J2:J69,A8,Scoring!I2:I69)/SUMIF(Scoring!J2:J69,A8,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2462,10 +2031,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <f>SUMIF(Scoring!K2:K134,A12,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A12,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A12,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A12,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2474,10 +2043,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <f>SUMIF(Scoring!K2:K134,A13,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A13,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A13,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A13,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2486,10 +2055,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="U14">
-        <f>SUMIF(Scoring!K2:K134,A14,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A14,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A14,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A14,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2498,10 +2067,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U15">
-        <f>SUMIF(Scoring!K2:K134,A15,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A15,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A15,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A15,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2510,10 +2079,10 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U16">
-        <f>SUMIF(Scoring!K2:K134,A16,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A16,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A16,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A16,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2522,10 +2091,10 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <f>SUMIF(Scoring!K2:K134,A17,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A17,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A17,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A17,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2534,10 +2103,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U18">
-        <f>SUMIF(Scoring!K2:K134,A18,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A18,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A18,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A18,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2546,10 +2115,10 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <f>SUMIF(Scoring!K2:K134,A19,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A19,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A19,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A19,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2558,10 +2127,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <f>SUMIF(Scoring!K2:K134,A20,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A20,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A20,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A20,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2570,10 +2139,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U21">
-        <f>SUMIF(Scoring!K2:K134,A21,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A21,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A21,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A21,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2582,10 +2151,10 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <f>SUMIF(Scoring!K2:K134,A22,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A22,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A22,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A22,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2597,7 +2166,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <f>SUMIF(Scoring!K2:K134,A23,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A23,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A23,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A23,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2606,10 +2175,10 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U24">
-        <f>SUMIF(Scoring!K2:K134,A24,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A24,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A24,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A24,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2618,10 +2187,10 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U25">
-        <f>SUMIF(Scoring!K2:K134,A25,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A25,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A25,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A25,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2630,10 +2199,10 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U26">
-        <f>SUMIF(Scoring!K2:K134,A26,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A26,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A26,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A26,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2645,7 +2214,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <f>SUMIF(Scoring!K2:K134,A27,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A27,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A27,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A27,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2654,10 +2223,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U28">
-        <f>SUMIF(Scoring!K2:K134,A28,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A28,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A28,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A28,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2666,10 +2235,10 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U29">
-        <f>SUMIF(Scoring!K2:K134,A29,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A29,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A29,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A29,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2678,10 +2247,10 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <f>SUMIF(Scoring!K2:K134,A30,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A30,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A30,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A30,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2693,7 +2262,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <f>SUMIF(Scoring!K2:K134,A31,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A31,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A31,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A31,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2702,10 +2271,10 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U32">
-        <f>SUMIF(Scoring!K2:K134,A32,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A32,Scoring!F2:F134)</f>
+        <f>SUMIF(Scoring!K2:K69,A32,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A32,Scoring!F2:F69)</f>
         <v>0</v>
       </c>
     </row>
@@ -2728,7 +2297,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K134"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -2790,19 +2359,19 @@
         <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>176</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>309</v>
+        <v>179</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>317</v>
+        <v>183</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>398</v>
+        <v>258</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2822,19 +2391,19 @@
         <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>309</v>
+        <v>179</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>318</v>
+        <v>184</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2854,19 +2423,19 @@
         <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>309</v>
+        <v>179</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>319</v>
+        <v>185</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2886,19 +2455,19 @@
         <v>46</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" t="s">
         <v>179</v>
       </c>
-      <c r="E5" t="s">
-        <v>309</v>
-      </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>320</v>
+        <v>186</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2913,24 +2482,26 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C6" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" t="s">
         <v>180</v>
       </c>
-      <c r="E6" t="s">
-        <v>310</v>
-      </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>321</v>
+        <v>187</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2940,28 +2511,28 @@
         <v>7</v>
       </c>
       <c r="K6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>181</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -2971,26 +2542,31 @@
         <v>7</v>
       </c>
       <c r="K7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="C8" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>182</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
-        <v>311</v>
+        <v>181</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
+      <c r="G8" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="H8" s="1" t="s">
-        <v>400</v>
+        <v>261</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -3000,7 +2576,7 @@
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3010,16 +2586,19 @@
         <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>311</v>
+        <v>179</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
+      <c r="G9" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="H9" s="1" t="s">
-        <v>400</v>
+        <v>262</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -3029,7 +2608,7 @@
         <v>7</v>
       </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3039,19 +2618,19 @@
         <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>184</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>322</v>
+        <v>190</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -3061,26 +2640,31 @@
         <v>7</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="C11" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>311</v>
+        <v>179</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
+      <c r="G11" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="H11" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -3090,28 +2674,29 @@
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>186</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>312</v>
+        <v>179</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
+      <c r="G12" s="1" t="s">
+        <v>192</v>
+      </c>
       <c r="H12" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -3121,7 +2706,7 @@
         <v>7</v>
       </c>
       <c r="K12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3131,16 +2716,19 @@
         <v>54</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>187</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
-        <v>311</v>
+        <v>179</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
+      <c r="G13" s="1" t="s">
+        <v>193</v>
+      </c>
       <c r="H13" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3150,7 +2738,7 @@
         <v>7</v>
       </c>
       <c r="K13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3160,16 +2748,19 @@
         <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>188</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>311</v>
+        <v>179</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
+      <c r="G14" s="1" t="s">
+        <v>194</v>
+      </c>
       <c r="H14" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3179,7 +2770,7 @@
         <v>7</v>
       </c>
       <c r="K14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3189,16 +2780,19 @@
         <v>56</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>189</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>311</v>
+        <v>179</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
+      <c r="G15" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3208,7 +2802,7 @@
         <v>7</v>
       </c>
       <c r="K15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3218,16 +2812,19 @@
         <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="E16" t="s">
-        <v>311</v>
+        <v>179</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
+      <c r="G16" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="H16" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3237,26 +2834,28 @@
         <v>7</v>
       </c>
       <c r="K16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="C17" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>191</v>
+        <v>126</v>
       </c>
       <c r="E17" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3266,28 +2865,26 @@
         <v>7</v>
       </c>
       <c r="K17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>192</v>
+        <v>127</v>
       </c>
       <c r="E18" t="s">
-        <v>310</v>
+        <v>180</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>401</v>
+        <v>260</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3297,29 +2894,28 @@
         <v>7</v>
       </c>
       <c r="K18" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C19" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>193</v>
+        <v>128</v>
       </c>
       <c r="E19" t="s">
-        <v>313</v>
+        <v>179</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="H19" s="1" t="s">
-        <v>402</v>
+        <v>263</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3329,39 +2925,40 @@
         <v>7</v>
       </c>
       <c r="K19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C20" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
-        <v>309</v>
+        <v>180</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="H20" s="1" t="s">
-        <v>403</v>
+        <v>264</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3371,29 +2968,29 @@
         <v>62</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>195</v>
+        <v>130</v>
       </c>
       <c r="E21" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>325</v>
+        <v>197</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3403,92 +3000,89 @@
         <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>196</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s">
-        <v>310</v>
+        <v>180</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>401</v>
+        <v>265</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2"/>
-      <c r="B23" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B23" s="2"/>
       <c r="C23" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>197</v>
+        <v>132</v>
       </c>
       <c r="E23" t="s">
-        <v>309</v>
+        <v>180</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>326</v>
+        <v>198</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K23" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="C24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>198</v>
+        <v>133</v>
       </c>
       <c r="E24" t="s">
-        <v>309</v>
+        <v>180</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="H24" s="1" t="s">
-        <v>399</v>
+        <v>266</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K24" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3498,61 +3092,57 @@
         <v>66</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>199</v>
+        <v>134</v>
       </c>
       <c r="E25" t="s">
-        <v>309</v>
+        <v>180</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="H25" s="1" t="s">
-        <v>399</v>
+        <v>260</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K25" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C26" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="E26" t="s">
-        <v>309</v>
+        <v>180</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="H26" s="1" t="s">
-        <v>399</v>
+        <v>260</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K26" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3562,29 +3152,26 @@
         <v>68</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>309</v>
+        <v>180</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="H27" s="1" t="s">
-        <v>399</v>
+        <v>260</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3594,60 +3181,60 @@
         <v>69</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>202</v>
+        <v>137</v>
       </c>
       <c r="E28" t="s">
-        <v>309</v>
+        <v>180</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>331</v>
+        <v>199</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K28" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>203</v>
+        <v>138</v>
       </c>
       <c r="E29" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>400</v>
+        <v>267</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K29" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3657,55 +3244,60 @@
         <v>71</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="E30" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>400</v>
+        <v>266</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K30" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C31" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
+      <c r="G31" s="1" t="s">
+        <v>200</v>
+      </c>
       <c r="H31" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K31" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3715,26 +3307,29 @@
         <v>73</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="E32" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
+      <c r="G32" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="H32" s="1" t="s">
-        <v>400</v>
+        <v>266</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K32" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3744,26 +3339,29 @@
         <v>74</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="E33" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
+      <c r="G33" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="H33" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K33" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3773,57 +3371,61 @@
         <v>75</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="E34" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
+      <c r="G34" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="H34" s="1" t="s">
-        <v>400</v>
+        <v>266</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K34" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2"/>
-      <c r="B35" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>209</v>
+        <v>144</v>
       </c>
       <c r="E35" t="s">
-        <v>309</v>
+        <v>180</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
+      <c r="G35" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="H35" s="1" t="s">
-        <v>404</v>
+        <v>266</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K35" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3833,61 +3435,63 @@
         <v>77</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>210</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
-        <v>314</v>
+        <v>180</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>332</v>
+        <v>205</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K36" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C37" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s">
-        <v>314</v>
+        <v>180</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>333</v>
+        <v>206</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K37" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3897,52 +3501,48 @@
         <v>79</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
       <c r="E38" t="s">
-        <v>314</v>
+        <v>180</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>334</v>
+        <v>207</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K38" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>213</v>
+        <v>148</v>
       </c>
       <c r="E39" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>405</v>
+        <v>268</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -3952,7 +3552,7 @@
         <v>9</v>
       </c>
       <c r="K39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3962,19 +3562,19 @@
         <v>81</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>214</v>
+        <v>149</v>
       </c>
       <c r="E40" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>335</v>
+        <v>208</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -3984,26 +3584,28 @@
         <v>9</v>
       </c>
       <c r="K40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
+      <c r="B41" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C41" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="E41" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>406</v>
+        <v>269</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -4013,7 +3615,7 @@
         <v>9</v>
       </c>
       <c r="K41" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -4023,16 +3625,19 @@
         <v>83</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>216</v>
+        <v>151</v>
       </c>
       <c r="E42" t="s">
-        <v>310</v>
+        <v>180</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>401</v>
+        <v>259</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -4042,7 +3647,7 @@
         <v>9</v>
       </c>
       <c r="K42" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -4052,16 +3657,19 @@
         <v>84</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>217</v>
+        <v>152</v>
       </c>
       <c r="E43" t="s">
-        <v>310</v>
+        <v>180</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>401</v>
+        <v>259</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -4071,7 +3679,7 @@
         <v>9</v>
       </c>
       <c r="K43" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -4081,16 +3689,16 @@
         <v>85</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>218</v>
+        <v>153</v>
       </c>
       <c r="E44" t="s">
-        <v>310</v>
+        <v>182</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>401</v>
+        <v>269</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -4100,26 +3708,31 @@
         <v>9</v>
       </c>
       <c r="K44" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
+      <c r="B45" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="C45" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>219</v>
+        <v>154</v>
       </c>
       <c r="E45" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
+      <c r="G45" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="H45" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -4129,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="K45" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -4139,16 +3752,19 @@
         <v>87</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="E46" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
+      <c r="G46" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="H46" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4158,7 +3774,7 @@
         <v>9</v>
       </c>
       <c r="K46" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -4168,19 +3784,16 @@
         <v>88</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>221</v>
+        <v>156</v>
       </c>
       <c r="E47" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="H47" s="1" t="s">
-        <v>399</v>
+        <v>270</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4190,65 +3803,71 @@
         <v>9</v>
       </c>
       <c r="K47" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
+      <c r="A48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C48" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>222</v>
+        <v>157</v>
       </c>
       <c r="E48" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>400</v>
+        <v>271</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K48" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C49" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>223</v>
+        <v>158</v>
       </c>
       <c r="E49" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>400</v>
+        <v>264</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K49" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -4258,57 +3877,60 @@
         <v>91</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>224</v>
+        <v>159</v>
       </c>
       <c r="E50" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>400</v>
+        <v>264</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K50" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>225</v>
+        <v>160</v>
       </c>
       <c r="E51" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
+      <c r="G51" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="H51" s="1" t="s">
-        <v>407</v>
+        <v>259</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K51" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -4318,26 +3940,26 @@
         <v>93</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>226</v>
+        <v>161</v>
       </c>
       <c r="E52" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>400</v>
+        <v>272</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
         <v>0</v>
       </c>
       <c r="J52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -4347,26 +3969,29 @@
         <v>94</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>227</v>
+        <v>162</v>
       </c>
       <c r="E53" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
+      <c r="G53" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="H53" s="1" t="s">
-        <v>400</v>
+        <v>266</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
         <v>0</v>
       </c>
       <c r="J53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K53" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4376,26 +4001,26 @@
         <v>95</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>228</v>
+        <v>163</v>
       </c>
       <c r="E54" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>400</v>
+        <v>273</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
         <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -4405,86 +4030,95 @@
         <v>96</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>229</v>
+        <v>164</v>
       </c>
       <c r="E55" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
+      <c r="G55" s="1" t="s">
+        <v>215</v>
+      </c>
       <c r="H55" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
         <v>0</v>
       </c>
       <c r="J55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
+      <c r="B56" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C56" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="E56" t="s">
-        <v>311</v>
+        <v>179</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
+      <c r="G56" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="H56" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
         <v>0</v>
       </c>
       <c r="J56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2"/>
-      <c r="B57" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B57" s="2"/>
       <c r="C57" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>231</v>
+        <v>166</v>
       </c>
       <c r="E57" t="s">
-        <v>312</v>
+        <v>179</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
+      <c r="G57" s="1" t="s">
+        <v>217</v>
+      </c>
       <c r="H57" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
         <v>0</v>
       </c>
       <c r="J57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K57" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -4494,26 +4128,29 @@
         <v>99</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="E58" t="s">
-        <v>312</v>
+        <v>179</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
+      <c r="G58" s="1" t="s">
+        <v>218</v>
+      </c>
       <c r="H58" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
         <v>0</v>
       </c>
       <c r="J58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K58" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -4523,26 +4160,29 @@
         <v>100</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>233</v>
+        <v>168</v>
       </c>
       <c r="E59" t="s">
-        <v>310</v>
+        <v>179</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>401</v>
+        <v>259</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
         <v>0</v>
       </c>
       <c r="J59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K59" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -4552,26 +4192,29 @@
         <v>101</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="E60" t="s">
-        <v>310</v>
+        <v>180</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>401</v>
+        <v>259</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
         <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K60" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -4581,26 +4224,26 @@
         <v>102</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="E61" t="s">
-        <v>310</v>
+        <v>180</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>401</v>
+        <v>266</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
         <v>0</v>
       </c>
       <c r="J61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K61" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -4610,60 +4253,63 @@
         <v>103</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="E62" t="s">
-        <v>312</v>
+        <v>179</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>337</v>
+        <v>221</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
         <v>0</v>
       </c>
       <c r="J62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K62" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="E63" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
+      <c r="G63" s="1" t="s">
+        <v>222</v>
+      </c>
       <c r="H63" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
         <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -4673,26 +4319,29 @@
         <v>105</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="E64" t="s">
-        <v>312</v>
+        <v>179</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
+      <c r="G64" s="1" t="s">
+        <v>223</v>
+      </c>
       <c r="H64" s="1" t="s">
-        <v>408</v>
+        <v>259</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
         <v>0</v>
       </c>
       <c r="J64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -4702,26 +4351,29 @@
         <v>106</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>239</v>
+        <v>174</v>
       </c>
       <c r="E65" t="s">
-        <v>312</v>
+        <v>179</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
+      <c r="G65" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="H65" s="1" t="s">
-        <v>407</v>
+        <v>259</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
         <v>0</v>
       </c>
       <c r="J65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -4731,26 +4383,29 @@
         <v>107</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="E66" t="s">
-        <v>311</v>
+        <v>179</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
+      <c r="G66" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="H66" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
         <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -4760,26 +4415,29 @@
         <v>108</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>241</v>
+        <v>176</v>
       </c>
       <c r="E67" t="s">
-        <v>311</v>
+        <v>179</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
+      <c r="G67" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="H67" s="1" t="s">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -4789,2076 +4447,84 @@
         <v>109</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>242</v>
+        <v>177</v>
       </c>
       <c r="E68" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>400</v>
+        <v>272</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
         <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" s="2"/>
+      <c r="A69" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="B69" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>243</v>
+        <v>178</v>
       </c>
       <c r="E69" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="H69" s="1" t="s">
-        <v>399</v>
+        <v>274</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
         <v>0</v>
       </c>
       <c r="J69" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E70" t="s">
-        <v>312</v>
-      </c>
-      <c r="F70">
-        <v>1</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="I70">
-        <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J70" t="s">
-        <v>9</v>
-      </c>
-      <c r="K70" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E71" t="s">
-        <v>312</v>
-      </c>
-      <c r="F71">
-        <v>1</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I71">
-        <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J71" t="s">
-        <v>9</v>
-      </c>
-      <c r="K71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E72" t="s">
-        <v>312</v>
-      </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="I72">
-        <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J72" t="s">
-        <v>9</v>
-      </c>
-      <c r="K72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E73" t="s">
-        <v>312</v>
-      </c>
-      <c r="F73">
-        <v>1</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="I73">
-        <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J73" t="s">
-        <v>9</v>
-      </c>
-      <c r="K73" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E74" t="s">
-        <v>312</v>
-      </c>
-      <c r="F74">
-        <v>1</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I74">
-        <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J74" t="s">
-        <v>9</v>
-      </c>
-      <c r="K74" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E75" t="s">
-        <v>310</v>
-      </c>
-      <c r="F75">
-        <v>0</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I75">
-        <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J75" t="s">
-        <v>9</v>
-      </c>
-      <c r="K75" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E76" t="s">
-        <v>312</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I76">
-        <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J76" t="s">
-        <v>9</v>
-      </c>
-      <c r="K76" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E77" t="s">
-        <v>312</v>
-      </c>
-      <c r="F77">
-        <v>1</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I77">
-        <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J77" t="s">
-        <v>9</v>
-      </c>
-      <c r="K77" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E78" t="s">
-        <v>312</v>
-      </c>
-      <c r="F78">
-        <v>1</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="I78">
-        <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J78" t="s">
-        <v>9</v>
-      </c>
-      <c r="K78" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E79" t="s">
-        <v>310</v>
-      </c>
-      <c r="F79">
-        <v>0</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I79">
-        <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J79" t="s">
-        <v>9</v>
-      </c>
-      <c r="K79" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E80" t="s">
-        <v>310</v>
-      </c>
-      <c r="F80">
-        <v>0</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I80">
-        <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J80" t="s">
-        <v>9</v>
-      </c>
-      <c r="K80" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E81" t="s">
-        <v>312</v>
-      </c>
-      <c r="F81">
-        <v>1</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I81">
-        <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J81" t="s">
-        <v>9</v>
-      </c>
-      <c r="K81" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E82" t="s">
-        <v>310</v>
-      </c>
-      <c r="F82">
-        <v>0</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I82">
-        <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J82" t="s">
-        <v>9</v>
-      </c>
-      <c r="K82" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E83" t="s">
-        <v>315</v>
-      </c>
-      <c r="F83">
-        <v>0</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I83">
-        <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J83" t="s">
-        <v>9</v>
-      </c>
-      <c r="K83" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E84" t="s">
-        <v>310</v>
-      </c>
-      <c r="F84">
-        <v>0</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I84">
-        <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J84" t="s">
-        <v>9</v>
-      </c>
-      <c r="K84" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E85" t="s">
-        <v>310</v>
-      </c>
-      <c r="F85">
-        <v>0</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I85">
-        <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J85" t="s">
-        <v>9</v>
-      </c>
-      <c r="K85" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E86" t="s">
-        <v>312</v>
-      </c>
-      <c r="F86">
-        <v>1</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="I86">
-        <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J86" t="s">
-        <v>9</v>
-      </c>
-      <c r="K86" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E87" t="s">
-        <v>310</v>
-      </c>
-      <c r="F87">
-        <v>0</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I87">
-        <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J87" t="s">
-        <v>9</v>
-      </c>
-      <c r="K87" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E88" t="s">
-        <v>312</v>
-      </c>
-      <c r="F88">
-        <v>1</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I88">
-        <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J88" t="s">
-        <v>9</v>
-      </c>
-      <c r="K88" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E89" t="s">
-        <v>312</v>
-      </c>
-      <c r="F89">
-        <v>1</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I89">
-        <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J89" t="s">
-        <v>9</v>
-      </c>
-      <c r="K89" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="E90" t="s">
-        <v>310</v>
-      </c>
-      <c r="F90">
-        <v>0</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I90">
-        <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J90" t="s">
-        <v>9</v>
-      </c>
-      <c r="K90" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E91" t="s">
-        <v>316</v>
-      </c>
-      <c r="F91">
-        <v>1</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="I91">
-        <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J91" t="s">
-        <v>9</v>
-      </c>
-      <c r="K91" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="E92" t="s">
-        <v>311</v>
-      </c>
-      <c r="F92">
-        <v>1</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="I92">
-        <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J92" t="s">
-        <v>9</v>
-      </c>
-      <c r="K92" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E93" t="s">
-        <v>312</v>
-      </c>
-      <c r="F93">
-        <v>1</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I93">
-        <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J93" t="s">
-        <v>9</v>
-      </c>
-      <c r="K93" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="E94" t="s">
-        <v>312</v>
-      </c>
-      <c r="F94">
-        <v>1</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I94">
-        <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J94" t="s">
-        <v>9</v>
-      </c>
-      <c r="K94" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="E95" t="s">
-        <v>311</v>
-      </c>
-      <c r="F95">
-        <v>1</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="I95">
-        <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J95" t="s">
-        <v>9</v>
-      </c>
-      <c r="K95" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="E96" t="s">
-        <v>312</v>
-      </c>
-      <c r="F96">
-        <v>1</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="I96">
-        <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J96" t="s">
-        <v>9</v>
-      </c>
-      <c r="K96" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E97" t="s">
-        <v>311</v>
-      </c>
-      <c r="F97">
-        <v>1</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="I97">
-        <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J97" t="s">
-        <v>9</v>
-      </c>
-      <c r="K97" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="E98" t="s">
-        <v>311</v>
-      </c>
-      <c r="F98">
-        <v>1</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="I98">
-        <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J98" t="s">
-        <v>9</v>
-      </c>
-      <c r="K98" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11">
-      <c r="A99" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E99" t="s">
-        <v>310</v>
-      </c>
-      <c r="F99">
-        <v>0</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I99">
-        <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J99" t="s">
-        <v>8</v>
-      </c>
-      <c r="K99" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="E100" t="s">
-        <v>310</v>
-      </c>
-      <c r="F100">
-        <v>0</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I100">
-        <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J100" t="s">
-        <v>8</v>
-      </c>
-      <c r="K100" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="E101" t="s">
-        <v>310</v>
-      </c>
-      <c r="F101">
-        <v>0</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I101">
-        <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J101" t="s">
-        <v>8</v>
-      </c>
-      <c r="K101" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E102" t="s">
-        <v>310</v>
-      </c>
-      <c r="F102">
-        <v>0</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I102">
-        <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J102" t="s">
-        <v>8</v>
-      </c>
-      <c r="K102" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11">
-      <c r="A103" s="2"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E103" t="s">
-        <v>312</v>
-      </c>
-      <c r="F103">
-        <v>1</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="I103">
-        <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J103" t="s">
-        <v>8</v>
-      </c>
-      <c r="K103" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E104" t="s">
-        <v>310</v>
-      </c>
-      <c r="F104">
-        <v>0</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I104">
-        <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J104" t="s">
-        <v>8</v>
-      </c>
-      <c r="K104" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E105" t="s">
-        <v>312</v>
-      </c>
-      <c r="F105">
-        <v>1</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="I105">
-        <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J105" t="s">
-        <v>8</v>
-      </c>
-      <c r="K105" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E106" t="s">
-        <v>312</v>
-      </c>
-      <c r="F106">
-        <v>1</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="I106">
-        <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J106" t="s">
-        <v>8</v>
-      </c>
-      <c r="K106" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11">
-      <c r="A107" s="2"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E107" t="s">
-        <v>311</v>
-      </c>
-      <c r="F107">
-        <v>1</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="I107">
-        <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J107" t="s">
-        <v>8</v>
-      </c>
-      <c r="K107" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E108" t="s">
-        <v>311</v>
-      </c>
-      <c r="F108">
-        <v>1</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="I108">
-        <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J108" t="s">
-        <v>8</v>
-      </c>
-      <c r="K108" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E109" t="s">
-        <v>311</v>
-      </c>
-      <c r="F109">
-        <v>1</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="I109">
-        <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J109" t="s">
-        <v>8</v>
-      </c>
-      <c r="K109" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11">
-      <c r="A110" s="2"/>
-      <c r="B110" s="2"/>
-      <c r="C110" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E110" t="s">
-        <v>311</v>
-      </c>
-      <c r="F110">
-        <v>1</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="I110">
-        <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J110" t="s">
-        <v>8</v>
-      </c>
-      <c r="K110" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="E111" t="s">
-        <v>310</v>
-      </c>
-      <c r="F111">
-        <v>0</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I111">
-        <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J111" t="s">
-        <v>8</v>
-      </c>
-      <c r="K111" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E112" t="s">
-        <v>312</v>
-      </c>
-      <c r="F112">
-        <v>1</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I112">
-        <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J112" t="s">
-        <v>8</v>
-      </c>
-      <c r="K112" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11">
-      <c r="A113" s="2"/>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="E113" t="s">
-        <v>312</v>
-      </c>
-      <c r="F113">
-        <v>1</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I113">
-        <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J113" t="s">
-        <v>8</v>
-      </c>
-      <c r="K113" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11">
-      <c r="A114" s="2"/>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E114" t="s">
-        <v>312</v>
-      </c>
-      <c r="F114">
-        <v>1</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="I114">
-        <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J114" t="s">
-        <v>8</v>
-      </c>
-      <c r="K114" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
-      <c r="A115" s="2"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E115" t="s">
-        <v>312</v>
-      </c>
-      <c r="F115">
-        <v>1</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="I115">
-        <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J115" t="s">
-        <v>8</v>
-      </c>
-      <c r="K115" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E116" t="s">
-        <v>312</v>
-      </c>
-      <c r="F116">
-        <v>1</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I116">
-        <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J116" t="s">
-        <v>8</v>
-      </c>
-      <c r="K116" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11">
-      <c r="A117" s="2"/>
-      <c r="B117" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E117" t="s">
-        <v>309</v>
-      </c>
-      <c r="F117">
-        <v>1</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I117">
-        <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J117" t="s">
-        <v>8</v>
-      </c>
-      <c r="K117" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11">
-      <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="E118" t="s">
-        <v>309</v>
-      </c>
-      <c r="F118">
-        <v>1</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I118">
-        <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J118" t="s">
-        <v>8</v>
-      </c>
-      <c r="K118" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11">
-      <c r="A119" s="2"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="E119" t="s">
-        <v>309</v>
-      </c>
-      <c r="F119">
-        <v>1</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I119">
-        <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J119" t="s">
-        <v>8</v>
-      </c>
-      <c r="K119" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11">
-      <c r="A120" s="2"/>
-      <c r="B120" s="2"/>
-      <c r="C120" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E120" t="s">
-        <v>309</v>
-      </c>
-      <c r="F120">
-        <v>1</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="H120" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I120">
-        <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J120" t="s">
-        <v>8</v>
-      </c>
-      <c r="K120" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11">
-      <c r="A121" s="2"/>
-      <c r="B121" s="2"/>
-      <c r="C121" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E121" t="s">
-        <v>312</v>
-      </c>
-      <c r="F121">
-        <v>1</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I121">
-        <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J121" t="s">
-        <v>8</v>
-      </c>
-      <c r="K121" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11">
-      <c r="A122" s="2"/>
-      <c r="B122" s="2"/>
-      <c r="C122" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E122" t="s">
-        <v>312</v>
-      </c>
-      <c r="F122">
-        <v>1</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="I122">
-        <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J122" t="s">
-        <v>8</v>
-      </c>
-      <c r="K122" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11">
-      <c r="A123" s="2"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E123" t="s">
-        <v>309</v>
-      </c>
-      <c r="F123">
-        <v>1</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I123">
-        <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J123" t="s">
-        <v>8</v>
-      </c>
-      <c r="K123" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
-      <c r="A124" s="2"/>
-      <c r="B124" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="E124" t="s">
-        <v>312</v>
-      </c>
-      <c r="F124">
-        <v>1</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I124">
-        <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J124" t="s">
-        <v>8</v>
-      </c>
-      <c r="K124" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11">
-      <c r="A125" s="2"/>
-      <c r="B125" s="2"/>
-      <c r="C125" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E125" t="s">
-        <v>309</v>
-      </c>
-      <c r="F125">
-        <v>1</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I125">
-        <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J125" t="s">
-        <v>8</v>
-      </c>
-      <c r="K125" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11">
-      <c r="A126" s="2"/>
-      <c r="B126" s="2"/>
-      <c r="C126" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E126" t="s">
-        <v>309</v>
-      </c>
-      <c r="F126">
-        <v>1</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I126">
-        <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J126" t="s">
-        <v>8</v>
-      </c>
-      <c r="K126" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11">
-      <c r="A127" s="2"/>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E127" t="s">
-        <v>309</v>
-      </c>
-      <c r="F127">
-        <v>1</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I127">
-        <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J127" t="s">
-        <v>8</v>
-      </c>
-      <c r="K127" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11">
-      <c r="A128" s="2"/>
-      <c r="B128" s="2"/>
-      <c r="C128" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="E128" t="s">
-        <v>309</v>
-      </c>
-      <c r="F128">
-        <v>1</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I128">
-        <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J128" t="s">
-        <v>8</v>
-      </c>
-      <c r="K128" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11">
-      <c r="A129" s="2"/>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="E129" t="s">
-        <v>312</v>
-      </c>
-      <c r="F129">
-        <v>1</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I129">
-        <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J129" t="s">
-        <v>8</v>
-      </c>
-      <c r="K129" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11">
-      <c r="A130" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B130" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="E130" t="s">
-        <v>310</v>
-      </c>
-      <c r="F130">
-        <v>0</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I130">
-        <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J130" t="s">
-        <v>6</v>
-      </c>
-      <c r="K130" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11">
-      <c r="A131" s="2"/>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E131" t="s">
-        <v>310</v>
-      </c>
-      <c r="F131">
-        <v>0</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I131">
-        <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J131" t="s">
-        <v>6</v>
-      </c>
-      <c r="K131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11">
-      <c r="A132" s="2"/>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E132" t="s">
-        <v>310</v>
-      </c>
-      <c r="F132">
-        <v>0</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I132">
-        <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J132" t="s">
-        <v>6</v>
-      </c>
-      <c r="K132" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11">
-      <c r="A133" s="2"/>
-      <c r="B133" s="2"/>
-      <c r="C133" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E133" t="s">
-        <v>312</v>
-      </c>
-      <c r="F133">
-        <v>1</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="I133">
-        <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J133" t="s">
-        <v>6</v>
-      </c>
-      <c r="K133" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11">
-      <c r="A134" s="2"/>
-      <c r="B134" s="2"/>
-      <c r="C134" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="E134" t="s">
-        <v>310</v>
-      </c>
-      <c r="F134">
-        <v>0</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I134">
-        <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
-        <v>0</v>
-      </c>
-      <c r="J134" t="s">
-        <v>6</v>
-      </c>
-      <c r="K134" t="s">
-        <v>27</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A2:A38"/>
-    <mergeCell ref="A39:A98"/>
-    <mergeCell ref="A99:A129"/>
-    <mergeCell ref="A130:A134"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="B29:B34"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B39:B50"/>
-    <mergeCell ref="B51:B56"/>
-    <mergeCell ref="B57:B62"/>
+  <mergeCells count="19">
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="A48:A68"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="B56:B62"/>
     <mergeCell ref="B63:B68"/>
-    <mergeCell ref="B69:B75"/>
-    <mergeCell ref="B76:B82"/>
-    <mergeCell ref="B83:B91"/>
-    <mergeCell ref="B92:B98"/>
-    <mergeCell ref="B99:B104"/>
-    <mergeCell ref="B105:B110"/>
-    <mergeCell ref="B111:B116"/>
-    <mergeCell ref="B117:B123"/>
-    <mergeCell ref="B124:B129"/>
-    <mergeCell ref="B130:B134"/>
   </mergeCells>
-  <dataValidations count="133">
+  <dataValidations count="68">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"0: 0 items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
@@ -6872,391 +4538,196 @@
       <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+      <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-8),4: Developing. Score Range (9-17),7: Established. Score Range (18-24),10: Optimizing. Score Range (25-29)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-15),4: Developing. Score Range (16-31),7: Established. Score Range (32-44),10: Optimizing. Score Range (45-52)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
-      <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: item 1 completed,4: items 1-2 completed,6: items 1-3 completed,8: items 1-4 completed,10: items 1-5 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
+      <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
+      <formula1>"0: Not done,10: Done and clearly defined"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
-      <formula1>"0: Low Maturity. Score Range (0-8),4: Developing. Score Range (9-17),7: Established. Score Range (18-24),10: Optimizing. Score Range (25-29)"</formula1>
+      <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
-      <formula1>"0: Low Maturity. Score Range (0-15),4: Developing. Score Range (16-31),7: Established. Score Range (32-44),10: Optimizing. Score Range (45-52)"</formula1>
+      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
-      <formula1>"0: None"</formula1>
+      <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
-      <formula1>"0: No items completed,2: item 1 completed,4: items 1-2 completed,6: items 1-3 completed,8: items 1-4 completed,10: items 1-5 completed"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
+      <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
+      <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
+      <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
+      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
+      <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
+      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
+      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
+      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
+      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
+      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
+      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
+      <formula1>"0: Does not exist,10: Exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
+      <formula1>"0: Does not exist,10: Exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
+      <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
+      <formula1>"0: No alerting,10: Alerting exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
+      <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
-      <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
-      <formula1>"0: Not done,10: Done and clearly defined"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
-      <formula1>"0: Not done,10: Defined"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
-      <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
-      <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
-      <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
-      <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
-      <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H78">
-      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
-      <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H83">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H84">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
-      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
-      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
-      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
-      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
-      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
-      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H105">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H106">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H110">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H111">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H112">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H113">
-      <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H114">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H115">
-      <formula1>"0: No alerting,10: Alerting exists"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H116">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H117">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H118">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H119">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H120">
-      <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H121">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H122">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H123">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H124">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H125">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H126">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H127">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H128">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H129">
-      <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H130">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H131">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H132">
-      <formula1>"0: None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H133">
       <formula1>"0: Not monitored,2: Reported,5: Manual remediation,10: Automated remediation"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H134">
-      <formula1>"0: None"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -7328,71 +4799,6 @@
     <hyperlink ref="D67" r:id="rId66"/>
     <hyperlink ref="D68" r:id="rId67"/>
     <hyperlink ref="D69" r:id="rId68"/>
-    <hyperlink ref="D70" r:id="rId69"/>
-    <hyperlink ref="D71" r:id="rId70"/>
-    <hyperlink ref="D72" r:id="rId71"/>
-    <hyperlink ref="D73" r:id="rId72"/>
-    <hyperlink ref="D74" r:id="rId73"/>
-    <hyperlink ref="D75" r:id="rId74"/>
-    <hyperlink ref="D76" r:id="rId75"/>
-    <hyperlink ref="D77" r:id="rId76"/>
-    <hyperlink ref="D78" r:id="rId77"/>
-    <hyperlink ref="D79" r:id="rId78"/>
-    <hyperlink ref="D80" r:id="rId79"/>
-    <hyperlink ref="D81" r:id="rId80"/>
-    <hyperlink ref="D82" r:id="rId81"/>
-    <hyperlink ref="D83" r:id="rId82"/>
-    <hyperlink ref="D84" r:id="rId83"/>
-    <hyperlink ref="D85" r:id="rId84"/>
-    <hyperlink ref="D86" r:id="rId85"/>
-    <hyperlink ref="D87" r:id="rId86"/>
-    <hyperlink ref="D88" r:id="rId87"/>
-    <hyperlink ref="D89" r:id="rId88"/>
-    <hyperlink ref="D90" r:id="rId89"/>
-    <hyperlink ref="D91" r:id="rId90"/>
-    <hyperlink ref="D92" r:id="rId91"/>
-    <hyperlink ref="D93" r:id="rId92"/>
-    <hyperlink ref="D94" r:id="rId93"/>
-    <hyperlink ref="D95" r:id="rId94"/>
-    <hyperlink ref="D96" r:id="rId95"/>
-    <hyperlink ref="D97" r:id="rId96"/>
-    <hyperlink ref="D98" r:id="rId97"/>
-    <hyperlink ref="D99" r:id="rId98"/>
-    <hyperlink ref="D100" r:id="rId99"/>
-    <hyperlink ref="D101" r:id="rId100"/>
-    <hyperlink ref="D102" r:id="rId101"/>
-    <hyperlink ref="D103" r:id="rId102"/>
-    <hyperlink ref="D104" r:id="rId103"/>
-    <hyperlink ref="D105" r:id="rId104"/>
-    <hyperlink ref="D106" r:id="rId105"/>
-    <hyperlink ref="D107" r:id="rId106"/>
-    <hyperlink ref="D108" r:id="rId107"/>
-    <hyperlink ref="D109" r:id="rId108"/>
-    <hyperlink ref="D110" r:id="rId109"/>
-    <hyperlink ref="D111" r:id="rId110"/>
-    <hyperlink ref="D112" r:id="rId111"/>
-    <hyperlink ref="D113" r:id="rId112"/>
-    <hyperlink ref="D114" r:id="rId113"/>
-    <hyperlink ref="D115" r:id="rId114"/>
-    <hyperlink ref="D116" r:id="rId115"/>
-    <hyperlink ref="D117" r:id="rId116"/>
-    <hyperlink ref="D118" r:id="rId117"/>
-    <hyperlink ref="D119" r:id="rId118"/>
-    <hyperlink ref="D120" r:id="rId119"/>
-    <hyperlink ref="D121" r:id="rId120"/>
-    <hyperlink ref="D122" r:id="rId121"/>
-    <hyperlink ref="D123" r:id="rId122"/>
-    <hyperlink ref="D124" r:id="rId123"/>
-    <hyperlink ref="D125" r:id="rId124"/>
-    <hyperlink ref="D126" r:id="rId125"/>
-    <hyperlink ref="D127" r:id="rId126"/>
-    <hyperlink ref="D128" r:id="rId127"/>
-    <hyperlink ref="D129" r:id="rId128"/>
-    <hyperlink ref="D130" r:id="rId129"/>
-    <hyperlink ref="D131" r:id="rId130"/>
-    <hyperlink ref="D132" r:id="rId131"/>
-    <hyperlink ref="D133" r:id="rId132"/>
-    <hyperlink ref="D134" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="344">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -160,12 +160,39 @@
     <t>Prioritize Actions &amp; Publish Roadmap</t>
   </si>
   <si>
+    <t>Assess Skills &amp; Training Needs</t>
+  </si>
+  <si>
+    <t>Develop Role-Based Learning Content</t>
+  </si>
+  <si>
+    <t>Offer Certifications &amp; Informal Learning</t>
+  </si>
+  <si>
     <t>Leverage Vendor Training Resources</t>
   </si>
   <si>
+    <t>Track Training Impact &amp; Refresh Content</t>
+  </si>
+  <si>
     <t>Define Org Model &amp; Budget</t>
   </si>
   <si>
+    <t>Create Implementation Roadmap</t>
+  </si>
+  <si>
+    <t>Integrate Cost Data in Workflows</t>
+  </si>
+  <si>
+    <t>Publish FinOps KPIs</t>
+  </si>
+  <si>
+    <t>Drive Stakeholder Engagement</t>
+  </si>
+  <si>
+    <t>Automate Tasks &amp; Review Maturity</t>
+  </si>
+  <si>
     <t>Evaluate Build vs Buy Options</t>
   </si>
   <si>
@@ -193,9 +220,21 @@
     <t>Drive Adoption &amp; Resolve Conflicts</t>
   </si>
   <si>
+    <t>Map Invoices to Allocation Model</t>
+  </si>
+  <si>
+    <t>Reconcile Rates &amp; Track Completion</t>
+  </si>
+  <si>
     <t>Design Chargeback with Finance</t>
   </si>
   <si>
+    <t>Automate Chargeback Data Flows</t>
+  </si>
+  <si>
+    <t>Distribute Reports &amp; Track Accuracy</t>
+  </si>
+  <si>
     <t>Resolve Variances &amp; Increase Coverage</t>
   </si>
   <si>
@@ -211,15 +250,42 @@
     <t>Estimate Trade-Offs &amp; Document Cases</t>
   </si>
   <si>
+    <t>Create Workload Selection Criteria</t>
+  </si>
+  <si>
+    <t>Define Success Criteria &amp; Scope</t>
+  </si>
+  <si>
     <t>Enforce Tagging at Onboarding</t>
   </si>
   <si>
+    <t>Align Timelines with Budgets</t>
+  </si>
+  <si>
+    <t>Start with Lower Environments</t>
+  </si>
+  <si>
+    <t>Review Outcomes &amp; Adjust Patterns</t>
+  </si>
+  <si>
     <t>Inventory Licenses &amp; Map Resources</t>
   </si>
   <si>
+    <t>Document Licensing Models</t>
+  </si>
+  <si>
+    <t>Integrate Billing with Procurement</t>
+  </si>
+  <si>
     <t>Validate Utilization &amp; Remediate</t>
   </si>
   <si>
+    <t>Influence Workload Design Choices</t>
+  </si>
+  <si>
+    <t>Publish License Spend &amp; Utilization</t>
+  </si>
+  <si>
     <t>Document Commitment Strategy</t>
   </si>
   <si>
@@ -229,12 +295,24 @@
     <t>Leverage Spot &amp; Negotiated Discounts</t>
   </si>
   <si>
+    <t>Define Optimization Strategy</t>
+  </si>
+  <si>
     <t>Inventory &amp; Classify Workloads</t>
   </si>
   <si>
     <t>Collect Metrics &amp; Identify Candidates</t>
   </si>
   <si>
+    <t>Partner on Scheduling Actions</t>
+  </si>
+  <si>
+    <t>Gamify Adoption &amp; Celebrate Wins</t>
+  </si>
+  <si>
+    <t>Track KPIs &amp; Document Playbooks</t>
+  </si>
+  <si>
     <t>Define Metadata &amp; Hierarchy Strategy</t>
   </si>
   <si>
@@ -277,15 +355,27 @@
     <t>Define ingestion frequency; include mandatory metadata.</t>
   </si>
   <si>
+    <t>Gather Requirements &amp; Define KPIs</t>
+  </si>
+  <si>
     <t>Enrich Billing with Business Logic</t>
   </si>
   <si>
     <t>Build Dashboards for All Views</t>
   </si>
   <si>
+    <t>Publish Documentation &amp; Support</t>
+  </si>
+  <si>
     <t>Embed Reports in Workflows</t>
   </si>
   <si>
+    <t>Track Adoption &amp; Manage Changes</t>
+  </si>
+  <si>
+    <t>Iterate Based on Feedback</t>
+  </si>
+  <si>
     <t>Track Trends &amp; Compare Over Time</t>
   </si>
   <si>
@@ -295,6 +385,18 @@
     <t>Integrate Rolling Forecasts</t>
   </si>
   <si>
+    <t>Increase Shared Cost Coverage</t>
+  </si>
+  <si>
+    <t>Publish Budget vs Actual Reports</t>
+  </si>
+  <si>
+    <t>Automate Budget Threshold Alerts</t>
+  </si>
+  <si>
+    <t>Review &amp; Adapt Budget Strategy</t>
+  </si>
+  <si>
     <t>Collect Business Drivers Regularly</t>
   </si>
   <si>
@@ -364,12 +466,39 @@
     <t>116</t>
   </si>
   <si>
+    <t>097</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>099</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
+    <t>101</t>
+  </si>
+  <si>
     <t>091</t>
   </si>
   <si>
+    <t>092</t>
+  </si>
+  <si>
+    <t>093</t>
+  </si>
+  <si>
+    <t>094</t>
+  </si>
+  <si>
+    <t>095</t>
+  </si>
+  <si>
+    <t>096</t>
+  </si>
+  <si>
     <t>125</t>
   </si>
   <si>
@@ -397,9 +526,21 @@
     <t>134</t>
   </si>
   <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
     <t>109</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
@@ -415,15 +556,42 @@
     <t>063</t>
   </si>
   <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>073</t>
   </si>
   <si>
+    <t>074</t>
+  </si>
+  <si>
+    <t>075</t>
+  </si>
+  <si>
     <t>076</t>
   </si>
   <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>078</t>
+  </si>
+  <si>
     <t>079</t>
   </si>
   <si>
@@ -433,12 +601,24 @@
     <t>084</t>
   </si>
   <si>
+    <t>067</t>
+  </si>
+  <si>
     <t>068</t>
   </si>
   <si>
     <t>069</t>
   </si>
   <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t>072</t>
+  </si>
+  <si>
     <t>009</t>
   </si>
   <si>
@@ -481,15 +661,27 @@
     <t>135</t>
   </si>
   <si>
+    <t>016</t>
+  </si>
+  <si>
     <t>017</t>
   </si>
   <si>
     <t>018</t>
   </si>
   <si>
+    <t>019</t>
+  </si>
+  <si>
     <t>020</t>
   </si>
   <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
     <t>053</t>
   </si>
   <si>
@@ -497,6 +689,18 @@
   </si>
   <si>
     <t>044</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>048</t>
   </si>
   <si>
     <t>038</t>
@@ -910,6 +1114,9 @@
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1-2 completed'}, {'Score': 8, 'Condition': 'items 1-3 completed'}, {'Score': 10, 'Condition': 'items 1-4 completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Completed'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
@@ -1941,14 +2148,14 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2">
-        <f>SUM(Scoring!F2:F69)</f>
+        <f>SUM(Scoring!F2:F103)</f>
         <v>0</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2">
-        <f>SUM(Scoring!I2:I69)/A2</f>
+        <f>SUM(Scoring!I2:I103)/A2</f>
         <v>0</v>
       </c>
       <c r="D2">
@@ -1972,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="U5">
-        <f>SUMIF(Scoring!J2:J69,A5,Scoring!I2:I69)/SUMIF(Scoring!J2:J69,A5,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!J2:J103,A5,Scoring!I2:I103)/SUMIF(Scoring!J2:J103,A5,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -1981,10 +2188,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="U6">
-        <f>SUMIF(Scoring!J2:J69,A6,Scoring!I2:I69)/SUMIF(Scoring!J2:J69,A6,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!J2:J103,A6,Scoring!I2:I103)/SUMIF(Scoring!J2:J103,A6,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -1993,10 +2200,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="U7">
-        <f>SUMIF(Scoring!J2:J69,A7,Scoring!I2:I69)/SUMIF(Scoring!J2:J69,A7,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!J2:J103,A7,Scoring!I2:I103)/SUMIF(Scoring!J2:J103,A7,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2005,10 +2212,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="U8">
-        <f>SUMIF(Scoring!J2:J69,A8,Scoring!I2:I69)/SUMIF(Scoring!J2:J69,A8,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!J2:J103,A8,Scoring!I2:I103)/SUMIF(Scoring!J2:J103,A8,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2034,7 +2241,7 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <f>SUMIF(Scoring!K2:K69,A12,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A12,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A12,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A12,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2046,7 +2253,7 @@
         <v>4</v>
       </c>
       <c r="U13">
-        <f>SUMIF(Scoring!K2:K69,A13,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A13,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A13,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A13,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2055,10 +2262,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <f>SUMIF(Scoring!K2:K69,A14,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A14,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A14,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A14,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2070,7 +2277,7 @@
         <v>3</v>
       </c>
       <c r="U15">
-        <f>SUMIF(Scoring!K2:K69,A15,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A15,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A15,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A15,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2079,10 +2286,10 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <f>SUMIF(Scoring!K2:K69,A16,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A16,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A16,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A16,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2094,7 +2301,7 @@
         <v>4</v>
       </c>
       <c r="U17">
-        <f>SUMIF(Scoring!K2:K69,A17,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A17,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A17,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A17,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2106,7 +2313,7 @@
         <v>1</v>
       </c>
       <c r="U18">
-        <f>SUMIF(Scoring!K2:K69,A18,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A18,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A18,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A18,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2118,7 +2325,7 @@
         <v>4</v>
       </c>
       <c r="U19">
-        <f>SUMIF(Scoring!K2:K69,A19,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A19,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A19,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A19,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2127,10 +2334,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <f>SUMIF(Scoring!K2:K69,A20,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A20,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A20,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A20,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2139,10 +2346,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <f>SUMIF(Scoring!K2:K69,A21,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A21,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A21,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A21,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2154,7 +2361,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <f>SUMIF(Scoring!K2:K69,A22,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A22,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A22,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A22,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2166,7 +2373,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <f>SUMIF(Scoring!K2:K69,A23,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A23,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A23,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A23,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2175,10 +2382,10 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <f>SUMIF(Scoring!K2:K69,A24,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A24,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A24,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A24,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2190,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="U25">
-        <f>SUMIF(Scoring!K2:K69,A25,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A25,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A25,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A25,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2199,10 +2406,10 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <f>SUMIF(Scoring!K2:K69,A26,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A26,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A26,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A26,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2214,7 +2421,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <f>SUMIF(Scoring!K2:K69,A27,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A27,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A27,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A27,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2226,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="U28">
-        <f>SUMIF(Scoring!K2:K69,A28,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A28,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A28,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A28,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2238,7 +2445,7 @@
         <v>3</v>
       </c>
       <c r="U29">
-        <f>SUMIF(Scoring!K2:K69,A29,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A29,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A29,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A29,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2247,10 +2454,10 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <f>SUMIF(Scoring!K2:K69,A30,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A30,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A30,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A30,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2262,7 +2469,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <f>SUMIF(Scoring!K2:K69,A31,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A31,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A31,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A31,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2271,10 +2478,10 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <f>SUMIF(Scoring!K2:K69,A32,Scoring!I2:I69)/SUMIF(Scoring!K2:K69,A32,Scoring!F2:F69)</f>
+        <f>SUMIF(Scoring!K2:K103,A32,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A32,Scoring!F2:F103)</f>
         <v>0</v>
       </c>
     </row>
@@ -2297,7 +2504,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -2359,19 +2566,19 @@
         <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>258</v>
+        <v>327</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2391,19 +2598,19 @@
         <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2423,19 +2630,19 @@
         <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2455,19 +2662,19 @@
         <v>46</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2489,19 +2696,16 @@
         <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2516,23 +2720,21 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>260</v>
+        <v>329</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -2542,31 +2744,26 @@
         <v>7</v>
       </c>
       <c r="K7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>261</v>
+        <v>329</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -2576,7 +2773,7 @@
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2586,19 +2783,19 @@
         <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>189</v>
+        <v>255</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>262</v>
+        <v>328</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -2608,7 +2805,7 @@
         <v>7</v>
       </c>
       <c r="K9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2618,19 +2815,16 @@
         <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="H10" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -2640,31 +2834,28 @@
         <v>7</v>
       </c>
       <c r="K10" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="H11" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -2674,7 +2865,7 @@
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2684,19 +2875,16 @@
         <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="E12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="H12" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -2706,7 +2894,7 @@
         <v>7</v>
       </c>
       <c r="K12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2716,19 +2904,16 @@
         <v>54</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="E13" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="H13" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -2738,7 +2923,7 @@
         <v>7</v>
       </c>
       <c r="K13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2748,19 +2933,16 @@
         <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="E14" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="H14" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -2770,7 +2952,7 @@
         <v>7</v>
       </c>
       <c r="K14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2780,19 +2962,16 @@
         <v>56</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="E15" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="H15" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -2802,7 +2981,7 @@
         <v>7</v>
       </c>
       <c r="K15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2812,19 +2991,16 @@
         <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="E16" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="H16" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -2834,28 +3010,31 @@
         <v>7</v>
       </c>
       <c r="K16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="E17" t="s">
-        <v>180</v>
+        <v>249</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
+      <c r="G17" s="1" t="s">
+        <v>256</v>
+      </c>
       <c r="H17" s="1" t="s">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -2865,7 +3044,7 @@
         <v>7</v>
       </c>
       <c r="K17" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2875,16 +3054,19 @@
         <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="E18" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
+      <c r="G18" s="1" t="s">
+        <v>257</v>
+      </c>
       <c r="H18" s="1" t="s">
-        <v>260</v>
+        <v>331</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -2894,28 +3076,29 @@
         <v>7</v>
       </c>
       <c r="K18" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2"/>
-      <c r="B19" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="E19" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
+      <c r="G19" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="H19" s="1" t="s">
-        <v>263</v>
+        <v>328</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -2925,40 +3108,41 @@
         <v>7</v>
       </c>
       <c r="K19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="E20" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
+      <c r="G20" s="1" t="s">
+        <v>259</v>
+      </c>
       <c r="H20" s="1" t="s">
-        <v>264</v>
+        <v>328</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K20" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2968,29 +3152,29 @@
         <v>62</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="E21" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K21" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3000,26 +3184,29 @@
         <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="E22" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
+      <c r="G22" s="1" t="s">
+        <v>261</v>
+      </c>
       <c r="H22" s="1" t="s">
-        <v>265</v>
+        <v>328</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K22" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3029,60 +3216,61 @@
         <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="E23" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>198</v>
+        <v>262</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K23" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2"/>
-      <c r="B24" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="E24" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
+      <c r="G24" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="H24" s="1" t="s">
-        <v>266</v>
+        <v>328</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3092,57 +3280,60 @@
         <v>66</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="E25" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
+      <c r="G25" s="1" t="s">
+        <v>264</v>
+      </c>
       <c r="H25" s="1" t="s">
-        <v>260</v>
+        <v>328</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K25" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="E26" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>260</v>
+        <v>329</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3152,26 +3343,26 @@
         <v>68</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="E27" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>260</v>
+        <v>329</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K27" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3181,60 +3372,55 @@
         <v>69</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="E28" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="H28" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K28" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2"/>
-      <c r="B29" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="E29" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>267</v>
+        <v>329</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K29" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3244,114 +3430,109 @@
         <v>71</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="E30" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K30" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2"/>
-      <c r="B31" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="E31" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="H31" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K31" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C32" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="E32" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="H32" s="1" t="s">
-        <v>266</v>
+        <v>332</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
         <v>0</v>
       </c>
       <c r="J32" t="s">
+        <v>7</v>
+      </c>
+      <c r="K32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C33" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="E33" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="H33" s="1" t="s">
-        <v>259</v>
+        <v>333</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3361,7 +3542,7 @@
         <v>9</v>
       </c>
       <c r="K33" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3371,19 +3552,19 @@
         <v>75</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="E34" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>203</v>
+        <v>265</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>266</v>
+        <v>328</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -3393,7 +3574,7 @@
         <v>9</v>
       </c>
       <c r="K34" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3403,19 +3584,16 @@
         <v>76</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="E35" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="H35" s="1" t="s">
-        <v>266</v>
+        <v>334</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -3425,7 +3603,7 @@
         <v>9</v>
       </c>
       <c r="K35" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3435,19 +3613,16 @@
         <v>77</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="E36" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="H36" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -3457,31 +3632,26 @@
         <v>9</v>
       </c>
       <c r="K36" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="2"/>
-      <c r="B37" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="E37" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="H37" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -3491,7 +3661,7 @@
         <v>9</v>
       </c>
       <c r="K37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3501,19 +3671,19 @@
         <v>79</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="E38" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>207</v>
+        <v>266</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -3523,7 +3693,7 @@
         <v>9</v>
       </c>
       <c r="K38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3533,16 +3703,16 @@
         <v>80</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="E39" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -3552,7 +3722,7 @@
         <v>9</v>
       </c>
       <c r="K39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3562,19 +3732,16 @@
         <v>81</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="E40" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="H40" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -3584,28 +3751,26 @@
         <v>9</v>
       </c>
       <c r="K40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="2"/>
-      <c r="B41" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B41" s="2"/>
       <c r="C41" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="E41" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>269</v>
+        <v>329</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -3615,29 +3780,28 @@
         <v>9</v>
       </c>
       <c r="K41" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
+      <c r="B42" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="C42" s="2" t="s">
         <v>83</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="E42" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="H42" s="1" t="s">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -3647,7 +3811,7 @@
         <v>9</v>
       </c>
       <c r="K42" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -3657,19 +3821,16 @@
         <v>84</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="E43" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="H43" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -3679,7 +3840,7 @@
         <v>9</v>
       </c>
       <c r="K43" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -3689,16 +3850,16 @@
         <v>85</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="E44" t="s">
-        <v>182</v>
+        <v>247</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>269</v>
+        <v>329</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -3708,31 +3869,26 @@
         <v>9</v>
       </c>
       <c r="K44" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="2"/>
-      <c r="B45" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="E45" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="H45" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -3742,7 +3898,7 @@
         <v>9</v>
       </c>
       <c r="K45" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -3752,19 +3908,16 @@
         <v>87</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="E46" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="H46" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -3774,7 +3927,7 @@
         <v>9</v>
       </c>
       <c r="K46" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -3784,16 +3937,16 @@
         <v>88</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="E47" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>270</v>
+        <v>329</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -3803,71 +3956,67 @@
         <v>9</v>
       </c>
       <c r="K47" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="E48" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>271</v>
+        <v>329</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K48" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="2"/>
-      <c r="B49" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B49" s="2"/>
       <c r="C49" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="E49" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>264</v>
+        <v>329</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K49" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -3877,60 +4026,60 @@
         <v>91</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="E50" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
+      <c r="G50" s="1" t="s">
+        <v>267</v>
+      </c>
       <c r="H50" s="1" t="s">
-        <v>264</v>
+        <v>328</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K50" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="E51" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="H51" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K51" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3940,26 +4089,26 @@
         <v>93</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="E52" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
         <v>0</v>
       </c>
       <c r="J52" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K52" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -3969,29 +4118,26 @@
         <v>94</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="E53" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="H53" s="1" t="s">
-        <v>266</v>
+        <v>335</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
         <v>0</v>
       </c>
       <c r="J53" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K53" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4001,26 +4147,26 @@
         <v>95</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="E54" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>273</v>
+        <v>329</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
         <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K54" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -4030,95 +4176,89 @@
         <v>96</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="E55" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="H55" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
         <v>0</v>
       </c>
       <c r="J55" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K55" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2"/>
-      <c r="B56" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="B56" s="2"/>
       <c r="C56" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="E56" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="H56" s="1" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
         <v>0</v>
       </c>
       <c r="J56" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K56" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
+      <c r="B57" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C57" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="E57" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>217</v>
+        <v>268</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
         <v>0</v>
       </c>
       <c r="J57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K57" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -4128,29 +4268,29 @@
         <v>99</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="E58" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>218</v>
+        <v>269</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
         <v>0</v>
       </c>
       <c r="J58" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K58" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -4160,29 +4300,29 @@
         <v>100</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="E59" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
         <v>0</v>
       </c>
       <c r="J59" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K59" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -4192,29 +4332,29 @@
         <v>101</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="E60" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
         <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K60" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -4224,26 +4364,29 @@
         <v>102</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="E61" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
+      <c r="G61" s="1" t="s">
+        <v>272</v>
+      </c>
       <c r="H61" s="1" t="s">
-        <v>266</v>
+        <v>335</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
         <v>0</v>
       </c>
       <c r="J61" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K61" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -4253,63 +4396,63 @@
         <v>103</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="E62" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
         <v>0</v>
       </c>
       <c r="J62" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K62" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="E63" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>222</v>
+        <v>274</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
         <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K63" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -4319,29 +4462,29 @@
         <v>105</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="E64" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
         <v>0</v>
       </c>
       <c r="J64" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K64" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -4351,29 +4494,26 @@
         <v>106</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="E65" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="H65" s="1" t="s">
-        <v>259</v>
+        <v>337</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
         <v>0</v>
       </c>
       <c r="J65" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K65" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -4383,61 +4523,60 @@
         <v>107</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="E66" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
         <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K66" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
+      <c r="B67" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C67" s="2" t="s">
         <v>108</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="E67" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="H67" s="1" t="s">
-        <v>259</v>
+        <v>338</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K67" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -4447,84 +4586,1140 @@
         <v>109</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>177</v>
+        <v>211</v>
       </c>
       <c r="E68" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
+      <c r="G68" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="H68" s="1" t="s">
-        <v>272</v>
+        <v>328</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
         <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K68" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
       <c r="C69" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="E69" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
+      <c r="G69" s="1" t="s">
+        <v>278</v>
+      </c>
       <c r="H69" s="1" t="s">
-        <v>274</v>
+        <v>328</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
         <v>0</v>
       </c>
       <c r="J69" t="s">
+        <v>9</v>
+      </c>
+      <c r="K69" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E70" t="s">
+        <v>250</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I70">
+        <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J70" t="s">
+        <v>9</v>
+      </c>
+      <c r="K70" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E71" t="s">
+        <v>247</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I71">
+        <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J71" t="s">
+        <v>9</v>
+      </c>
+      <c r="K71" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E72" t="s">
+        <v>248</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I72">
+        <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J72" t="s">
+        <v>9</v>
+      </c>
+      <c r="K72" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E73" t="s">
+        <v>248</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I73">
+        <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J73" t="s">
+        <v>9</v>
+      </c>
+      <c r="K73" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E74" t="s">
+        <v>247</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I74">
+        <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J74" t="s">
+        <v>9</v>
+      </c>
+      <c r="K74" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E75" t="s">
+        <v>248</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="I75">
+        <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J75" t="s">
+        <v>9</v>
+      </c>
+      <c r="K75" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E76" t="s">
+        <v>247</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I76">
+        <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J76" t="s">
+        <v>9</v>
+      </c>
+      <c r="K76" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E77" t="s">
+        <v>247</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I77">
+        <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J77" t="s">
+        <v>9</v>
+      </c>
+      <c r="K77" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E78" t="s">
+        <v>248</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="I78">
+        <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J78" t="s">
+        <v>8</v>
+      </c>
+      <c r="K78" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E79" t="s">
+        <v>248</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I79">
+        <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J79" t="s">
+        <v>8</v>
+      </c>
+      <c r="K79" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E80" t="s">
+        <v>248</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I80">
+        <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J80" t="s">
+        <v>8</v>
+      </c>
+      <c r="K80" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E81" t="s">
+        <v>247</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I81">
+        <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J81" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E82" t="s">
+        <v>247</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I82">
+        <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J82" t="s">
+        <v>8</v>
+      </c>
+      <c r="K82" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E83" t="s">
+        <v>247</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I83">
+        <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J83" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E84" t="s">
+        <v>247</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I84">
+        <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J84" t="s">
+        <v>8</v>
+      </c>
+      <c r="K84" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E85" t="s">
+        <v>248</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I85">
+        <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J85" t="s">
+        <v>8</v>
+      </c>
+      <c r="K85" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E86" t="s">
+        <v>248</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="I86">
+        <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J86" t="s">
+        <v>8</v>
+      </c>
+      <c r="K86" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E87" t="s">
+        <v>248</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="I87">
+        <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J87" t="s">
+        <v>8</v>
+      </c>
+      <c r="K87" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E88" t="s">
+        <v>248</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I88">
+        <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J88" t="s">
+        <v>8</v>
+      </c>
+      <c r="K88" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E89" t="s">
+        <v>248</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I89">
+        <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J89" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E90" t="s">
+        <v>247</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I90">
+        <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J90" t="s">
+        <v>8</v>
+      </c>
+      <c r="K90" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E91" t="s">
+        <v>247</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I91">
+        <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J91" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E92" t="s">
+        <v>247</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I92">
+        <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J92" t="s">
+        <v>8</v>
+      </c>
+      <c r="K92" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E93" t="s">
+        <v>247</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I93">
+        <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J93" t="s">
+        <v>8</v>
+      </c>
+      <c r="K93" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E94" t="s">
+        <v>248</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I94">
+        <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J94" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E95" t="s">
+        <v>248</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="I95">
+        <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J95" t="s">
+        <v>8</v>
+      </c>
+      <c r="K95" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E96" t="s">
+        <v>247</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I96">
+        <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J96" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E97" t="s">
+        <v>248</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I97">
+        <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J97" t="s">
+        <v>8</v>
+      </c>
+      <c r="K97" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E98" t="s">
+        <v>247</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I98">
+        <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J98" t="s">
+        <v>8</v>
+      </c>
+      <c r="K98" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E99" t="s">
+        <v>247</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I99">
+        <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J99" t="s">
+        <v>8</v>
+      </c>
+      <c r="K99" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E100" t="s">
+        <v>247</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I100">
+        <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J100" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E101" t="s">
+        <v>247</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I101">
+        <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J101" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E102" t="s">
+        <v>248</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="I102">
+        <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J102" t="s">
+        <v>8</v>
+      </c>
+      <c r="K102" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K69" t="s">
+      <c r="B103" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="C103" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E103" t="s">
+        <v>248</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I103">
+        <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J103" t="s">
+        <v>6</v>
+      </c>
+      <c r="K103" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A20:A47"/>
-    <mergeCell ref="A48:A68"/>
+  <mergeCells count="21">
+    <mergeCell ref="A2:A32"/>
+    <mergeCell ref="A33:A77"/>
+    <mergeCell ref="A78:A102"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B6:B10"/>
     <mergeCell ref="B11:B16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="B56:B62"/>
-    <mergeCell ref="B63:B68"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="B33:B41"/>
+    <mergeCell ref="B42:B47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B51:B56"/>
+    <mergeCell ref="B57:B62"/>
+    <mergeCell ref="B63:B66"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="B71:B77"/>
+    <mergeCell ref="B79:B84"/>
+    <mergeCell ref="B85:B89"/>
+    <mergeCell ref="B90:B96"/>
+    <mergeCell ref="B97:B102"/>
   </mergeCells>
-  <dataValidations count="68">
+  <dataValidations count="102">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"0: 0 items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
@@ -4538,169 +5733,169 @@
       <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
       <formula1>"0: Low Maturity. Score Range (0-8),4: Developing. Score Range (9-17),7: Established. Score Range (18-24),10: Optimizing. Score Range (25-29)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
       <formula1>"0: Low Maturity. Score Range (0-15),4: Developing. Score Range (16-31),7: Established. Score Range (32-44),10: Optimizing. Score Range (45-52)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
       <formula1>"0: No items completed,2: item 1 completed,4: items 1-2 completed,6: items 1-3 completed,8: items 1-4 completed,10: items 1-5 completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
-      <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
-      <formula1>"0: Not done,10: Done and clearly defined"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
-      <formula1>"0: Not done,10: Defined"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
-      <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
-      <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
+      <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
+      <formula1>"0: Not done,10: Done and clearly defined"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
+      <formula1>"0: Not done,10: Defined"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
+      <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
+      <formula1>"0: Does not exist,10: Exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
+      <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
       <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
-      <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
-      <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
-      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
-      <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
-      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
-      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
-      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
-      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
-      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
-      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
-      <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
-      <formula1>"0: No alerting,10: Alerting exists"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+      <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
-      <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
+      <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
@@ -4709,24 +5904,126 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
+      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
+      <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
+      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
+      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
+      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
+      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
+      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H78">
+      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
+      <formula1>"0: Does not exist,10: Exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
+      <formula1>"0: Does not exist,10: Exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H83">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H84">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
+      <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
+      <formula1>"0: No alerting,10: Alerting exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
+      <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
       <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
       <formula1>"0: Not monitored,2: Reported,5: Manual remediation,10: Automated remediation"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4799,6 +6096,40 @@
     <hyperlink ref="D67" r:id="rId66"/>
     <hyperlink ref="D68" r:id="rId67"/>
     <hyperlink ref="D69" r:id="rId68"/>
+    <hyperlink ref="D70" r:id="rId69"/>
+    <hyperlink ref="D71" r:id="rId70"/>
+    <hyperlink ref="D72" r:id="rId71"/>
+    <hyperlink ref="D73" r:id="rId72"/>
+    <hyperlink ref="D74" r:id="rId73"/>
+    <hyperlink ref="D75" r:id="rId74"/>
+    <hyperlink ref="D76" r:id="rId75"/>
+    <hyperlink ref="D77" r:id="rId76"/>
+    <hyperlink ref="D78" r:id="rId77"/>
+    <hyperlink ref="D79" r:id="rId78"/>
+    <hyperlink ref="D80" r:id="rId79"/>
+    <hyperlink ref="D81" r:id="rId80"/>
+    <hyperlink ref="D82" r:id="rId81"/>
+    <hyperlink ref="D83" r:id="rId82"/>
+    <hyperlink ref="D84" r:id="rId83"/>
+    <hyperlink ref="D85" r:id="rId84"/>
+    <hyperlink ref="D86" r:id="rId85"/>
+    <hyperlink ref="D87" r:id="rId86"/>
+    <hyperlink ref="D88" r:id="rId87"/>
+    <hyperlink ref="D89" r:id="rId88"/>
+    <hyperlink ref="D90" r:id="rId89"/>
+    <hyperlink ref="D91" r:id="rId90"/>
+    <hyperlink ref="D92" r:id="rId91"/>
+    <hyperlink ref="D93" r:id="rId92"/>
+    <hyperlink ref="D94" r:id="rId93"/>
+    <hyperlink ref="D95" r:id="rId94"/>
+    <hyperlink ref="D96" r:id="rId95"/>
+    <hyperlink ref="D97" r:id="rId96"/>
+    <hyperlink ref="D98" r:id="rId97"/>
+    <hyperlink ref="D99" r:id="rId98"/>
+    <hyperlink ref="D100" r:id="rId99"/>
+    <hyperlink ref="D101" r:id="rId100"/>
+    <hyperlink ref="D102" r:id="rId101"/>
+    <hyperlink ref="D103" r:id="rId102"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="350">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -193,6 +193,9 @@
     <t>Automate Tasks &amp; Review Maturity</t>
   </si>
   <si>
+    <t>Assess Tooling Needs &amp; Criteria</t>
+  </si>
+  <si>
     <t>Evaluate Build vs Buy Options</t>
   </si>
   <si>
@@ -499,6 +502,9 @@
     <t>096</t>
   </si>
   <si>
+    <t>124</t>
+  </si>
+  <si>
     <t>125</t>
   </si>
   <si>
@@ -760,16 +766,19 @@
     <t>105</t>
   </si>
   <si>
+    <t>1.1.0</t>
+  </si>
+  <si>
     <t>1.0.0</t>
   </si>
   <si>
-    <t>1.7.0</t>
-  </si>
-  <si>
-    <t>2.0.1</t>
-  </si>
-  <si>
-    <t>1.5.0</t>
+    <t>1.8.0</t>
+  </si>
+  <si>
+    <t>2.1.0</t>
+  </si>
+  <si>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>* Select which teams or groups are in scope for the planned assessments
@@ -803,11 +812,24 @@
 10*Ceil(x/2)</t>
   </si>
   <si>
+    <t>* Weighted sum
+  Criteria document (score x3),
+  KPI alignment (score x3),
+  Stakeholder count capped at 5 (score x2),
+  Refresh cadence (score x2).
+  Max Raw Score (31)
+* Criteria formally documented (0=None, 1=Draft, 2=Approved, 3=Versioned+Reviewed)
+* Criteria explicitly mapped to FinOps KPIs (0=None, 1=Partial, 2=Full)
+* of FinOps personas involved in criteria definition (0-5)
+* Criteria review frequency (0=Never, 1=Ad-hoc, 2=Annual, 3=Quarterly+)
+* Output Range (0 - Max Raw)</t>
+  </si>
+  <si>
     <t xml:space="preserve">* Weighted sum
-  TCO (score ×3),
-  Vendor scoring (score ×3),
-  Decision document (score ×3),
-  Rules established (score ×1).
+  TCO (score x3),
+  Vendor scoring (score x3),
+  Decision document (score x3),
+  Rules established (score x1).
   Max Raw Score (29)
 * TCO_Analysis - Total Cost of Ownership analysis performed
   (0=None, 1=High-level, 2=Detailed, 3=Validated with Finance)
@@ -1125,6 +1147,9 @@
     <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Defined'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity (0-9)'}, {'Score': 4, 'Condition': 'Developing (10-18)'}, {'Score': 7, 'Condition': 'Established (19-26)'}, {'Score': 10, 'Condition': 'Optimizing (27-31)'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-8)'}, {'Score': 4, 'Condition': 'Developing, Score Range (9-17)'}, {'Score': 7, 'Condition': 'Established, Score Range (18-24)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (25-29)'}]</t>
   </si>
   <si>
@@ -1207,6 +1232,9 @@
   </si>
   <si>
     <t>0: Not done</t>
+  </si>
+  <si>
+    <t>0: Low Maturity (0-9)</t>
   </si>
   <si>
     <t>0: Low Maturity. Score Range (0-8)</t>
@@ -2148,14 +2176,14 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2">
-        <f>SUM(Scoring!F2:F103)</f>
+        <f>SUM(Scoring!F2:F104)</f>
         <v>0</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2">
-        <f>SUM(Scoring!I2:I103)/A2</f>
+        <f>SUM(Scoring!I2:I104)/A2</f>
         <v>0</v>
       </c>
       <c r="D2">
@@ -2179,7 +2207,7 @@
         <v>1</v>
       </c>
       <c r="U5">
-        <f>SUMIF(Scoring!J2:J103,A5,Scoring!I2:I103)/SUMIF(Scoring!J2:J103,A5,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!J2:J104,A5,Scoring!I2:I104)/SUMIF(Scoring!J2:J104,A5,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2188,10 +2216,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U6">
-        <f>SUMIF(Scoring!J2:J103,A6,Scoring!I2:I103)/SUMIF(Scoring!J2:J103,A6,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!J2:J104,A6,Scoring!I2:I104)/SUMIF(Scoring!J2:J104,A6,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2203,7 +2231,7 @@
         <v>25</v>
       </c>
       <c r="U7">
-        <f>SUMIF(Scoring!J2:J103,A7,Scoring!I2:I103)/SUMIF(Scoring!J2:J103,A7,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!J2:J104,A7,Scoring!I2:I104)/SUMIF(Scoring!J2:J104,A7,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2215,7 +2243,7 @@
         <v>45</v>
       </c>
       <c r="U8">
-        <f>SUMIF(Scoring!J2:J103,A8,Scoring!I2:I103)/SUMIF(Scoring!J2:J103,A8,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!J2:J104,A8,Scoring!I2:I104)/SUMIF(Scoring!J2:J104,A8,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2241,7 +2269,7 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <f>SUMIF(Scoring!K2:K103,A12,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A12,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A12,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A12,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2253,7 +2281,7 @@
         <v>4</v>
       </c>
       <c r="U13">
-        <f>SUMIF(Scoring!K2:K103,A13,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A13,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A13,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A13,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2265,7 +2293,7 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <f>SUMIF(Scoring!K2:K103,A14,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A14,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A14,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A14,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2274,10 +2302,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <f>SUMIF(Scoring!K2:K103,A15,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A15,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A15,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A15,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2289,7 +2317,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <f>SUMIF(Scoring!K2:K103,A16,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A16,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A16,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A16,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2301,7 +2329,7 @@
         <v>4</v>
       </c>
       <c r="U17">
-        <f>SUMIF(Scoring!K2:K103,A17,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A17,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A17,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A17,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2313,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="U18">
-        <f>SUMIF(Scoring!K2:K103,A18,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A18,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A18,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A18,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2325,7 +2353,7 @@
         <v>4</v>
       </c>
       <c r="U19">
-        <f>SUMIF(Scoring!K2:K103,A19,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A19,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A19,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A19,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2337,7 +2365,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <f>SUMIF(Scoring!K2:K103,A20,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A20,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A20,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A20,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2349,7 +2377,7 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <f>SUMIF(Scoring!K2:K103,A21,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A21,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A21,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A21,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2361,7 +2389,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <f>SUMIF(Scoring!K2:K103,A22,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A22,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A22,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A22,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2373,7 +2401,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <f>SUMIF(Scoring!K2:K103,A23,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A23,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A23,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A23,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2385,7 +2413,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <f>SUMIF(Scoring!K2:K103,A24,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A24,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A24,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A24,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2397,7 +2425,7 @@
         <v>1</v>
       </c>
       <c r="U25">
-        <f>SUMIF(Scoring!K2:K103,A25,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A25,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A25,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A25,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2409,7 +2437,7 @@
         <v>6</v>
       </c>
       <c r="U26">
-        <f>SUMIF(Scoring!K2:K103,A26,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A26,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A26,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A26,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2421,7 +2449,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <f>SUMIF(Scoring!K2:K103,A27,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A27,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A27,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A27,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2433,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="U28">
-        <f>SUMIF(Scoring!K2:K103,A28,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A28,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A28,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A28,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2445,7 +2473,7 @@
         <v>3</v>
       </c>
       <c r="U29">
-        <f>SUMIF(Scoring!K2:K103,A29,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A29,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A29,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A29,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2457,7 +2485,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <f>SUMIF(Scoring!K2:K103,A30,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A30,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A30,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A30,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2469,7 +2497,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <f>SUMIF(Scoring!K2:K103,A31,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A31,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A31,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A31,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2481,7 +2509,7 @@
         <v>6</v>
       </c>
       <c r="U32">
-        <f>SUMIF(Scoring!K2:K103,A32,Scoring!I2:I103)/SUMIF(Scoring!K2:K103,A32,Scoring!F2:F103)</f>
+        <f>SUMIF(Scoring!K2:K104,A32,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A32,Scoring!F2:F104)</f>
         <v>0</v>
       </c>
     </row>
@@ -2504,7 +2532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -2566,19 +2594,19 @@
         <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2598,19 +2626,19 @@
         <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2630,19 +2658,19 @@
         <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2662,19 +2690,19 @@
         <v>46</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2696,16 +2724,16 @@
         <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2725,16 +2753,16 @@
         <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -2754,16 +2782,16 @@
         <v>49</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -2783,19 +2811,19 @@
         <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -2815,16 +2843,16 @@
         <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E10" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -2846,16 +2874,16 @@
         <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -2875,16 +2903,16 @@
         <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -2904,16 +2932,16 @@
         <v>54</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -2933,16 +2961,16 @@
         <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -2962,16 +2990,16 @@
         <v>56</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -2991,16 +3019,16 @@
         <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3022,19 +3050,19 @@
         <v>58</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3054,19 +3082,19 @@
         <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E18" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3086,19 +3114,19 @@
         <v>60</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3113,26 +3141,24 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E20" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3142,29 +3168,31 @@
         <v>7</v>
       </c>
       <c r="K20" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="C21" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E21" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3184,19 +3212,19 @@
         <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E22" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3216,19 +3244,19 @@
         <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E23" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3248,19 +3276,19 @@
         <v>65</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E24" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3280,19 +3308,19 @@
         <v>66</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E25" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3307,23 +3335,24 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2"/>
-      <c r="B26" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E26" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
+      <c r="G26" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="H26" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3333,26 +3362,28 @@
         <v>7</v>
       </c>
       <c r="K26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="C27" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E27" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3372,16 +3403,16 @@
         <v>69</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E28" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3401,16 +3432,16 @@
         <v>70</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E29" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3430,16 +3461,16 @@
         <v>71</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E30" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3459,16 +3490,16 @@
         <v>72</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E31" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3483,23 +3514,21 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2"/>
-      <c r="B32" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E32" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3509,62 +3538,61 @@
         <v>7</v>
       </c>
       <c r="K32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E33" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
         <v>0</v>
       </c>
       <c r="J33" t="s">
+        <v>7</v>
+      </c>
+      <c r="K33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K33" t="s">
+      <c r="B34" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E34" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="H34" s="1" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -3584,16 +3612,19 @@
         <v>76</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E35" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
+      <c r="G35" s="1" t="s">
+        <v>269</v>
+      </c>
       <c r="H35" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -3613,16 +3644,16 @@
         <v>77</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E36" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -3642,16 +3673,16 @@
         <v>78</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E37" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -3671,19 +3702,16 @@
         <v>79</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E38" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="H38" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -3703,16 +3731,19 @@
         <v>80</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E39" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
+      <c r="G39" s="1" t="s">
+        <v>270</v>
+      </c>
       <c r="H39" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -3732,16 +3763,16 @@
         <v>81</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E40" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -3761,16 +3792,16 @@
         <v>82</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E41" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -3785,23 +3816,21 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="2"/>
-      <c r="B42" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
         <v>83</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E42" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -3811,26 +3840,28 @@
         <v>9</v>
       </c>
       <c r="K42" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
+      <c r="B43" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="C43" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E43" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -3850,16 +3881,16 @@
         <v>85</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E44" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -3879,16 +3910,16 @@
         <v>86</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E45" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -3908,16 +3939,16 @@
         <v>87</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E46" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -3937,16 +3968,16 @@
         <v>88</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E47" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -3961,23 +3992,21 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="2"/>
-      <c r="B48" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E48" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -3987,26 +4016,28 @@
         <v>9</v>
       </c>
       <c r="K48" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C49" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E49" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4026,19 +4057,16 @@
         <v>91</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E50" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="H50" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4053,23 +4081,24 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="2"/>
-      <c r="B51" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E51" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
+      <c r="G51" s="1" t="s">
+        <v>271</v>
+      </c>
       <c r="H51" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4079,26 +4108,28 @@
         <v>9</v>
       </c>
       <c r="K51" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
+      <c r="B52" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C52" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E52" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4118,16 +4149,16 @@
         <v>94</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E53" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4147,16 +4178,16 @@
         <v>95</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E54" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4176,16 +4207,16 @@
         <v>96</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E55" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4205,16 +4236,16 @@
         <v>97</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E56" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4229,26 +4260,21 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2"/>
-      <c r="B57" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B57" s="2"/>
       <c r="C57" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E57" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="H57" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4258,29 +4284,31 @@
         <v>9</v>
       </c>
       <c r="K57" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C58" s="2" t="s">
         <v>99</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E58" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4300,19 +4328,19 @@
         <v>100</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E59" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4332,19 +4360,19 @@
         <v>101</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E60" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4364,19 +4392,19 @@
         <v>102</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E61" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4396,19 +4424,19 @@
         <v>103</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E62" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4423,26 +4451,24 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2"/>
-      <c r="B63" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B63" s="2"/>
       <c r="C63" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E63" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4452,29 +4478,31 @@
         <v>9</v>
       </c>
       <c r="K63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
+      <c r="B64" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C64" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E64" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4494,16 +4522,19 @@
         <v>106</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E65" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
+      <c r="G65" s="1" t="s">
+        <v>279</v>
+      </c>
       <c r="H65" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4523,19 +4554,16 @@
         <v>107</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E66" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="H66" s="1" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4550,23 +4578,24 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="2"/>
-      <c r="B67" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B67" s="2"/>
       <c r="C67" s="2" t="s">
         <v>108</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E67" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
+      <c r="G67" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="H67" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -4576,29 +4605,28 @@
         <v>9</v>
       </c>
       <c r="K67" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
+      <c r="B68" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C68" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E68" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="H68" s="1" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -4618,19 +4646,19 @@
         <v>110</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E69" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -4650,16 +4678,19 @@
         <v>111</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E70" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
+      <c r="G70" s="1" t="s">
+        <v>282</v>
+      </c>
       <c r="H70" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -4674,23 +4705,21 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="2"/>
-      <c r="B71" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B71" s="2"/>
       <c r="C71" s="2" t="s">
         <v>112</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E71" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -4700,29 +4729,28 @@
         <v>9</v>
       </c>
       <c r="K71" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="C72" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E72" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="H72" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -4742,19 +4770,19 @@
         <v>114</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E73" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -4774,16 +4802,19 @@
         <v>115</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E74" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
+      <c r="G74" s="1" t="s">
+        <v>284</v>
+      </c>
       <c r="H74" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -4803,16 +4834,16 @@
         <v>116</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E75" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -4832,16 +4863,16 @@
         <v>117</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E76" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -4861,16 +4892,16 @@
         <v>118</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E77" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -4884,57 +4915,55 @@
       </c>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
       <c r="C78" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E78" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
         <v>0</v>
       </c>
       <c r="J78" t="s">
+        <v>9</v>
+      </c>
+      <c r="K78" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K78" t="s">
+      <c r="B79" s="2" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E79" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -4944,26 +4973,28 @@
         <v>8</v>
       </c>
       <c r="K79" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
+      <c r="B80" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C80" s="2" t="s">
         <v>121</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E80" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -4983,16 +5014,16 @@
         <v>122</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E81" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5012,16 +5043,16 @@
         <v>123</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E82" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5041,16 +5072,16 @@
         <v>124</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E83" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5070,16 +5101,16 @@
         <v>125</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E84" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5094,26 +5125,21 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="2"/>
-      <c r="B85" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="B85" s="2"/>
       <c r="C85" s="2" t="s">
         <v>126</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E85" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
-      <c r="G85" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="H85" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5123,26 +5149,31 @@
         <v>8</v>
       </c>
       <c r="K85" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
+      <c r="B86" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="C86" s="2" t="s">
         <v>127</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E86" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
+      <c r="G86" s="1" t="s">
+        <v>285</v>
+      </c>
       <c r="H86" s="1" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5162,19 +5193,16 @@
         <v>128</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E87" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
-      <c r="G87" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="H87" s="1" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5194,16 +5222,19 @@
         <v>129</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E88" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
+      <c r="G88" s="1" t="s">
+        <v>286</v>
+      </c>
       <c r="H88" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5223,19 +5254,16 @@
         <v>130</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E89" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
-      <c r="G89" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="H89" s="1" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5250,26 +5278,24 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="2"/>
-      <c r="B90" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
         <v>131</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E90" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5279,29 +5305,31 @@
         <v>8</v>
       </c>
       <c r="K90" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
+      <c r="B91" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C91" s="2" t="s">
         <v>132</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E91" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5321,19 +5349,19 @@
         <v>133</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E92" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5353,19 +5381,19 @@
         <v>134</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E93" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5385,19 +5413,19 @@
         <v>135</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E94" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5417,16 +5445,19 @@
         <v>136</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E95" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
+      <c r="G95" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="H95" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -5446,19 +5477,16 @@
         <v>137</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E96" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
-      <c r="G96" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="H96" s="1" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -5473,26 +5501,24 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="2"/>
-      <c r="B97" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="B97" s="2"/>
       <c r="C97" s="2" t="s">
         <v>138</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E97" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -5502,29 +5528,31 @@
         <v>8</v>
       </c>
       <c r="K97" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
+      <c r="B98" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="C98" s="2" t="s">
         <v>139</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E98" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -5544,19 +5572,19 @@
         <v>140</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E99" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -5576,19 +5604,19 @@
         <v>141</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E100" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -5608,19 +5636,19 @@
         <v>142</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E101" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -5640,16 +5668,19 @@
         <v>143</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E102" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
+      <c r="G102" s="1" t="s">
+        <v>298</v>
+      </c>
       <c r="H102" s="1" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -5663,63 +5694,92 @@
       </c>
     </row>
     <row r="103" spans="1:11">
-      <c r="A103" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
         <v>144</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E103" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
         <v>0</v>
       </c>
       <c r="J103" t="s">
+        <v>8</v>
+      </c>
+      <c r="K103" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K103" t="s">
+      <c r="B104" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E104" t="s">
+        <v>251</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I104">
+        <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J104" t="s">
+        <v>6</v>
+      </c>
+      <c r="K104" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A2:A32"/>
-    <mergeCell ref="A33:A77"/>
-    <mergeCell ref="A78:A102"/>
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="A34:A78"/>
+    <mergeCell ref="A79:A103"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="B11:B16"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="B26:B31"/>
-    <mergeCell ref="B33:B41"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B51:B56"/>
-    <mergeCell ref="B57:B62"/>
-    <mergeCell ref="B63:B66"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="B71:B77"/>
-    <mergeCell ref="B79:B84"/>
-    <mergeCell ref="B85:B89"/>
-    <mergeCell ref="B90:B96"/>
-    <mergeCell ref="B97:B102"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B21:B26"/>
+    <mergeCell ref="B27:B32"/>
+    <mergeCell ref="B34:B42"/>
+    <mergeCell ref="B43:B48"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="B52:B57"/>
+    <mergeCell ref="B58:B63"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="B72:B78"/>
+    <mergeCell ref="B80:B85"/>
+    <mergeCell ref="B86:B90"/>
+    <mergeCell ref="B91:B97"/>
+    <mergeCell ref="B98:B103"/>
   </mergeCells>
-  <dataValidations count="102">
+  <dataValidations count="103">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"0: 0 items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
@@ -5766,73 +5826,73 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
+      <formula1>"0: Low Maturity (0-9),4: Developing (10-18),7: Established (19-26),10: Optimizing (27-31)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
       <formula1>"0: Low Maturity. Score Range (0-8),4: Developing. Score Range (9-17),7: Established. Score Range (18-24),10: Optimizing. Score Range (25-29)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
       <formula1>"0: Low Maturity. Score Range (0-15),4: Developing. Score Range (16-31),7: Established. Score Range (32-44),10: Optimizing. Score Range (45-52)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
       <formula1>"0: No items completed,2: item 1 completed,4: items 1-2 completed,6: items 1-3 completed,8: items 1-4 completed,10: items 1-5 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
       <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
       <formula1>"0: Not done,10: Done and clearly defined"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
       <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
       <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -5841,43 +5901,43 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
       <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -5886,79 +5946,79 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
       <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
       <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
       <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
-      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
+      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
       <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H75">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
       <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H78">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
       <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -5970,22 +6030,22 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H85">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
       <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
       <formula1>"0: No alerting,10: Alerting exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
@@ -5994,36 +6054,39 @@
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
       <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
       <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
       <formula1>"0: Not monitored,2: Reported,5: Manual remediation,10: Automated remediation"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6130,6 +6193,7 @@
     <hyperlink ref="D101" r:id="rId100"/>
     <hyperlink ref="D102" r:id="rId101"/>
     <hyperlink ref="D103" r:id="rId102"/>
+    <hyperlink ref="D104" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -1442,7 +1442,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:style val="37"/>
+  <c:style val="29"/>
   <c:chart>
     <c:plotArea>
       <c:layout/>
@@ -1528,7 +1528,6 @@
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
-    <c:plotVisOnly val="1"/>
   </c:chart>
 </c:chartSpace>
 </file>
@@ -1536,7 +1535,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:style val="37"/>
+  <c:style val="29"/>
   <c:chart>
     <c:plotArea>
       <c:layout/>
@@ -1724,7 +1723,6 @@
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
-    <c:plotVisOnly val="1"/>
   </c:chart>
 </c:chartSpace>
 </file>
@@ -2152,12 +2150,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:U33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -2533,7 +2532,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K104"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -2156,7 +2156,7 @@
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="0" hidden="1" customWidth="1"/>
+    <col min="6" max="16384" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -2190,6 +2190,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="1:21"/>
     <row r="4" spans="1:21">
       <c r="A4" t="s">
         <v>4</v>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -1517,11 +1517,12 @@
         <c:axId val="50020002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="10"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -1712,11 +1713,12 @@
         <c:axId val="50030002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="10"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
@@ -2253,6 +2255,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10" spans="1:21"/>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
         <v>10</v>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="414">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -160,6 +160,9 @@
     <t>Prioritize Actions &amp; Publish Roadmap</t>
   </si>
   <si>
+    <t>Reassess Progress &amp; Update Priorities</t>
+  </si>
+  <si>
     <t>Assess Skills &amp; Training Needs</t>
   </si>
   <si>
@@ -205,6 +208,9 @@
     <t>Train Users &amp; Integrate Data</t>
   </si>
   <si>
+    <t>Monitor Adoption &amp; Iterate Tools</t>
+  </si>
+  <si>
     <t>Establish Cross-Team Collab</t>
   </si>
   <si>
@@ -244,6 +250,15 @@
     <t>Establish Executive Sponsorship</t>
   </si>
   <si>
+    <t>Define Decision Rights &amp; Guardrails</t>
+  </si>
+  <si>
+    <t>Build Multi-Year Investment Forecast</t>
+  </si>
+  <si>
+    <t>Establish Decision Support Cadence</t>
+  </si>
+  <si>
     <t>Establish Architecture Review Process</t>
   </si>
   <si>
@@ -253,6 +268,15 @@
     <t>Estimate Trade-Offs &amp; Document Cases</t>
   </si>
   <si>
+    <t>Implement Iteratively &amp; Measure Results</t>
+  </si>
+  <si>
+    <t>Publish Benefits &amp; Update References</t>
+  </si>
+  <si>
+    <t>Strengthen Architecture Collaboration</t>
+  </si>
+  <si>
     <t>Create Workload Selection Criteria</t>
   </si>
   <si>
@@ -295,6 +319,15 @@
     <t>Build Commitment Analysis Process</t>
   </si>
   <si>
+    <t>Purchase Commitments Regularly</t>
+  </si>
+  <si>
+    <t>Track ROI &amp; Notify Owners</t>
+  </si>
+  <si>
+    <t>Allocate Upfront Costs Transparently</t>
+  </si>
+  <si>
     <t>Leverage Spot &amp; Negotiated Discounts</t>
   </si>
   <si>
@@ -334,6 +367,9 @@
     <t>Automate Tagging &amp; Enforcement</t>
   </si>
   <si>
+    <t>Iterate Strategies &amp; Communicate</t>
+  </si>
+  <si>
     <t>Configure Cost Spike Detection</t>
   </si>
   <si>
@@ -343,18 +379,42 @@
     <t>Automate Alert Routing</t>
   </si>
   <si>
+    <t>Record Anomaly Context &amp; Timeline</t>
+  </si>
+  <si>
+    <t>Analyze Root Causes &amp; Fix Issues</t>
+  </si>
+  <si>
     <t>Track Metrics &amp; Avoidance Rates</t>
   </si>
   <si>
+    <t>Tune Thresholds to Reduce Noise</t>
+  </si>
+  <si>
+    <t>Inventory All Data Sources</t>
+  </si>
+  <si>
+    <t>Choose Data Landing Tooling</t>
+  </si>
+  <si>
+    <t>Create Landing Zones &amp; Controls</t>
+  </si>
+  <si>
     <t>Define Data Granularity &amp; Frequency</t>
   </si>
   <si>
+    <t>Document Normalization Rules</t>
+  </si>
+  <si>
     <t>Implement Data Quality Checks</t>
   </si>
   <si>
     <t>Build Ingestion Anomaly Dashboards</t>
   </si>
   <si>
+    <t>Optimize Pipelines for Timeliness</t>
+  </si>
+  <si>
     <t>Define ingestion frequency; include mandatory metadata.</t>
   </si>
   <si>
@@ -379,9 +439,24 @@
     <t>Iterate Based on Feedback</t>
   </si>
   <si>
+    <t>Select KPIs &amp; Measurement Scope</t>
+  </si>
+  <si>
+    <t>Validate Tagging for Comparability</t>
+  </si>
+  <si>
+    <t>Choose Internal vs External Benchmarks</t>
+  </si>
+  <si>
+    <t>Stand Up Internal Benchmarking</t>
+  </si>
+  <si>
     <t>Track Trends &amp; Compare Over Time</t>
   </si>
   <si>
+    <t>Translate Gaps to Initiatives</t>
+  </si>
+  <si>
     <t>Define Budgeting Strategy</t>
   </si>
   <si>
@@ -400,6 +475,9 @@
     <t>Review &amp; Adapt Budget Strategy</t>
   </si>
   <si>
+    <t>Establish Forecasting Approach</t>
+  </si>
+  <si>
     <t>Collect Business Drivers Regularly</t>
   </si>
   <si>
@@ -454,9 +532,21 @@
     <t>Communicate Unit Cost Wins</t>
   </si>
   <si>
+    <t>Draft Cloud Financial Policies</t>
+  </si>
+  <si>
+    <t>Publish Guidelines &amp; Guardrails</t>
+  </si>
+  <si>
+    <t>Educate Stakeholders on Policy</t>
+  </si>
+  <si>
     <t>Monitor Compliance &amp; Report Breaches</t>
   </si>
   <si>
+    <t>Iterate Policies Based on Feedback</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
@@ -469,6 +559,9 @@
     <t>116</t>
   </si>
   <si>
+    <t>117</t>
+  </si>
+  <si>
     <t>097</t>
   </si>
   <si>
@@ -514,6 +607,9 @@
     <t>127</t>
   </si>
   <si>
+    <t>128</t>
+  </si>
+  <si>
     <t>129</t>
   </si>
   <si>
@@ -553,6 +649,15 @@
     <t>136</t>
   </si>
   <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
     <t>061</t>
   </si>
   <si>
@@ -562,6 +667,15 @@
     <t>063</t>
   </si>
   <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
     <t>118</t>
   </si>
   <si>
@@ -604,6 +718,15 @@
     <t>080</t>
   </si>
   <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
     <t>084</t>
   </si>
   <si>
@@ -643,6 +766,9 @@
     <t>014</t>
   </si>
   <si>
+    <t>015</t>
+  </si>
+  <si>
     <t>023</t>
   </si>
   <si>
@@ -652,18 +778,42 @@
     <t>025</t>
   </si>
   <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
     <t>028</t>
   </si>
   <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
     <t>004</t>
   </si>
   <si>
+    <t>005</t>
+  </si>
+  <si>
     <t>006</t>
   </si>
   <si>
     <t>007</t>
   </si>
   <si>
+    <t>008</t>
+  </si>
+  <si>
     <t>135</t>
   </si>
   <si>
@@ -688,9 +838,24 @@
     <t>022</t>
   </si>
   <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
     <t>053</t>
   </si>
   <si>
+    <t>054</t>
+  </si>
+  <si>
     <t>043</t>
   </si>
   <si>
@@ -709,6 +874,9 @@
     <t>048</t>
   </si>
   <si>
+    <t>037</t>
+  </si>
+  <si>
     <t>038</t>
   </si>
   <si>
@@ -763,7 +931,19 @@
     <t>060</t>
   </si>
   <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
     <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
   </si>
   <si>
     <t>1.1.0</t>
@@ -805,6 +985,12 @@
 2. Determine owners for addressing each of the prioritized gaps
 3. Owners will work with relevant teams to scope out how to meet the target score for each gap
 4. Work is then scheduled in a roadmap with deadlines that can be tracked at the leadership level</t>
+  </si>
+  <si>
+    <t>* Schedule a cadence to report progress outcomes to key stakeholders.
+* Create reporting to show progress on key outcomes across all maturity initiatives.
+* After successful outcomes are achieved, move on to the next prioritized item in the roadmap.
+* Periodically reevaluate the gap analysis and priority list based on lessons learned and new business goals.</t>
   </si>
   <si>
     <t>* Define process for reviewing asking for credits from CSPs
@@ -905,6 +1091,24 @@
     <t>* Come up with shared responses as allied teams to external conflicts
 * Resolve internal conflicts before deciding on the next steps needed to reach shared goals
 * Communication to external teams or leaders includes the full story of how allied teams achieve goals together
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Document decision rights and approval authority for technology spend
+* Define and publish spend guardrails with named owners
+* Establish escalation path for spend exceptions
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Inventory vendor commitments across technology categories (cloud, SaaS, data center, AI)
+* Create a multi-year forecast incorporating renewal timelines and growth projections
+* Incorporate transition and modernization costs into the investment plan
+10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>* Define a regular review cadence for technology investment decisions
+* Deliver cost and outcome comparisons for competing initiatives at reviews
+* Track and report action follow-through from investment decisions
 10*Ceil(x/3)</t>
   </si>
   <si>
@@ -2177,14 +2381,14 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2">
-        <f>SUM(Scoring!F2:F104)</f>
+        <f>SUM(Scoring!F2:F134)</f>
         <v>0</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2">
-        <f>SUM(Scoring!I2:I104)/A2</f>
+        <f>SUM(Scoring!I2:I134)/A2</f>
         <v>0</v>
       </c>
       <c r="D2">
@@ -2206,10 +2410,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U5">
-        <f>SUMIF(Scoring!J2:J104,A5,Scoring!I2:I104)/SUMIF(Scoring!J2:J104,A5,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!J2:J134,A5,Scoring!I2:I134)/SUMIF(Scoring!J2:J134,A5,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2218,10 +2422,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="U6">
-        <f>SUMIF(Scoring!J2:J104,A6,Scoring!I2:I104)/SUMIF(Scoring!J2:J104,A6,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!J2:J134,A6,Scoring!I2:I134)/SUMIF(Scoring!J2:J134,A6,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2230,10 +2434,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="U7">
-        <f>SUMIF(Scoring!J2:J104,A7,Scoring!I2:I104)/SUMIF(Scoring!J2:J104,A7,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!J2:J134,A7,Scoring!I2:I134)/SUMIF(Scoring!J2:J134,A7,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2242,10 +2446,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="U8">
-        <f>SUMIF(Scoring!J2:J104,A8,Scoring!I2:I104)/SUMIF(Scoring!J2:J104,A8,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!J2:J134,A8,Scoring!I2:I134)/SUMIF(Scoring!J2:J134,A8,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2269,10 +2473,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <f>SUMIF(Scoring!K2:K104,A12,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A12,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A12,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A12,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2281,10 +2485,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <f>SUMIF(Scoring!K2:K104,A13,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A13,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A13,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A13,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2293,10 +2497,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U14">
-        <f>SUMIF(Scoring!K2:K104,A14,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A14,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A14,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A14,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2305,10 +2509,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <f>SUMIF(Scoring!K2:K104,A15,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A15,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A15,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A15,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2320,7 +2524,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <f>SUMIF(Scoring!K2:K104,A16,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A16,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A16,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A16,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2329,10 +2533,10 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <f>SUMIF(Scoring!K2:K104,A17,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A17,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A17,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A17,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2341,10 +2545,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <f>SUMIF(Scoring!K2:K104,A18,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A18,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A18,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A18,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2353,10 +2557,10 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <f>SUMIF(Scoring!K2:K104,A19,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A19,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A19,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A19,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2368,7 +2572,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <f>SUMIF(Scoring!K2:K104,A20,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A20,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A20,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A20,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2380,7 +2584,7 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <f>SUMIF(Scoring!K2:K104,A21,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A21,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A21,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A21,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2389,10 +2593,10 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <f>SUMIF(Scoring!K2:K104,A22,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A22,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A22,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A22,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2404,7 +2608,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <f>SUMIF(Scoring!K2:K104,A23,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A23,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A23,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A23,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2416,7 +2620,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <f>SUMIF(Scoring!K2:K104,A24,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A24,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A24,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A24,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2425,10 +2629,10 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <f>SUMIF(Scoring!K2:K104,A25,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A25,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A25,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A25,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2440,7 +2644,7 @@
         <v>6</v>
       </c>
       <c r="U26">
-        <f>SUMIF(Scoring!K2:K104,A26,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A26,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A26,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A26,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2452,7 +2656,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <f>SUMIF(Scoring!K2:K104,A27,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A27,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A27,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A27,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2461,10 +2665,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U28">
-        <f>SUMIF(Scoring!K2:K104,A28,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A28,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A28,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A28,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2473,10 +2677,10 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <f>SUMIF(Scoring!K2:K104,A29,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A29,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A29,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A29,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2488,7 +2692,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <f>SUMIF(Scoring!K2:K104,A30,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A30,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A30,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A30,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2500,7 +2704,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <f>SUMIF(Scoring!K2:K104,A31,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A31,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A31,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A31,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2512,7 +2716,7 @@
         <v>6</v>
       </c>
       <c r="U32">
-        <f>SUMIF(Scoring!K2:K104,A32,Scoring!I2:I104)/SUMIF(Scoring!K2:K104,A32,Scoring!F2:F104)</f>
+        <f>SUMIF(Scoring!K2:K134,A32,Scoring!I2:I134)/SUMIF(Scoring!K2:K134,A32,Scoring!F2:F134)</f>
         <v>0</v>
       </c>
     </row>
@@ -2535,7 +2739,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K134"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -2597,19 +2801,19 @@
         <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>332</v>
+        <v>396</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2629,19 +2833,19 @@
         <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="E3" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>255</v>
+        <v>315</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2661,19 +2865,19 @@
         <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="E4" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>256</v>
+        <v>316</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2693,19 +2897,19 @@
         <v>46</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>257</v>
+        <v>317</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2720,23 +2924,24 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E6" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
+      <c r="G6" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="H6" s="1" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2746,26 +2951,28 @@
         <v>7</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C7" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="E7" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -2785,16 +2992,16 @@
         <v>49</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="E8" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -2814,19 +3021,16 @@
         <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="E9" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -2846,16 +3050,19 @@
         <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="E10" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
+      <c r="G10" s="1" t="s">
+        <v>319</v>
+      </c>
       <c r="H10" s="1" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -2870,23 +3077,21 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E11" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -2896,26 +3101,28 @@
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C12" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="E12" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -2935,16 +3142,16 @@
         <v>54</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="E13" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -2964,16 +3171,16 @@
         <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="E14" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -2993,16 +3200,16 @@
         <v>56</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="E15" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3022,16 +3229,16 @@
         <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="E16" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3046,26 +3253,21 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2"/>
-      <c r="B17" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="E17" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="H17" s="1" t="s">
-        <v>335</v>
+        <v>398</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3075,29 +3277,31 @@
         <v>7</v>
       </c>
       <c r="K17" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="C18" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="E18" t="s">
-        <v>252</v>
+        <v>310</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>336</v>
+        <v>399</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3117,19 +3321,19 @@
         <v>60</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="E19" t="s">
-        <v>249</v>
+        <v>312</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>261</v>
+        <v>321</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>337</v>
+        <v>400</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3149,19 +3353,19 @@
         <v>61</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="E20" t="s">
-        <v>251</v>
+        <v>309</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>333</v>
+        <v>401</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3176,26 +3380,24 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="E21" t="s">
-        <v>249</v>
+        <v>311</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3205,7 +3407,7 @@
         <v>7</v>
       </c>
       <c r="K21" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3215,19 +3417,16 @@
         <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="E22" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="H22" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3237,29 +3436,31 @@
         <v>7</v>
       </c>
       <c r="K22" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="C23" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="E23" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3279,19 +3480,19 @@
         <v>65</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="E24" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3311,19 +3512,19 @@
         <v>66</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="E25" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>267</v>
+        <v>326</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3343,19 +3544,19 @@
         <v>67</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="E26" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>268</v>
+        <v>327</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3370,23 +3571,24 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2"/>
-      <c r="B27" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="E27" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
+      <c r="G27" s="1" t="s">
+        <v>328</v>
+      </c>
       <c r="H27" s="1" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3396,7 +3598,7 @@
         <v>7</v>
       </c>
       <c r="K27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3406,16 +3608,19 @@
         <v>69</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="E28" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
+      <c r="G28" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="H28" s="1" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3425,26 +3630,28 @@
         <v>7</v>
       </c>
       <c r="K28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="C29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="E29" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3464,16 +3671,16 @@
         <v>71</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="E30" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3493,16 +3700,16 @@
         <v>72</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="E31" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3522,16 +3729,16 @@
         <v>73</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E32" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3546,23 +3753,21 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2"/>
-      <c r="B33" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="E33" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>338</v>
+        <v>398</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3572,72 +3777,67 @@
         <v>7</v>
       </c>
       <c r="K33" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="E34" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K34" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
+      <c r="B35" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C35" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="E35" t="s">
-        <v>251</v>
+        <v>309</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="H35" s="1" t="s">
-        <v>333</v>
+        <v>402</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3647,26 +3847,29 @@
         <v>77</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="E36" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
+      <c r="G36" s="1" t="s">
+        <v>330</v>
+      </c>
       <c r="H36" s="1" t="s">
-        <v>340</v>
+        <v>397</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3676,26 +3879,29 @@
         <v>78</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="E37" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
+      <c r="G37" s="1" t="s">
+        <v>331</v>
+      </c>
       <c r="H37" s="1" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3705,48 +3911,52 @@
         <v>79</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="E38" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
+      <c r="G38" s="1" t="s">
+        <v>332</v>
+      </c>
       <c r="H38" s="1" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
         <v>0</v>
       </c>
       <c r="J38" t="s">
+        <v>7</v>
+      </c>
+      <c r="K38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K38" t="s">
+      <c r="B39" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="E39" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="H39" s="1" t="s">
-        <v>333</v>
+        <v>403</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -3766,16 +3976,19 @@
         <v>81</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="E40" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
+      <c r="G40" s="1" t="s">
+        <v>333</v>
+      </c>
       <c r="H40" s="1" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -3795,16 +4008,16 @@
         <v>82</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="E41" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>334</v>
+        <v>404</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -3824,16 +4037,16 @@
         <v>83</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="E42" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -3848,23 +4061,21 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="2"/>
-      <c r="B43" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="E43" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -3874,7 +4085,7 @@
         <v>9</v>
       </c>
       <c r="K43" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -3884,16 +4095,16 @@
         <v>85</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="E44" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -3903,7 +4114,7 @@
         <v>9</v>
       </c>
       <c r="K44" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3913,16 +4124,16 @@
         <v>86</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="E45" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -3932,7 +4143,7 @@
         <v>9</v>
       </c>
       <c r="K45" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -3942,16 +4153,16 @@
         <v>87</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="E46" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -3961,7 +4172,7 @@
         <v>9</v>
       </c>
       <c r="K46" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -3971,16 +4182,19 @@
         <v>88</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="E47" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
+      <c r="G47" s="1" t="s">
+        <v>334</v>
+      </c>
       <c r="H47" s="1" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -3990,7 +4204,7 @@
         <v>9</v>
       </c>
       <c r="K47" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -4000,16 +4214,16 @@
         <v>89</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="E48" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4019,28 +4233,26 @@
         <v>9</v>
       </c>
       <c r="K48" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="2"/>
-      <c r="B49" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B49" s="2"/>
       <c r="C49" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="E49" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4050,7 +4262,7 @@
         <v>9</v>
       </c>
       <c r="K49" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -4060,16 +4272,16 @@
         <v>91</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="E50" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4079,29 +4291,28 @@
         <v>9</v>
       </c>
       <c r="K50" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
+      <c r="B51" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="C51" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="E51" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="H51" s="1" t="s">
-        <v>333</v>
+        <v>405</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4111,28 +4322,26 @@
         <v>9</v>
       </c>
       <c r="K51" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="2"/>
-      <c r="B52" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B52" s="2"/>
       <c r="C52" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="E52" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4142,7 +4351,7 @@
         <v>9</v>
       </c>
       <c r="K52" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -4152,16 +4361,16 @@
         <v>94</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="E53" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>342</v>
+        <v>398</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4171,7 +4380,7 @@
         <v>9</v>
       </c>
       <c r="K53" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4181,16 +4390,16 @@
         <v>95</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="E54" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4200,7 +4409,7 @@
         <v>9</v>
       </c>
       <c r="K54" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -4210,16 +4419,16 @@
         <v>96</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="E55" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4229,7 +4438,7 @@
         <v>9</v>
       </c>
       <c r="K55" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -4239,16 +4448,16 @@
         <v>97</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="E56" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4258,26 +4467,28 @@
         <v>9</v>
       </c>
       <c r="K56" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
+      <c r="B57" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C57" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="E57" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4287,31 +4498,26 @@
         <v>9</v>
       </c>
       <c r="K57" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="2"/>
-      <c r="B58" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B58" s="2"/>
       <c r="C58" s="2" t="s">
         <v>99</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="E58" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="H58" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4321,7 +4527,7 @@
         <v>9</v>
       </c>
       <c r="K58" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -4331,19 +4537,16 @@
         <v>100</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="E59" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="H59" s="1" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4353,7 +4556,7 @@
         <v>9</v>
       </c>
       <c r="K59" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -4363,19 +4566,16 @@
         <v>101</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E60" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="H60" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4385,7 +4585,7 @@
         <v>9</v>
       </c>
       <c r="K60" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -4395,19 +4595,16 @@
         <v>102</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="E61" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="H61" s="1" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4417,7 +4614,7 @@
         <v>9</v>
       </c>
       <c r="K61" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -4427,19 +4624,19 @@
         <v>103</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="E62" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>276</v>
+        <v>335</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>341</v>
+        <v>397</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4449,29 +4646,28 @@
         <v>9</v>
       </c>
       <c r="K62" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
+      <c r="B63" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C63" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="E63" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="H63" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4481,31 +4677,26 @@
         <v>9</v>
       </c>
       <c r="K63" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="2"/>
-      <c r="B64" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B64" s="2"/>
       <c r="C64" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="E64" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="H64" s="1" t="s">
-        <v>333</v>
+        <v>406</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4515,7 +4706,7 @@
         <v>9</v>
       </c>
       <c r="K64" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -4525,19 +4716,16 @@
         <v>106</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="E65" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="H65" s="1" t="s">
-        <v>333</v>
+        <v>405</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4547,7 +4735,7 @@
         <v>9</v>
       </c>
       <c r="K65" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -4557,16 +4745,16 @@
         <v>107</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="E66" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>343</v>
+        <v>398</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4576,7 +4764,7 @@
         <v>9</v>
       </c>
       <c r="K66" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -4586,19 +4774,16 @@
         <v>108</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="E67" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="H67" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -4608,28 +4793,26 @@
         <v>9</v>
       </c>
       <c r="K67" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="2"/>
-      <c r="B68" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B68" s="2"/>
       <c r="C68" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="E68" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>344</v>
+        <v>398</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -4639,29 +4822,31 @@
         <v>9</v>
       </c>
       <c r="K68" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
+      <c r="B69" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C69" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -4671,7 +4856,7 @@
         <v>9</v>
       </c>
       <c r="K69" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -4681,19 +4866,19 @@
         <v>111</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="E70" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>333</v>
+        <v>405</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -4703,7 +4888,7 @@
         <v>9</v>
       </c>
       <c r="K70" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -4713,16 +4898,19 @@
         <v>112</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="E71" t="s">
-        <v>253</v>
+        <v>311</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
+      <c r="G71" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="H71" s="1" t="s">
-        <v>344</v>
+        <v>397</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -4732,28 +4920,29 @@
         <v>9</v>
       </c>
       <c r="K71" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="2"/>
-      <c r="B72" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B72" s="2"/>
       <c r="C72" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="E72" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
+      <c r="G72" s="1" t="s">
+        <v>339</v>
+      </c>
       <c r="H72" s="1" t="s">
-        <v>334</v>
+        <v>405</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -4763,7 +4952,7 @@
         <v>9</v>
       </c>
       <c r="K72" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -4773,19 +4962,19 @@
         <v>114</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="E73" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>283</v>
+        <v>340</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>333</v>
+        <v>405</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -4795,7 +4984,7 @@
         <v>9</v>
       </c>
       <c r="K73" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -4805,19 +4994,19 @@
         <v>115</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="E74" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>284</v>
+        <v>341</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -4827,7 +5016,7 @@
         <v>9</v>
       </c>
       <c r="K74" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -4837,16 +5026,16 @@
         <v>116</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="E75" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -4856,26 +5045,31 @@
         <v>9</v>
       </c>
       <c r="K75" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
+      <c r="B76" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C76" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="E76" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
+      <c r="G76" s="1" t="s">
+        <v>342</v>
+      </c>
       <c r="H76" s="1" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -4885,7 +5079,7 @@
         <v>9</v>
       </c>
       <c r="K76" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -4895,16 +5089,19 @@
         <v>118</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="E77" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
+      <c r="G77" s="1" t="s">
+        <v>343</v>
+      </c>
       <c r="H77" s="1" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -4914,7 +5111,7 @@
         <v>9</v>
       </c>
       <c r="K77" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -4924,16 +5121,16 @@
         <v>119</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="E78" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>334</v>
+        <v>407</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -4943,71 +5140,65 @@
         <v>9</v>
       </c>
       <c r="K78" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:11">
-      <c r="A79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
       <c r="C79" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="E79" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>346</v>
+        <v>398</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
         <v>0</v>
       </c>
       <c r="J79" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K79" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="2"/>
-      <c r="B80" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B80" s="2"/>
       <c r="C80" s="2" t="s">
         <v>121</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="E80" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
         <v>0</v>
       </c>
       <c r="J80" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K80" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -5017,26 +5208,29 @@
         <v>122</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="E81" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
+      <c r="G81" s="1" t="s">
+        <v>344</v>
+      </c>
       <c r="H81" s="1" t="s">
-        <v>339</v>
+        <v>397</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
         <v>0</v>
       </c>
       <c r="J81" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K81" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -5046,55 +5240,57 @@
         <v>123</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="E82" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
         <v>0</v>
       </c>
       <c r="J82" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K82" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
+      <c r="B83" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C83" s="2" t="s">
         <v>124</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="E83" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
         <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K83" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -5104,26 +5300,26 @@
         <v>125</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="E84" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
         <v>0</v>
       </c>
       <c r="J84" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K84" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -5133,60 +5329,55 @@
         <v>126</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="E85" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
         <v>0</v>
       </c>
       <c r="J85" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="2"/>
-      <c r="B86" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="B86" s="2"/>
       <c r="C86" s="2" t="s">
         <v>127</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="E86" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
-      <c r="G86" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="H86" s="1" t="s">
-        <v>333</v>
+        <v>408</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
         <v>0</v>
       </c>
       <c r="J86" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K86" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -5196,26 +5387,26 @@
         <v>128</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="E87" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>347</v>
+        <v>398</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K87" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -5225,29 +5416,29 @@
         <v>129</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="E88" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>286</v>
+        <v>345</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>341</v>
+        <v>397</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
         <v>0</v>
       </c>
       <c r="J88" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K88" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -5257,26 +5448,29 @@
         <v>130</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="E89" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
+      <c r="G89" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="H89" s="1" t="s">
-        <v>348</v>
+        <v>397</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
         <v>0</v>
       </c>
       <c r="J89" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K89" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -5286,95 +5480,86 @@
         <v>131</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="E90" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
-      <c r="G90" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="H90" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K90" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="2"/>
-      <c r="B91" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="B91" s="2"/>
       <c r="C91" s="2" t="s">
         <v>132</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="E91" t="s">
-        <v>249</v>
+        <v>313</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
-      <c r="G91" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="H91" s="1" t="s">
-        <v>333</v>
+        <v>408</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
         <v>0</v>
       </c>
       <c r="J91" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K91" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
+      <c r="B92" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="C92" s="2" t="s">
         <v>133</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="E92" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
-      <c r="G92" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="H92" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K92" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -5384,29 +5569,29 @@
         <v>134</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="E93" t="s">
-        <v>249</v>
+        <v>311</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>290</v>
+        <v>347</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K93" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -5416,29 +5601,29 @@
         <v>135</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="E94" t="s">
-        <v>249</v>
+        <v>311</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>291</v>
+        <v>348</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K94" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -5448,29 +5633,26 @@
         <v>136</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="E95" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
-      <c r="G95" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="H95" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K95" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -5480,26 +5662,26 @@
         <v>137</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="E96" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>341</v>
+        <v>409</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
         <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K96" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -5509,85 +5691,78 @@
         <v>138</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="E97" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
-      <c r="G97" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="H97" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K97" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="2"/>
-      <c r="B98" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="B98" s="2"/>
       <c r="C98" s="2" t="s">
         <v>139</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="E98" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
-      <c r="G98" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="H98" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
         <v>0</v>
       </c>
       <c r="J98" t="s">
+        <v>9</v>
+      </c>
+      <c r="K98" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K98" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
+      <c r="B99" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C99" s="2" t="s">
         <v>140</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="E99" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
-      <c r="G99" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="H99" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -5597,7 +5772,7 @@
         <v>8</v>
       </c>
       <c r="K99" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -5607,19 +5782,16 @@
         <v>141</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="E100" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
-      <c r="G100" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="H100" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -5629,7 +5801,7 @@
         <v>8</v>
       </c>
       <c r="K100" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -5639,19 +5811,16 @@
         <v>142</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="E101" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
-      <c r="G101" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="H101" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -5661,7 +5830,7 @@
         <v>8</v>
       </c>
       <c r="K101" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -5671,19 +5840,16 @@
         <v>143</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="E102" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
-      <c r="G102" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="H102" s="1" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -5693,7 +5859,7 @@
         <v>8</v>
       </c>
       <c r="K102" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -5703,16 +5869,16 @@
         <v>144</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="E103" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>347</v>
+        <v>410</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -5722,67 +5888,991 @@
         <v>8</v>
       </c>
       <c r="K103" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104" spans="1:11">
-      <c r="A104" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
       <c r="C104" s="2" t="s">
         <v>145</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="E104" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>349</v>
+        <v>398</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
         <v>0</v>
       </c>
       <c r="J104" t="s">
+        <v>8</v>
+      </c>
+      <c r="K104" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E105" t="s">
+        <v>311</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="I105">
+        <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J105" t="s">
+        <v>8</v>
+      </c>
+      <c r="K105" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E106" t="s">
+        <v>311</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="I106">
+        <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J106" t="s">
+        <v>8</v>
+      </c>
+      <c r="K106" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E107" t="s">
+        <v>310</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I107">
+        <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J107" t="s">
+        <v>8</v>
+      </c>
+      <c r="K107" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E108" t="s">
+        <v>310</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I108">
+        <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J108" t="s">
+        <v>8</v>
+      </c>
+      <c r="K108" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E109" t="s">
+        <v>310</v>
+      </c>
+      <c r="F109">
+        <v>1</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I109">
+        <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J109" t="s">
+        <v>8</v>
+      </c>
+      <c r="K109" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E110" t="s">
+        <v>310</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I110">
+        <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J110" t="s">
+        <v>8</v>
+      </c>
+      <c r="K110" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" s="2"/>
+      <c r="B111" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E111" t="s">
+        <v>310</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I111">
+        <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J111" t="s">
+        <v>8</v>
+      </c>
+      <c r="K111" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E112" t="s">
+        <v>311</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I112">
+        <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J112" t="s">
+        <v>8</v>
+      </c>
+      <c r="K112" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E113" t="s">
+        <v>311</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="I113">
+        <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J113" t="s">
+        <v>8</v>
+      </c>
+      <c r="K113" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E114" t="s">
+        <v>311</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I114">
+        <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J114" t="s">
+        <v>8</v>
+      </c>
+      <c r="K114" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E115" t="s">
+        <v>311</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I115">
+        <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J115" t="s">
+        <v>8</v>
+      </c>
+      <c r="K115" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E116" t="s">
+        <v>311</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I116">
+        <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J116" t="s">
+        <v>8</v>
+      </c>
+      <c r="K116" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E117" t="s">
+        <v>309</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I117">
+        <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J117" t="s">
+        <v>8</v>
+      </c>
+      <c r="K117" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E118" t="s">
+        <v>309</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I118">
+        <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J118" t="s">
+        <v>8</v>
+      </c>
+      <c r="K118" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E119" t="s">
+        <v>309</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I119">
+        <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J119" t="s">
+        <v>8</v>
+      </c>
+      <c r="K119" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E120" t="s">
+        <v>309</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I120">
+        <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J120" t="s">
+        <v>8</v>
+      </c>
+      <c r="K120" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E121" t="s">
+        <v>311</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I121">
+        <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J121" t="s">
+        <v>8</v>
+      </c>
+      <c r="K121" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E122" t="s">
+        <v>311</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I122">
+        <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J122" t="s">
+        <v>8</v>
+      </c>
+      <c r="K122" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E123" t="s">
+        <v>309</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I123">
+        <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J123" t="s">
+        <v>8</v>
+      </c>
+      <c r="K123" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" s="2"/>
+      <c r="B124" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E124" t="s">
+        <v>311</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I124">
+        <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J124" t="s">
+        <v>8</v>
+      </c>
+      <c r="K124" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125" s="2"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E125" t="s">
+        <v>309</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I125">
+        <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J125" t="s">
+        <v>8</v>
+      </c>
+      <c r="K125" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E126" t="s">
+        <v>309</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I126">
+        <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J126" t="s">
+        <v>8</v>
+      </c>
+      <c r="K126" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E127" t="s">
+        <v>309</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I127">
+        <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J127" t="s">
+        <v>8</v>
+      </c>
+      <c r="K127" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E128" t="s">
+        <v>309</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I128">
+        <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J128" t="s">
+        <v>8</v>
+      </c>
+      <c r="K128" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E129" t="s">
+        <v>311</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="I129">
+        <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J129" t="s">
+        <v>8</v>
+      </c>
+      <c r="K129" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K104" t="s">
+      <c r="B130" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="C130" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E130" t="s">
+        <v>310</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I130">
+        <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J130" t="s">
+        <v>6</v>
+      </c>
+      <c r="K130" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="2"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E131" t="s">
+        <v>310</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I131">
+        <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J131" t="s">
+        <v>6</v>
+      </c>
+      <c r="K131" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" s="2"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E132" t="s">
+        <v>310</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I132">
+        <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J132" t="s">
+        <v>6</v>
+      </c>
+      <c r="K132" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133" s="2"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E133" t="s">
+        <v>311</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="I133">
+        <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J133" t="s">
+        <v>6</v>
+      </c>
+      <c r="K133" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E134" t="s">
+        <v>310</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I134">
+        <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
+        <v>0</v>
+      </c>
+      <c r="J134" t="s">
+        <v>6</v>
+      </c>
+      <c r="K134" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A2:A33"/>
-    <mergeCell ref="A34:A78"/>
-    <mergeCell ref="A79:A103"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="B11:B16"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B21:B26"/>
-    <mergeCell ref="B27:B32"/>
-    <mergeCell ref="B34:B42"/>
-    <mergeCell ref="B43:B48"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="B52:B57"/>
-    <mergeCell ref="B58:B63"/>
-    <mergeCell ref="B64:B67"/>
-    <mergeCell ref="B68:B71"/>
-    <mergeCell ref="B72:B78"/>
-    <mergeCell ref="B80:B85"/>
-    <mergeCell ref="B86:B90"/>
-    <mergeCell ref="B91:B97"/>
-    <mergeCell ref="B98:B103"/>
+  <mergeCells count="25">
+    <mergeCell ref="A2:A38"/>
+    <mergeCell ref="A39:A98"/>
+    <mergeCell ref="A99:A129"/>
+    <mergeCell ref="A130:A134"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B39:B50"/>
+    <mergeCell ref="B51:B56"/>
+    <mergeCell ref="B57:B62"/>
+    <mergeCell ref="B63:B68"/>
+    <mergeCell ref="B69:B75"/>
+    <mergeCell ref="B76:B82"/>
+    <mergeCell ref="B83:B91"/>
+    <mergeCell ref="B92:B98"/>
+    <mergeCell ref="B99:B104"/>
+    <mergeCell ref="B105:B110"/>
+    <mergeCell ref="B111:B116"/>
+    <mergeCell ref="B117:B123"/>
+    <mergeCell ref="B124:B129"/>
+    <mergeCell ref="B130:B134"/>
   </mergeCells>
-  <dataValidations count="103">
+  <dataValidations count="133">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"0: 0 items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
@@ -5796,7 +6886,7 @@
       <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -5805,16 +6895,16 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
       <formula1>"0: Not done,10: Defined"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -5829,85 +6919,85 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
       <formula1>"0: Low Maturity (0-9),4: Developing (10-18),7: Established (19-26),10: Optimizing (27-31)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
       <formula1>"0: Low Maturity. Score Range (0-8),4: Developing. Score Range (9-17),7: Established. Score Range (18-24),10: Optimizing. Score Range (25-29)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
       <formula1>"0: Low Maturity. Score Range (0-15),4: Developing. Score Range (16-31),7: Established. Score Range (32-44),10: Optimizing. Score Range (45-52)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
       <formula1>"0: No items completed,2: item 1 completed,4: items 1-2 completed,6: items 1-3 completed,8: items 1-4 completed,10: items 1-5 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H24">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H25">
-      <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H26">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27">
+      <formula1>"0: No items completed,3: item 1 completed,5: items 1-2 completed,8: items 1-3 completed,10: items 1-4 completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
       <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
-      <formula1>"0: Not done,10: Done and clearly defined"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H30">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H31">
+      <formula1>"0: Not done,10: Done and clearly defined"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H32">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
       <formula1>"0: Not done,10: Defined"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
       <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
       <formula1>"0: Does not exist,10: Exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
       <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
-      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H41">
-      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -5916,31 +7006,31 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H51">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H52">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53">
-      <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54">
-      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H55">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -5949,55 +7039,55 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H57">
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
+      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H58">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
+      <formula1>"0: No teardown/shutdown policy,3: Published policy,6: Classification tagged or otherwise identifiable,10: Enforced Policy with tagged/identifiable classifications"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
+      <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80% ,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
       <formula1>"0: No items completed,5: 1 item  completed,10: 2 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H61">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
-      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
-      <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
-      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H69">
-      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
-      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
-      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
-      <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
-      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H74">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
@@ -6006,22 +7096,22 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H76">
-      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H77">
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H78">
+      <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H78">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79">
-      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H80">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H81">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H82">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -6036,61 +7126,151 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H86">
+      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
+      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
+      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
+      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
+      <formula1>"0: No alerting in workflow tools,1: Alerting in at least one tool,3: Alerting in some tooling [&gt;20%],6: Alerting in most tooling [&gt;60%],10: Alerting in all workflow tools [100%]"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
+      <formula1>"0: No review of trends,3: Manual review of trends,6: Automated trend detection,10: Manual review and automated trend detection"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H105">
+      <formula1>"0: Does not exist,10: Exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H106">
+      <formula1>"0: Does not exist,10: Exists"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H107">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H109">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H110">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H111">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H112">
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H113">
       <formula1>"0: None,1: Annual,2: Quarterly,5: Monthly,7: Bi-Weekly,8: Weekly,10: Daily"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H88">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H114">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H89">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H115">
       <formula1>"0: No alerting,10: Alerting exists"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H90">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H116">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H117">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H118">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H119">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H94">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H120">
       <formula1>"0: No items completed,5: item 1 completed,10: item 2 completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H95">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H121">
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H96">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H122">
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H97">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H123">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H124">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H99">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H125">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H100">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H126">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H127">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H102">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H128">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H103">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H129">
       <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H104">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H130">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H131">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H132">
+      <formula1>"0: Not done,10: Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H133">
       <formula1>"0: Not monitored,2: Reported,5: Manual remediation,10: Automated remediation"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H134">
+      <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -6197,6 +7377,36 @@
     <hyperlink ref="D102" r:id="rId101"/>
     <hyperlink ref="D103" r:id="rId102"/>
     <hyperlink ref="D104" r:id="rId103"/>
+    <hyperlink ref="D105" r:id="rId104"/>
+    <hyperlink ref="D106" r:id="rId105"/>
+    <hyperlink ref="D107" r:id="rId106"/>
+    <hyperlink ref="D108" r:id="rId107"/>
+    <hyperlink ref="D109" r:id="rId108"/>
+    <hyperlink ref="D110" r:id="rId109"/>
+    <hyperlink ref="D111" r:id="rId110"/>
+    <hyperlink ref="D112" r:id="rId111"/>
+    <hyperlink ref="D113" r:id="rId112"/>
+    <hyperlink ref="D114" r:id="rId113"/>
+    <hyperlink ref="D115" r:id="rId114"/>
+    <hyperlink ref="D116" r:id="rId115"/>
+    <hyperlink ref="D117" r:id="rId116"/>
+    <hyperlink ref="D118" r:id="rId117"/>
+    <hyperlink ref="D119" r:id="rId118"/>
+    <hyperlink ref="D120" r:id="rId119"/>
+    <hyperlink ref="D121" r:id="rId120"/>
+    <hyperlink ref="D122" r:id="rId121"/>
+    <hyperlink ref="D123" r:id="rId122"/>
+    <hyperlink ref="D124" r:id="rId123"/>
+    <hyperlink ref="D125" r:id="rId124"/>
+    <hyperlink ref="D126" r:id="rId125"/>
+    <hyperlink ref="D127" r:id="rId126"/>
+    <hyperlink ref="D128" r:id="rId127"/>
+    <hyperlink ref="D129" r:id="rId128"/>
+    <hyperlink ref="D130" r:id="rId129"/>
+    <hyperlink ref="D131" r:id="rId130"/>
+    <hyperlink ref="D132" r:id="rId131"/>
+    <hyperlink ref="D133" r:id="rId132"/>
+    <hyperlink ref="D134" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -415,7 +415,7 @@
     <t>Optimize Pipelines for Timeliness</t>
   </si>
   <si>
-    <t>Define ingestion frequency; include mandatory metadata.</t>
+    <t>Define Data Ingestion Requirements</t>
   </si>
   <si>
     <t>Gather Requirements &amp; Define KPIs</t>
@@ -958,7 +958,7 @@
     <t>2.1.0</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.6.1</t>
   </si>
   <si>
     <t>* Select which teams or groups are in scope for the planned assessments
@@ -2744,7 +2744,7 @@
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -2935,7 +2935,7 @@
         <v>310</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>318</v>
@@ -3056,7 +3056,7 @@
         <v>311</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>319</v>
@@ -3235,7 +3235,7 @@
         <v>310</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>398</v>
@@ -3359,7 +3359,7 @@
         <v>309</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>322</v>
@@ -3550,7 +3550,7 @@
         <v>309</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>327</v>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -2935,7 +2935,7 @@
         <v>310</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>318</v>
@@ -3056,7 +3056,7 @@
         <v>311</v>
       </c>
       <c r="F10">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>319</v>
@@ -3235,7 +3235,7 @@
         <v>310</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>398</v>
@@ -3359,7 +3359,7 @@
         <v>309</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>322</v>
@@ -3550,7 +3550,7 @@
         <v>309</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>327</v>

--- a/assessments/FinOps++/assessment.xlsx
+++ b/assessments/FinOps++/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="417">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -956,6 +956,9 @@
   </si>
   <si>
     <t>2.1.0</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>1.6.1</t>
@@ -1118,6 +1121,21 @@
 * Define thresholds to change
 * Combine with architecture analysis for SP &amp; RIs
 10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Implement architecture changes in time boxed iterations rather than big migrations
+* Track actual cost outcomes vs estimated savings documented in prior trade off analysis
+* Define and monitor success metrics (cost delta, performance, reliability) for each iteration
+* Hold structured retrospectives after each iteration to capture lessons learned
+* Feed iteration outcomes back into the modernization backlog to reprioritize remaining work
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Document and publish cost savings and performance outcomes achieved through architecture changes
+* Update internal architecture reference guides and design patterns with validated approaches
+* Share case studies and reusable blueprints with engineering teams to accelerate adoption
+* Establish a regular cadence to refresh published benefits data and retire outdated references
+10*Ceil(x/4)</t>
   </si>
   <si>
     <t>* Process defined for new accounts and resources deployed
@@ -2810,10 +2828,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2842,10 +2860,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2874,10 +2892,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2906,10 +2924,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2938,10 +2956,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -2972,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -3001,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -3030,7 +3048,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -3059,10 +3077,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -3091,7 +3109,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -3122,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -3151,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3180,7 +3198,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3209,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3238,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3267,7 +3285,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3298,10 +3316,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3330,10 +3348,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3362,10 +3380,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3394,10 +3412,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3426,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3457,10 +3475,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3489,10 +3507,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3521,10 +3539,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3553,10 +3571,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3585,10 +3603,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3617,10 +3635,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3651,7 +3669,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3680,7 +3698,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3709,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3738,7 +3756,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3767,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3796,7 +3814,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -3827,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -3856,10 +3874,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -3888,10 +3906,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -3920,10 +3938,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -3956,7 +3974,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -3985,10 +4003,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -4017,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -4040,13 +4058,16 @@
         <v>216</v>
       </c>
       <c r="E42" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
+      <c r="G42" s="1" t="s">
+        <v>335</v>
+      </c>
       <c r="H42" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -4069,13 +4090,16 @@
         <v>217</v>
       </c>
       <c r="E43" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
+      <c r="G43" s="1" t="s">
+        <v>336</v>
+      </c>
       <c r="H43" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -4104,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -4133,7 +4157,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -4162,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4191,10 +4215,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4223,7 +4247,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4252,7 +4276,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4281,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4312,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4341,7 +4365,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4370,7 +4394,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4399,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4428,7 +4452,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4457,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4488,7 +4512,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4517,7 +4541,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4546,7 +4570,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4575,7 +4599,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4604,7 +4628,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4633,10 +4657,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4667,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4696,7 +4720,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4725,7 +4749,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4754,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4783,7 +4807,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -4812,7 +4836,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -4843,10 +4867,10 @@
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -4875,10 +4899,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -4907,10 +4931,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -4939,10 +4963,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -4971,10 +4995,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -5003,10 +5027,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -5035,7 +5059,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -5066,10 +5090,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -5098,10 +5122,10 @@
         <v>1</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -5130,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -5159,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -5188,7 +5212,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5217,10 +5241,10 @@
         <v>1</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5249,7 +5273,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5280,7 +5304,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5309,7 +5333,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5338,7 +5362,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5367,7 +5391,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5396,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5425,10 +5449,10 @@
         <v>1</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5457,10 +5481,10 @@
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5489,7 +5513,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5512,13 +5536,13 @@
         <v>265</v>
       </c>
       <c r="E91" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5549,7 +5573,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5578,10 +5602,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5610,10 +5634,10 @@
         <v>1</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5642,7 +5666,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -5671,7 +5695,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -5700,7 +5724,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -5729,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -5762,7 +5786,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -5791,7 +5815,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -5820,7 +5844,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -5849,7 +5873,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -5878,7 +5902,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -5907,7 +5931,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -5938,7 +5962,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -5967,7 +5991,7 @@
         <v>1</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -5996,7 +6020,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -6025,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -6054,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -6083,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
@@ -6114,7 +6138,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -6143,10 +6167,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -6175,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -6204,10 +6228,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -6236,7 +6260,7 @@
         <v>1</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6265,10 +6289,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6299,10 +6323,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6331,10 +6355,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6363,10 +6387,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -6395,10 +6419,10 @@
         <v>1</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -6427,10 +6451,10 @@
         <v>1</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -6459,7 +6483,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -6488,10 +6512,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -6522,10 +6546,10 @@
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -6554,10 +6578,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -6586,10 +6610,10 @@
         <v>1</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
@@ -6618,10 +6642,10 @@
         <v>1</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
@@ -6650,10 +6674,10 @@
         <v>1</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
@@ -6682,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
@@ -6715,7 +6739,7 @@
         <v>1</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -6744,7 +6768,7 @@
         <v>1</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I131">
         <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
@@ -6773,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I132">
         <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
@@ -6802,7 +6826,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="I133">
         <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
@@ -6831,7 +6855,7 @@
         <v>1</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I134">
         <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
@@ -6994,10 +7018,10 @@
       <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H42">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H43">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
       <formula1>"0: Not done,10: Completed"</formula1>
